--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
         <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
         <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4382,261 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Brooklyn FC</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rowdies</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>950</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Shenzhen 2028</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -1351,36 +1351,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,33 +1859,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2367,17 +2367,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2402,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,36 +3637,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
         <v>1.01</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,36 +3891,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q14" t="n">
         <v>1.01</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,31 +4150,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,515 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-18 04:37:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Plaza Colonia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Atenas</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,17 +843,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns II</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shenzhen 2028</t>
+          <t>Shandong Taishan B</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -872,7 +872,7 @@
         <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng II</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wenzhou Professional</t>
+          <t>Shenzhen 2028</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,36 +1351,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="Q6" t="n">
         <v>1.01</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2875,17 +2875,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
         <v>1.01</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -4404,12 +4404,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4636,261 +4636,515 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-18 06:47:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Uruguayan Segunda Division</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Plaza Colonia</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Atenas</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-06-18 04:37:53</t>
+      <c r="F18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,222 +872,222 @@
         <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chinese League 2</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns II</t>
+          <t>FK Altay</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shenzhen 2028</t>
+          <t>FC Zhetysu</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1117,224 +1117,224 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
         <v>1.04</v>
       </c>
-      <c r="I3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng II</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wenzhou Professional</t>
+          <t>Shenzhen 2028</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1383,219 +1383,219 @@
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
         <v>3.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
         <v>1.01</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.02</v>
+        <v>1.23</v>
       </c>
       <c r="G7" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>2.14</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>1.38</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,36 +2621,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="Q9" t="n">
         <v>1.01</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.71</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,27 +3129,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
         <v>1.04</v>
       </c>
-      <c r="G12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
         <v>1.04</v>
       </c>
-      <c r="I12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
         <v>1.04</v>
       </c>
-      <c r="G13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
         <v>1.04</v>
       </c>
-      <c r="I13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0</v>
-      </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,36 +3891,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="G15" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="Q16" t="n">
         <v>1.01</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.01</v>
@@ -4890,261 +4890,2547 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Brown de Adrogue</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Argentino de Quilmes</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Excursionistas</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Camioneros</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Real Pilar FC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Villa San Carlos</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Deportivo Armenio</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Flandria</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Villa Dalmine</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sportivo Italiano</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Uruguayan Segunda Division</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tacuarembo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Paysandu FC</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Plaza Colonia</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Atenas</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F27" t="n">
         <v>1.87</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G27" t="n">
         <v>2.14</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H27" t="n">
         <v>4.4</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I27" t="n">
         <v>6.4</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J27" t="n">
         <v>3.1</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K27" t="n">
         <v>3.6</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>2026-06-18 06:47:11</t>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
@@ -890,13 +890,13 @@
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
         <v>1.09</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="H5" t="n">
         <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
@@ -1643,16 +1643,16 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
         <v>1.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R5" t="n">
         <v>1.66</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -1885,22 +1885,22 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
@@ -1909,201 +1909,201 @@
         <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,33 +2113,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Pors</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Irtysh Pavlodar</t>
+          <t>Eik-Tonsberg</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,28 +2151,28 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2292,72 +2292,72 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,246 +2372,246 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Irtysh Pavlodar</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.32</v>
+        <v>1.23</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>1.37</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>1.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.71</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,28 +3388,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Ulytau Zhezkazgan</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,34 +3421,34 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>1.58</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3702,7 +3702,7 @@
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.02</v>
+        <v>1.09</v>
       </c>
       <c r="G14" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>1.09</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -4912,12 +4912,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -5161,17 +5161,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -5415,17 +5415,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5450,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -5695,7 +5695,7 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5704,7 +5704,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>2.82</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,36 +6685,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -7176,261 +7176,515 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:11:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Uruguayan Segunda Division</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Plaza Colonia</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Atenas</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="F28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I28" t="n">
         <v>6.4</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J28" t="n">
         <v>3.1</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K28" t="n">
         <v>3.6</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB27" t="inlineStr">
-        <is>
-          <t>2026-06-18 08:58:41</t>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,10 +881,10 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
@@ -899,16 +899,16 @@
         <v>1.56</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1144,13 +1144,13 @@
         <v>1.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
         <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q4" t="n">
         <v>1.47</v>
@@ -1404,19 +1404,19 @@
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -1619,145 +1619,145 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G5" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
         <v>5.9</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.62</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q5" t="n">
         <v>1.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
@@ -1766,28 +1766,28 @@
         <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK5" t="n">
         <v>1.01</v>
@@ -1799,50 +1799,50 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS5" t="n">
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
         <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY5" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA5" t="n">
         <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1912,19 +1912,19 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.02</v>
       </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2166,19 +2166,19 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.02</v>
       </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.46</v>
+        <v>1.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.48</v>
+        <v>1.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2797,10 +2797,10 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>2.92</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.57</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="X11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC11" t="n">
         <v>7.6</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.3</v>
+        <v>2.96</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.82</v>
+        <v>2.34</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BK11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT11" t="n">
         <v>6.6</v>
       </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>13</v>
-      </c>
       <c r="BU11" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,121 +3388,121 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1.58</v>
       </c>
       <c r="H12" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="S12" t="n">
-        <v>1.08</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP12" t="n">
         <v>1.01</v>
@@ -3511,10 +3511,10 @@
         <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
         <v>1.01</v>
@@ -3526,7 +3526,7 @@
         <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
         <v>1.01</v>
@@ -3559,75 +3559,75 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,33 +3637,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.58</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="P13" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3702,7 +3702,7 @@
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3759,52 +3759,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3816,65 +3816,65 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -3911,13 +3911,13 @@
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.09</v>
+        <v>2.3</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3956,7 +3956,7 @@
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dalvik/Reynir</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,17 +4399,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KF Fjallabyggd</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4425,225 +4425,225 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P16" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
         <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="P17" t="n">
-        <v>1.63</v>
+        <v>1.07</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,244 +4907,244 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -5415,17 +5415,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -5669,17 +5669,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -5695,7 +5695,7 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5704,7 +5704,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -5928,12 +5928,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6457,7 +6457,7 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,36 +6685,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,36 +6939,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -7430,261 +7430,515 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-18 13:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Uruguayan Segunda Division</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Plaza Colonia</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Atenas</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="F29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G29" t="n">
         <v>2.08</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H29" t="n">
         <v>4.8</v>
       </c>
-      <c r="I28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="I29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J29" t="n">
         <v>3.1</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K29" t="n">
         <v>3.6</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB28" t="inlineStr">
-        <is>
-          <t>2026-06-18 11:11:50</t>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB29"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -890,7 +890,7 @@
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O3" t="n">
         <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q3" t="n">
         <v>1.4</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1398,7 +1398,7 @@
         <v>1.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1652,13 +1652,13 @@
         <v>2.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R5" t="n">
         <v>1.68</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
         <v>1.46</v>
@@ -1787,16 +1787,16 @@
         <v>3.8</v>
       </c>
       <c r="BJ5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
@@ -1808,13 +1808,13 @@
         <v>16</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR5" t="n">
         <v>23</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT5" t="n">
         <v>7</v>
@@ -1826,23 +1826,23 @@
         <v>20</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX5" t="n">
         <v>26</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2166,7 +2166,7 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2292,65 +2292,65 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2420,7 +2420,7 @@
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.25</v>
@@ -2668,7 +2668,7 @@
         <v>1.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R9" t="n">
         <v>1.05</v>
@@ -2677,16 +2677,16 @@
         <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2800,65 +2800,65 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2892,13 +2892,13 @@
         <v>2.34</v>
       </c>
       <c r="G10" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
         <v>2.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
         <v>2.92</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.01</v>
@@ -2922,7 +2922,7 @@
         <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.14</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
         <v>2.74</v>
@@ -3161,7 +3161,7 @@
         <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
@@ -3194,7 +3194,7 @@
         <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="G12" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.25</v>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
         <v>1.57</v>
@@ -3436,19 +3436,19 @@
         <v>1.49</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="V12" t="n">
         <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="X12" t="n">
         <v>28</v>
@@ -3457,10 +3457,10 @@
         <v>38</v>
       </c>
       <c r="Z12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA12" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="AB12" t="n">
         <v>12</v>
@@ -3469,10 +3469,10 @@
         <v>14.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE12" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF12" t="n">
         <v>11.5</v>
@@ -3481,13 +3481,13 @@
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
         <v>18</v>
@@ -3496,67 +3496,67 @@
         <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
         <v>6.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH12" t="n">
         <v>4.6</v>
@@ -3580,10 +3580,10 @@
         <v>4.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="BP12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ12" t="n">
         <v>4</v>
@@ -3595,10 +3595,10 @@
         <v>5.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3613,14 +3613,14 @@
         <v>6.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O13" t="n">
         <v>1.08</v>
@@ -3816,65 +3816,65 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -3896,29 +3896,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FK Ulytau Zhezkazgan</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.09</v>
       </c>
-      <c r="G14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="K14" t="n">
         <v>1000</v>
       </c>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3956,7 +3956,7 @@
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4165,13 +4165,13 @@
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.58</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,22 +4183,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -4210,7 +4210,7 @@
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.07</v>
@@ -4452,13 +4452,13 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -4578,72 +4578,72 @@
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,28 +4658,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>KFA Austfjarda</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KF Fjallabyggd</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,28 +4691,28 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="P17" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
@@ -4832,72 +4832,72 @@
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,31 +4912,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4945,34 +4945,34 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>1.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="S18" t="n">
-        <v>2.28</v>
+        <v>1.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5083,75 +5083,75 @@
         <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,244 +5161,244 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -5420,12 +5420,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -5441,22 +5441,22 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
@@ -5465,194 +5465,194 @@
         <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -5669,17 +5669,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -5695,22 +5695,22 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P21" t="n">
         <v>1.24</v>
@@ -5719,194 +5719,194 @@
         <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -5923,17 +5923,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5955,16 +5955,16 @@
         <v>1000</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P22" t="n">
         <v>1.24</v>
@@ -5973,194 +5973,194 @@
         <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,36 +6939,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="K26" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,36 +7193,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -7684,261 +7684,515 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:36:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Uruguayan Segunda Division</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Plaza Colonia</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Atenas</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F30" t="n">
         <v>1.9</v>
       </c>
-      <c r="G29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="G30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H30" t="n">
         <v>4.8</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>5.7</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>3.1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K30" t="n">
         <v>3.6</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>1.52</v>
       </c>
-      <c r="Q29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB29" t="inlineStr">
-        <is>
-          <t>2026-06-18 13:25:02</t>
+      <c r="Q30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB30"/>
+  <dimension ref="A1:CB36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
         <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.22</v>
       </c>
       <c r="G5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.9</v>
@@ -1637,7 +1637,7 @@
         <v>4.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
@@ -1652,7 +1652,7 @@
         <v>2.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R5" t="n">
         <v>1.68</v>
@@ -1661,7 +1661,7 @@
         <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U5" t="n">
         <v>2.68</v>
@@ -1727,7 +1727,7 @@
         <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ5" t="n">
         <v>15</v>
@@ -1736,7 +1736,7 @@
         <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
         <v>13</v>
@@ -1754,16 +1754,16 @@
         <v>15</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC5" t="n">
         <v>16.5</v>
@@ -1772,7 +1772,7 @@
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
         <v>8.4</v>
@@ -1790,7 +1790,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP5" t="n">
         <v>16</v>
@@ -1820,7 +1820,7 @@
         <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV5" t="n">
         <v>20</v>
@@ -1838,11 +1838,11 @@
         <v>14.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2665,7 +2665,7 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Q9" t="n">
         <v>1.24</v>
@@ -2674,7 +2674,7 @@
         <v>1.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -2889,46 +2889,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J10" t="n">
-        <v>2.92</v>
+        <v>2.24</v>
       </c>
       <c r="K10" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2937,52 +2937,52 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2991,64 +2991,64 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -3143,61 +3143,61 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
         <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
         <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W11" t="n">
         <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
@@ -3206,7 +3206,7 @@
         <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
         <v>8.800000000000001</v>
@@ -3215,52 +3215,52 @@
         <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>50</v>
       </c>
-      <c r="AF11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>60</v>
-      </c>
       <c r="AK11" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AL11" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM11" t="n">
         <v>180</v>
       </c>
       <c r="AN11" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
@@ -3272,7 +3272,7 @@
         <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
         <v>13</v>
@@ -3281,28 +3281,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC11" t="n">
         <v>28</v>
       </c>
-      <c r="BC11" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF11" t="n">
         <v>25</v>
       </c>
       <c r="BG11" t="n">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="n">
         <v>2.96</v>
@@ -3344,7 +3344,7 @@
         <v>6.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H12" t="n">
         <v>7.6</v>
       </c>
       <c r="I12" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K12" t="n">
         <v>6.2</v>
@@ -3421,49 +3421,49 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
         <v>1.57</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
         <v>2.44</v>
       </c>
       <c r="T12" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
         <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="X12" t="n">
         <v>28</v>
       </c>
       <c r="Y12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z12" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA12" t="n">
         <v>330</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
         <v>14.5</v>
@@ -3475,13 +3475,13 @@
         <v>150</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG12" t="n">
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI12" t="n">
         <v>130</v>
@@ -3490,16 +3490,16 @@
         <v>15</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
         <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO12" t="n">
         <v>180</v>
@@ -3508,13 +3508,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
         <v>7.2</v>
@@ -3523,58 +3523,58 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
         <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF12" t="n">
         <v>4.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH12" t="n">
         <v>4.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN12" t="n">
         <v>4.4</v>
@@ -3586,19 +3586,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BR12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT12" t="n">
         <v>13</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3610,17 +3610,17 @@
         <v>70</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA12" t="n">
         <v>4.7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -3759,52 +3759,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,55 +3896,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>KFG</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>Dalvik/Reynir</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S14" t="n">
         <v>1.05</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.21</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3956,7 +3956,7 @@
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -4150,28 +4150,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Ulytau Zhezkazgan</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.38</v>
+        <v>1.6</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,22 +4183,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -4210,7 +4210,7 @@
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,22 +4404,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KFG</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalvik/Reynir</t>
+          <t>FK Ulytau Zhezkazgan</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -4440,19 +4440,19 @@
         <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4521,52 +4521,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,28 +4658,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KFA Austfjarda</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4694,19 +4694,19 @@
         <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KF Fjallabyggd</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>2.86</v>
       </c>
       <c r="O18" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,55 +5166,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>KFA Austfjarda</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.64</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="P19" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>1.05</v>
       </c>
       <c r="T19" t="n">
         <v>1.11</v>
@@ -5223,10 +5223,10 @@
         <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5283,122 +5283,122 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.01</v>
@@ -5462,7 +5462,7 @@
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R20" t="n">
         <v>1.12</v>
@@ -5477,10 +5477,10 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5537,52 +5537,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5707,7 +5707,7 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
         <v>1.01</v>
@@ -5731,10 +5731,10 @@
         <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -5791,52 +5791,52 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5973,7 +5973,7 @@
         <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
         <v>1.05</v>
@@ -5985,10 +5985,10 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6045,52 +6045,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -6203,218 +6203,218 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P23" t="n">
         <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6457,22 +6457,22 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
@@ -6481,194 +6481,194 @@
         <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -6711,22 +6711,22 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
         <v>1.24</v>
@@ -6735,194 +6735,194 @@
         <v>1.01</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -6965,225 +6965,225 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P26" t="n">
         <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,246 +7198,246 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="G27" t="n">
         <v>2.28</v>
       </c>
       <c r="H27" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,234 +7447,234 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,251 +7701,251 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Anapolis GO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,244 +7955,1768 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="G30" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="H30" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I30" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
         <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-18 17:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chilean Segunda Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Deportes Rengo Unido</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-06-18 17:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Santa Cruz PE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ypiranga RS</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-06-18 17:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plaza Colonia</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Atenas</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2.54</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>2026-06-18 15:36:00</t>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-06-18 17:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>2026-06-18 17:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="inlineStr">
+        <is>
+          <t>2026-06-18 17:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="inlineStr">
+        <is>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.22</v>
       </c>
       <c r="G5" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
         <v>2.72</v>
@@ -1631,218 +1631,218 @@
         <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="R5" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="U5" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="V5" t="n">
         <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X5" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z5" t="n">
         <v>34</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>29</v>
       </c>
       <c r="AA5" t="n">
         <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
         <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AN5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV5" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
         <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
         <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.6</v>
+        <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
         <v>11.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BP5" t="n">
         <v>16</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT5" t="n">
         <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV5" t="n">
         <v>20</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA5" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2665,13 +2665,13 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Q9" t="n">
         <v>1.24</v>
       </c>
       <c r="R9" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="S9" t="n">
         <v>1.35</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -2901,34 +2901,34 @@
         <v>3.85</v>
       </c>
       <c r="J10" t="n">
-        <v>2.24</v>
+        <v>2.68</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2946,43 +2946,43 @@
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2991,64 +2991,64 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
         <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J11" t="n">
         <v>2.88</v>
@@ -3161,34 +3161,34 @@
         <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
         <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
         <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
         <v>1.39</v>
@@ -3251,7 +3251,7 @@
         <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.6</v>
@@ -3287,7 +3287,7 @@
         <v>6.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BC11" t="n">
         <v>28</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.37</v>
       </c>
       <c r="G12" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="H12" t="n">
         <v>7.6</v>
@@ -3415,7 +3415,7 @@
         <v>6.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -3439,16 +3439,16 @@
         <v>2.44</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V12" t="n">
         <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="X12" t="n">
         <v>28</v>
@@ -3463,7 +3463,7 @@
         <v>330</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
         <v>14.5</v>
@@ -3508,13 +3508,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>7.2</v>
@@ -3523,10 +3523,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
@@ -3538,25 +3538,25 @@
         <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BB12" t="n">
         <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
         <v>4.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH12" t="n">
         <v>4.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4210,7 +4210,7 @@
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -4775,52 +4775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
         <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I18" t="n">
         <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="K18" t="n">
         <v>3.55</v>
@@ -4954,7 +4954,7 @@
         <v>1.61</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R18" t="n">
         <v>1.22</v>
@@ -4963,16 +4963,16 @@
         <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V18" t="n">
         <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X18" t="n">
         <v>12.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5462,13 +5462,13 @@
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R20" t="n">
         <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>1.6</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5477,7 +5477,7 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
         <v>1.02</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5716,13 +5716,13 @@
         <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R21" t="n">
         <v>1.12</v>
       </c>
       <c r="S21" t="n">
-        <v>1.05</v>
+        <v>1.6</v>
       </c>
       <c r="T21" t="n">
         <v>1.11</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,7 +5961,7 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,7 +6215,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.16</v>
@@ -6224,13 +6224,13 @@
         <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="R23" t="n">
         <v>1.12</v>
       </c>
       <c r="S23" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6239,7 +6239,7 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
         <v>1.02</v>
@@ -6299,52 +6299,52 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6469,7 +6469,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
         <v>1.01</v>
@@ -6478,13 +6478,13 @@
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R24" t="n">
         <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>1.05</v>
+        <v>1.66</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6553,52 +6553,52 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6723,7 +6723,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="O25" t="n">
         <v>1.01</v>
@@ -6732,13 +6732,13 @@
         <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R25" t="n">
         <v>1.12</v>
       </c>
       <c r="S25" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -6977,7 +6977,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.01</v>
@@ -6992,7 +6992,7 @@
         <v>1.12</v>
       </c>
       <c r="S26" t="n">
-        <v>1.05</v>
+        <v>1.7</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G27" t="n">
         <v>2.22</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.28</v>
-      </c>
       <c r="H27" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I27" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K27" t="n">
         <v>3.7</v>
@@ -7231,16 +7231,16 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R27" t="n">
         <v>1.37</v>
@@ -7255,22 +7255,22 @@
         <v>2.14</v>
       </c>
       <c r="V27" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W27" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X27" t="n">
         <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB27" t="n">
         <v>10.5</v>
@@ -7279,16 +7279,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>42</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
         <v>17.5</v>
@@ -7303,16 +7303,16 @@
         <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP27" t="n">
         <v>12.5</v>
@@ -7342,31 +7342,31 @@
         <v>13</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
         <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
         <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BF27" t="n">
         <v>15.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BH27" t="n">
         <v>3.45</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
         <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
@@ -7626,7 +7626,7 @@
         <v>3.05</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -7757,10 +7757,10 @@
         <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
         <v>1.25</v>
@@ -7823,52 +7823,52 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
         <v>1.01</v>
@@ -7880,65 +7880,65 @@
         <v>3.05</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BN29" t="n">
         <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -7972,37 +7972,37 @@
         <v>1.99</v>
       </c>
       <c r="G30" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I30" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="R30" t="n">
         <v>1.17</v>
@@ -8011,16 +8011,16 @@
         <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W30" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8077,52 +8077,52 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
         <v>1.01</v>
@@ -8134,65 +8134,65 @@
         <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -8247,16 +8247,16 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O31" t="n">
         <v>1.01</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="R31" t="n">
         <v>1.16</v>
@@ -8265,10 +8265,10 @@
         <v>2.46</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
@@ -8331,52 +8331,52 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
         <v>1.01</v>
@@ -8388,65 +8388,65 @@
         <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31" t="n">
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT31" t="n">
         <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -8483,10 +8483,10 @@
         <v>2.26</v>
       </c>
       <c r="H32" t="n">
-        <v>1.79</v>
+        <v>3.75</v>
       </c>
       <c r="I32" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J32" t="n">
         <v>2.84</v>
@@ -8495,212 +8495,212 @@
         <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q32" t="n">
         <v>2.38</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -8749,212 +8749,212 @@
         <v>3.6</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P33" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q33" t="n">
         <v>2.54</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -8985,230 +8985,230 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P34" t="n">
         <v>1.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BT34" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BX34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -9239,230 +9239,230 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB36"/>
+  <dimension ref="A1:CB37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
         <v>1.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.12</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1365,20 +1365,20 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
         <v>1.1</v>
       </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.19</v>
-      </c>
       <c r="K4" t="n">
         <v>1000</v>
       </c>
@@ -1389,10 +1389,10 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
@@ -1401,10 +1401,10 @@
         <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
         <v>1.42</v>
       </c>
       <c r="U5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V5" t="n">
         <v>1.46</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1873,20 +1873,20 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.1</v>
       </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.19</v>
-      </c>
       <c r="K6" t="n">
         <v>1000</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O9" t="n">
         <v>1.25</v>
@@ -2668,13 +2668,13 @@
         <v>1.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R9" t="n">
         <v>1.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2892,13 +2892,13 @@
         <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
         <v>2.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
         <v>2.68</v>
@@ -2910,19 +2910,19 @@
         <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P10" t="n">
         <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.14</v>
@@ -2946,43 +2946,43 @@
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2991,64 +2991,64 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
         <v>2.7</v>
@@ -3161,7 +3161,7 @@
         <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
@@ -3260,7 +3260,7 @@
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
@@ -3272,7 +3272,7 @@
         <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX11" t="n">
         <v>13</v>
@@ -3284,7 +3284,7 @@
         <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
         <v>32</v>
@@ -3293,16 +3293,16 @@
         <v>28</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
         <v>25</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="BH11" t="n">
         <v>2.96</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
         <v>6.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -3454,10 +3454,10 @@
         <v>28</v>
       </c>
       <c r="Y12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AA12" t="n">
         <v>330</v>
@@ -3481,7 +3481,7 @@
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI12" t="n">
         <v>130</v>
@@ -3490,7 +3490,7 @@
         <v>15</v>
       </c>
       <c r="AK12" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
         <v>42</v>
@@ -3499,7 +3499,7 @@
         <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
         <v>180</v>
@@ -3508,13 +3508,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS12" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>7.2</v>
@@ -3523,10 +3523,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
@@ -3535,10 +3535,10 @@
         <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
         <v>9</v>
@@ -3547,16 +3547,16 @@
         <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BF12" t="n">
         <v>4.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BH12" t="n">
         <v>4.6</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4210,7 +4210,7 @@
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G18" t="n">
         <v>2.24</v>
@@ -4933,13 +4933,13 @@
         <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
         <v>3.55</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
@@ -5086,7 +5086,7 @@
         <v>3</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="BJ18" t="n">
         <v>11.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,16 +5453,16 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="R20" t="n">
         <v>1.12</v>
@@ -5477,7 +5477,7 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
         <v>1.02</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5716,7 +5716,7 @@
         <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
         <v>1.12</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6239,7 +6239,7 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
         <v>1.02</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6469,16 +6469,16 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="R24" t="n">
         <v>1.12</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6723,19 +6723,19 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O25" t="n">
         <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S25" t="n">
         <v>1.55</v>
@@ -6747,7 +6747,7 @@
         <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -6980,7 +6980,7 @@
         <v>1.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P26" t="n">
         <v>1.24</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,246 +7198,246 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H27" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I27" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="P27" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="U27" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="V27" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W27" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="X27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y27" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>14</v>
-      </c>
       <c r="Z27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH27" t="n">
         <v>26</v>
       </c>
-      <c r="AA27" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AI27" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AJ27" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AL27" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AM27" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="AN27" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AO27" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AP27" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS27" t="n">
-        <v>55</v>
+        <v>4.3</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV27" t="n">
         <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>36</v>
+        <v>4.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
         <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>44</v>
+        <v>4.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BC27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>34</v>
+        <v>4.3</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="BJ27" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO27" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="BP27" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BR27" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BS27" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BT27" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BV27" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BW27" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY27" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ27" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA27" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,239 +7452,239 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="G28" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H28" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="J28" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>2.86</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="R28" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="V28" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD28" t="n">
         <v>15</v>
       </c>
-      <c r="Z28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR28" t="n">
         <v>22</v>
       </c>
-      <c r="AE28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>21</v>
-      </c>
       <c r="AS28" t="n">
-        <v>4.2</v>
+        <v>55</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="AX28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
         <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.1</v>
+        <v>44</v>
       </c>
       <c r="BB28" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC28" t="n">
         <v>20</v>
       </c>
-      <c r="BC28" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BD28" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BF28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP28" t="n">
         <v>16.5</v>
       </c>
-      <c r="BG28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ28" t="n">
+      <c r="BQ28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY28" t="n">
         <v>11</v>
       </c>
-      <c r="BK28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>2.64</v>
       </c>
       <c r="H29" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I29" t="n">
         <v>5</v>
@@ -7730,7 +7730,7 @@
         <v>2.62</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7742,10 +7742,10 @@
         <v>2.48</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q29" t="n">
         <v>2.58</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -8247,13 +8247,13 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q31" t="n">
         <v>1.32</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,246 +8468,246 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="G32" t="n">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="H32" t="n">
-        <v>3.75</v>
+        <v>2.94</v>
       </c>
       <c r="I32" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X32" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>2.84</v>
       </c>
-      <c r="K32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK32" t="n">
         <v>3.15</v>
       </c>
-      <c r="BI32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK32" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.48</v>
+        <v>4.1</v>
       </c>
       <c r="BN32" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.48</v>
+        <v>3.65</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.48</v>
+        <v>3.55</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.48</v>
+        <v>3.8</v>
       </c>
       <c r="BT32" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.48</v>
+        <v>4.5</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.48</v>
+        <v>3.7</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.48</v>
+        <v>3.85</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.48</v>
+        <v>3.8</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8722,246 +8722,246 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H33" t="n">
         <v>4.8</v>
       </c>
       <c r="I33" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K33" t="n">
         <v>3.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M33" t="n">
         <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="O33" t="n">
         <v>1.5</v>
       </c>
       <c r="P33" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="R33" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V33" t="n">
         <v>1.21</v>
       </c>
       <c r="W33" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH33" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33" t="n">
         <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BN33" t="n">
         <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BT33" t="n">
         <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,246 +8976,246 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="G34" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S34" t="n">
         <v>2.68</v>
       </c>
-      <c r="H34" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.55</v>
-      </c>
       <c r="T34" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="W34" t="n">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="X34" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="n">
         <v>3.15</v>
       </c>
-      <c r="AT34" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BI34" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="BJ34" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.15</v>
+        <v>1.48</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>4.1</v>
+        <v>1.48</v>
       </c>
       <c r="BN34" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.65</v>
+        <v>1.48</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>3.55</v>
+        <v>1.48</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>3.8</v>
+        <v>1.48</v>
       </c>
       <c r="BT34" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>4.5</v>
+        <v>1.48</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>3.7</v>
+        <v>1.48</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>3.85</v>
+        <v>1.48</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>3.8</v>
+        <v>1.48</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9230,246 +9230,246 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.92</v>
       </c>
-      <c r="G35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.95</v>
-      </c>
       <c r="X35" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ35" t="n">
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BN35" t="n">
         <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BT35" t="n">
         <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BZ35" t="n">
         <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9479,234 +9479,234 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.98</v>
+        <v>5.5</v>
       </c>
       <c r="G36" t="n">
-        <v>2.16</v>
+        <v>7.4</v>
       </c>
       <c r="H36" t="n">
-        <v>4.2</v>
+        <v>1.56</v>
       </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>1.71</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P36" t="n">
-        <v>1.64</v>
+        <v>2.22</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ36" t="n">
         <v>0</v>
@@ -9716,7 +9716,261 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB37" t="inlineStr">
+        <is>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB37"/>
+  <dimension ref="A1:CB42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -890,7 +890,7 @@
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.02</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         <v>14.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>16.5</v>
@@ -1736,7 +1736,7 @@
         <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>34</v>
+        <v>5.5</v>
       </c>
       <c r="AT5" t="n">
         <v>14.5</v>
@@ -1763,7 +1763,7 @@
         <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
         <v>15</v>
@@ -1838,11 +1838,11 @@
         <v>14</v>
       </c>
       <c r="CA5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.13</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2178,7 +2178,7 @@
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
         <v>2.14</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>1.19</v>
+        <v>2.7</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="O9" t="n">
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Q9" t="n">
         <v>1.25</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
         <v>2.6</v>
@@ -2913,7 +2913,7 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
         <v>1.04</v>
@@ -2922,7 +2922,7 @@
         <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R10" t="n">
         <v>1.14</v>
@@ -2940,7 +2940,7 @@
         <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2955,7 +2955,7 @@
         <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.800000000000001</v>
@@ -3003,10 +3003,10 @@
         <v>6.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.14</v>
+        <v>12.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AT10" t="n">
         <v>6</v>
@@ -3018,7 +3018,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3030,25 +3030,25 @@
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BB10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BC10" t="n">
         <v>2.26</v>
       </c>
-      <c r="BC10" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BD10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>IF Magni</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.82</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="P11" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>1.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>1.08</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.52</v>
       </c>
-      <c r="H12" t="n">
+      <c r="X12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC12" t="n">
         <v>7.6</v>
       </c>
-      <c r="I12" t="n">
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV12" t="n">
         <v>10.5</v>
       </c>
-      <c r="J12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="AW12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT12" t="n">
         <v>6.2</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X12" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>330</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU12" t="n">
+      <c r="BU12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>4.7</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,239 +3642,239 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IF Magni</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.52</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.26</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>1.08</v>
+        <v>2.46</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4165,13 @@
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -4437,10 +4437,10 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
         <v>1.36</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,28 +4658,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Augnablik</t>
+          <t>KFA Austfjarda</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KF Fjallabyggd</t>
+          <t>Kormakur/Hvot</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4694,16 +4694,16 @@
         <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="P17" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
         <v>1.05</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Augnablik</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>KF Fjallabyggd</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.06</v>
+        <v>1.02</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
         <v>1.1</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.86</v>
-      </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>1.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>1.05</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,239 +5166,239 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KFA Austfjarda</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kormakur/Hvot</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H19" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>2.86</v>
       </c>
       <c r="O19" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
@@ -6723,19 +6723,19 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O25" t="n">
         <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
         <v>1.01</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S25" t="n">
         <v>1.55</v>
@@ -6750,7 +6750,7 @@
         <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G26" t="n">
         <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I26" t="n">
         <v>1000</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,246 +7198,246 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paysandu FC</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G27" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.8</v>
       </c>
-      <c r="I27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O27" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="R27" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="T27" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="V27" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W27" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X27" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF27" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>15</v>
-      </c>
       <c r="AG27" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AJ27" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AK27" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="AN27" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.3</v>
+        <v>55</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
         <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.2</v>
+        <v>36</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
         <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.3</v>
+        <v>44</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BC27" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="BF27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP27" t="n">
         <v>16.5</v>
       </c>
-      <c r="BG27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ27" t="n">
+      <c r="BQ27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY27" t="n">
         <v>11</v>
       </c>
-      <c r="BK27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV27" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,239 +7452,239 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Paysandu FC</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G28" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H28" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I28" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.6</v>
       </c>
-      <c r="K28" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="V28" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W28" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="X28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y28" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y28" t="n">
-        <v>14</v>
-      </c>
       <c r="Z28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH28" t="n">
         <v>26</v>
       </c>
-      <c r="AA28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AI28" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AJ28" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK28" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AL28" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="AN28" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AO28" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AP28" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>55</v>
+        <v>4.3</v>
       </c>
       <c r="AT28" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>36</v>
+        <v>4.3</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
         <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>44</v>
+        <v>4.3</v>
       </c>
       <c r="BB28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BC28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>4.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>34</v>
+        <v>4.3</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="BJ28" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BN28" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO28" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="BP28" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR28" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BS28" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BT28" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU28" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BV28" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BW28" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY28" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ28" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA28" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>2.44</v>
@@ -7984,7 +7984,7 @@
         <v>2.74</v>
       </c>
       <c r="K30" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="L30" t="n">
         <v>1.43</v>
@@ -7993,7 +7993,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
         <v>1.23</v>
@@ -8002,7 +8002,7 @@
         <v>1.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
         <v>1.17</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
         <v>1.16</v>
       </c>
       <c r="S31" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,246 +8468,246 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Atenas</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="G32" t="n">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="H32" t="n">
-        <v>2.94</v>
+        <v>4.8</v>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.82</v>
+        <v>2.42</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="P32" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="S32" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="W32" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="X32" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="n">
         <v>3.15</v>
       </c>
-      <c r="AT32" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BI32" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="BJ32" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>3.15</v>
+        <v>1.48</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>4.1</v>
+        <v>1.48</v>
       </c>
       <c r="BN32" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.65</v>
+        <v>1.48</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>3.55</v>
+        <v>1.48</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>3.8</v>
+        <v>1.48</v>
       </c>
       <c r="BT32" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>4.5</v>
+        <v>1.48</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>3.7</v>
+        <v>1.48</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>3.85</v>
+        <v>1.48</v>
       </c>
       <c r="BZ32" t="n">
         <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>3.8</v>
+        <v>1.48</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8722,246 +8722,246 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Santa Cruz PE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="G33" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="H33" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="I33" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="J33" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="n">
         <v>3.15</v>
       </c>
-      <c r="K33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="X33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI33" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ33" t="n">
         <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BN33" t="n">
         <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BP33" t="n">
         <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BR33" t="n">
         <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BT33" t="n">
         <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BV33" t="n">
         <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,55 +8976,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Santa Cruz PE</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="G34" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="H34" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="I34" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N34" t="n">
-        <v>2.18</v>
+        <v>2.82</v>
       </c>
       <c r="O34" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="R34" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="S34" t="n">
-        <v>2.68</v>
+        <v>3.55</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -9033,189 +9033,189 @@
         <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="W34" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK34" t="n">
         <v>3.15</v>
       </c>
-      <c r="BI34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.48</v>
+        <v>4.1</v>
       </c>
       <c r="BN34" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.48</v>
+        <v>3.65</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.48</v>
+        <v>3.55</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.48</v>
+        <v>3.8</v>
       </c>
       <c r="BT34" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.48</v>
+        <v>4.5</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.48</v>
+        <v>3.7</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.48</v>
+        <v>3.85</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.48</v>
+        <v>3.8</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9230,239 +9230,239 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atenas</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H35" t="n">
         <v>4.8</v>
       </c>
       <c r="I35" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K35" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M35" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N35" t="n">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="O35" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P35" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R35" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T35" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U35" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V35" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W35" t="n">
         <v>1.92</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ35" t="n">
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BN35" t="n">
         <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BT35" t="n">
         <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BZ35" t="n">
         <v>1000</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="O36" t="n">
         <v>1.2</v>
@@ -9529,7 +9529,7 @@
         <v>1.65</v>
       </c>
       <c r="R36" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
         <v>2.56</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -9918,59 +9918,1329 @@
         <v>1000</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BN37" t="n">
         <v>1000</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BT37" t="n">
         <v>1000</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Maranhao</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CB38" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:23:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Birmingham Legion FC</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Loudoun United FC</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:23:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks FC</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Colorado Springs Switchback</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X40" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:23:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>23:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Monterey Bay FC</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB41" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:23:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Phoenix Rising FC</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB42" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1141,7 +1141,7 @@
         <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O4" t="n">
         <v>1.47</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G5" t="n">
         <v>2.5</v>
@@ -1628,10 +1628,10 @@
         <v>2.72</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
         <v>4.8</v>
@@ -1643,13 +1643,13 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>1.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="Q5" t="n">
         <v>1.44</v>
@@ -1658,7 +1658,7 @@
         <v>1.8</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T5" t="n">
         <v>1.42</v>
@@ -1679,7 +1679,7 @@
         <v>26</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
         <v>55</v>
@@ -1706,7 +1706,7 @@
         <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="n">
         <v>38</v>
@@ -1724,61 +1724,61 @@
         <v>10</v>
       </c>
       <c r="AO5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>17</v>
+        <v>4.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="n">
         <v>5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R9" t="n">
         <v>1.1</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H10" t="n">
         <v>2.6</v>
@@ -2904,7 +2904,7 @@
         <v>2.68</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
@@ -2940,7 +2940,7 @@
         <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3018,7 +3018,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3027,13 +3027,13 @@
         <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12.5</v>
+        <v>2.18</v>
       </c>
       <c r="BA10" t="n">
         <v>2.34</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BC10" t="n">
         <v>2.26</v>
@@ -3048,7 +3048,7 @@
         <v>2.26</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G12" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H12" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
         <v>3.4</v>
@@ -3418,10 +3418,10 @@
         <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O12" t="n">
         <v>1.46</v>
@@ -3436,16 +3436,16 @@
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T12" t="n">
         <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.52</v>
@@ -3463,7 +3463,7 @@
         <v>80</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
         <v>7.6</v>
@@ -3478,7 +3478,7 @@
         <v>28</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>25</v>
@@ -3493,7 +3493,7 @@
         <v>44</v>
       </c>
       <c r="AL12" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AM12" t="n">
         <v>180</v>
@@ -3508,7 +3508,7 @@
         <v>8.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
         <v>14.5</v>
@@ -3526,10 +3526,10 @@
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY12" t="n">
         <v>12.5</v>
@@ -3538,7 +3538,7 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB12" t="n">
         <v>32</v>
@@ -3547,10 +3547,10 @@
         <v>30</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
         <v>25</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H13" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I13" t="n">
         <v>10.5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
@@ -3693,16 +3693,16 @@
         <v>2.46</v>
       </c>
       <c r="T13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X13" t="n">
         <v>28</v>
@@ -3711,10 +3711,10 @@
         <v>38</v>
       </c>
       <c r="Z13" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA13" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AB13" t="n">
         <v>12</v>
@@ -3723,10 +3723,10 @@
         <v>14.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE13" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF13" t="n">
         <v>10.5</v>
@@ -3738,7 +3738,7 @@
         <v>29</v>
       </c>
       <c r="AI13" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ13" t="n">
         <v>15</v>
@@ -3756,64 +3756,64 @@
         <v>7</v>
       </c>
       <c r="AO13" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP13" t="n">
-        <v>16</v>
+        <v>3.85</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AS13" t="n">
         <v>4.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.4</v>
+        <v>3.35</v>
       </c>
       <c r="AU13" t="n">
-        <v>9</v>
+        <v>3.65</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.6</v>
+        <v>3.15</v>
       </c>
       <c r="AY13" t="n">
-        <v>7.8</v>
+        <v>3.55</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>3.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.4</v>
+        <v>3.45</v>
       </c>
       <c r="BC13" t="n">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI13" t="n">
         <v>3.25</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN13" t="n">
         <v>4.4</v>
@@ -3840,31 +3840,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR13" t="n">
         <v>25</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT13" t="n">
         <v>13</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW13" t="n">
         <v>6.4</v>
       </c>
       <c r="BX13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>14.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4210,7 +4210,7 @@
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3</v>
+        <v>1.09</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -4443,7 +4443,7 @@
         <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
         <v>1.43</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K19" t="n">
         <v>3.55</v>
@@ -5223,22 +5223,22 @@
         <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="X19" t="n">
         <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA19" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
         <v>9</v>
@@ -5247,10 +5247,10 @@
         <v>9</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="n">
         <v>15</v>
@@ -5259,10 +5259,10 @@
         <v>13.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="n">
         <v>34</v>
@@ -5280,73 +5280,73 @@
         <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AR19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW19" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AX19" t="n">
-        <v>9</v>
+        <v>3.55</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15.5</v>
+        <v>3.9</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>19.5</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>19.5</v>
+        <v>4</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>17</v>
+        <v>3.95</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH19" t="n">
         <v>3</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ19" t="n">
         <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5355,13 +5355,13 @@
         <v>10</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP19" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ19" t="n">
         <v>6.6</v>
@@ -5373,32 +5373,32 @@
         <v>8.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6723,13 +6723,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
         <v>3.65</v>
       </c>
       <c r="I27" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>3.6</v>
@@ -7231,7 +7231,7 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
         <v>1.32</v>
@@ -7240,22 +7240,22 @@
         <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R27" t="n">
         <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
         <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V27" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
         <v>1.81</v>
@@ -7264,7 +7264,7 @@
         <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z27" t="n">
         <v>26</v>
@@ -7273,7 +7273,7 @@
         <v>70</v>
       </c>
       <c r="AB27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC27" t="n">
         <v>8.199999999999999</v>
@@ -7282,7 +7282,7 @@
         <v>15</v>
       </c>
       <c r="AE27" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF27" t="n">
         <v>14.5</v>
@@ -7291,16 +7291,16 @@
         <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
         <v>55</v>
       </c>
       <c r="AJ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
         <v>42</v>
@@ -7309,7 +7309,7 @@
         <v>95</v>
       </c>
       <c r="AN27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
         <v>42</v>
@@ -7333,19 +7333,19 @@
         <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW27" t="n">
         <v>36</v>
       </c>
       <c r="AX27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA27" t="n">
         <v>44</v>
@@ -7354,7 +7354,7 @@
         <v>25</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
         <v>32</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
         <v>3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
@@ -7527,10 +7527,10 @@
         <v>120</v>
       </c>
       <c r="AB28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC28" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9</v>
       </c>
       <c r="AD28" t="n">
         <v>21</v>
@@ -7569,70 +7569,70 @@
         <v>100</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="AR28" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="AS28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE28" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BF28" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7650,13 +7650,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR28" t="n">
         <v>38</v>
       </c>
       <c r="BS28" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT28" t="n">
         <v>7.6</v>
@@ -7665,16 +7665,16 @@
         <v>5.5</v>
       </c>
       <c r="BV28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX28" t="n">
         <v>60</v>
       </c>
       <c r="BY28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>2.64</v>
       </c>
       <c r="H29" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I29" t="n">
         <v>5</v>
@@ -7730,7 +7730,7 @@
         <v>2.62</v>
       </c>
       <c r="K29" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7745,10 +7745,10 @@
         <v>1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="R29" t="n">
         <v>1.17</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="G30" t="n">
         <v>2.44</v>
@@ -7984,7 +7984,7 @@
         <v>2.74</v>
       </c>
       <c r="K30" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.43</v>
@@ -7999,7 +7999,7 @@
         <v>1.23</v>
       </c>
       <c r="P30" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q30" t="n">
         <v>2.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -8250,19 +8250,19 @@
         <v>1.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
         <v>1.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R31" t="n">
         <v>1.16</v>
       </c>
       <c r="S31" t="n">
-        <v>2.78</v>
+        <v>1.32</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H32" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I32" t="n">
         <v>5.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K32" t="n">
         <v>3.6</v>
@@ -8498,7 +8498,7 @@
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N32" t="n">
         <v>2.42</v>
@@ -8528,7 +8528,7 @@
         <v>1.21</v>
       </c>
       <c r="W32" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G33" t="n">
         <v>2.26</v>
@@ -8740,13 +8740,13 @@
         <v>3.75</v>
       </c>
       <c r="I33" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J33" t="n">
         <v>2.84</v>
       </c>
       <c r="K33" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -8985,28 +8985,28 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G34" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="H34" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J34" t="n">
         <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N34" t="n">
         <v>2.82</v>
@@ -9027,16 +9027,16 @@
         <v>3.55</v>
       </c>
       <c r="T34" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U34" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V34" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W34" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="X34" t="n">
         <v>15</v>
@@ -9048,7 +9048,7 @@
         <v>30</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB34" t="n">
         <v>12</v>
@@ -9057,13 +9057,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE34" t="n">
         <v>60</v>
       </c>
       <c r="AF34" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG34" t="n">
         <v>970</v>
@@ -9093,7 +9093,7 @@
         <v>70</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="AQ34" t="n">
         <v>9</v>
@@ -9102,49 +9102,49 @@
         <v>15.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AV34" t="n">
         <v>11</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AX34" t="n">
         <v>11</v>
       </c>
       <c r="AY34" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="BA34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB34" t="n">
         <v>3.1</v>
       </c>
-      <c r="BB34" t="n">
-        <v>3</v>
-      </c>
       <c r="BC34" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BE34" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BH34" t="n">
         <v>3.45</v>
@@ -9153,62 +9153,62 @@
         <v>2.48</v>
       </c>
       <c r="BJ34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BN34" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BT34" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BU34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -9242,19 +9242,19 @@
         <v>2.02</v>
       </c>
       <c r="G35" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H35" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I35" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
         <v>3.2</v>
       </c>
       <c r="K35" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L35" t="n">
         <v>1.52</v>
@@ -9263,7 +9263,7 @@
         <v>1.12</v>
       </c>
       <c r="N35" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O35" t="n">
         <v>1.51</v>
@@ -9281,46 +9281,46 @@
         <v>5.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U35" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W35" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="X35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y35" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AA35" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE35" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH35" t="n">
         <v>36</v>
@@ -9329,10 +9329,10 @@
         <v>130</v>
       </c>
       <c r="AJ35" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AK35" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL35" t="n">
         <v>80</v>
@@ -9341,34 +9341,34 @@
         <v>240</v>
       </c>
       <c r="AN35" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO35" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP35" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR35" t="n">
         <v>25</v>
       </c>
       <c r="AS35" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU35" t="n">
         <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AW35" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX35" t="n">
         <v>9.199999999999999</v>
@@ -9380,25 +9380,25 @@
         <v>21</v>
       </c>
       <c r="BA35" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB35" t="n">
         <v>20</v>
       </c>
       <c r="BC35" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BD35" t="n">
         <v>9.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF35" t="n">
         <v>19.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>2.74</v>
+        <v>1.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.2</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -9747,16 +9747,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G37" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H37" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>3.15</v>
@@ -9774,7 +9774,7 @@
         <v>2.42</v>
       </c>
       <c r="O37" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P37" t="n">
         <v>1.64</v>
@@ -9795,10 +9795,10 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W37" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G38" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H38" t="n">
         <v>2.86</v>
@@ -10025,7 +10025,7 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
         <v>1.41</v>
@@ -10052,7 +10052,7 @@
         <v>1.4</v>
       </c>
       <c r="W38" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
         <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R39" t="n">
         <v>1.39</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -10512,13 +10512,13 @@
         <v>2.44</v>
       </c>
       <c r="G40" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H40" t="n">
         <v>2.66</v>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J40" t="n">
         <v>3.45</v>
@@ -10545,7 +10545,7 @@
         <v>1.63</v>
       </c>
       <c r="R40" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S40" t="n">
         <v>2.62</v>
@@ -10560,7 +10560,7 @@
         <v>1.47</v>
       </c>
       <c r="W40" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X40" t="n">
         <v>22</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
         <v>3.7</v>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -10787,16 +10787,16 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O41" t="n">
         <v>1.15</v>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="R41" t="n">
         <v>1.47</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11035,7 @@
         <v>4.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M42" t="n">
         <v>1.04</v>
@@ -11071,58 +11071,58 @@
         <v>1.68</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP42" t="n">
         <v>1.03</v>
@@ -11173,74 +11173,74 @@
         <v>1.03</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH42" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ42" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BN42" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP42" t="n">
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BT42" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1144,13 +1144,13 @@
         <v>1.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1383,13 +1383,13 @@
         <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
@@ -1410,16 +1410,16 @@
         <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
         <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
         <v>20</v>
@@ -1443,7 +1443,7 @@
         <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
@@ -1467,118 +1467,118 @@
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BN4" t="n">
         <v>4.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2659,16 +2659,16 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="O9" t="n">
         <v>1.02</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2889,31 +2889,31 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
         <v>1.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.12</v>
       </c>
       <c r="O10" t="n">
         <v>1.25</v>
@@ -2922,13 +2922,13 @@
         <v>1.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
         <v>4.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AW11" t="n">
         <v>6.4</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3397,82 +3397,82 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H12" t="n">
         <v>2.2</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J12" t="n">
         <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
         <v>28</v>
@@ -3481,16 +3481,16 @@
         <v>17</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL12" t="n">
         <v>60</v>
@@ -3499,118 +3499,118 @@
         <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BN12" t="n">
         <v>6.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BT12" t="n">
         <v>5.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV12" t="n">
         <v>18</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX12" t="n">
         <v>32</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
@@ -3684,7 +3684,7 @@
         <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
         <v>1.24</v>
@@ -3729,7 +3729,7 @@
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="AG13" t="n">
         <v>14.5</v>
@@ -3780,7 +3780,7 @@
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX13" t="n">
         <v>15</v>
@@ -3792,7 +3792,7 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
         <v>32</v>
@@ -3801,10 +3801,10 @@
         <v>30</v>
       </c>
       <c r="BD13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
         <v>25</v>
@@ -3822,7 +3822,7 @@
         <v>11</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,7 +3834,7 @@
         <v>5.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP13" t="n">
         <v>25</v>
@@ -3852,7 +3852,7 @@
         <v>6.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
         <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
         <v>1.81</v>
@@ -4001,7 +4001,7 @@
         <v>18</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
         <v>150</v>
@@ -4013,7 +4013,7 @@
         <v>170</v>
       </c>
       <c r="AP14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ14" t="n">
         <v>22</v>
@@ -4034,7 +4034,7 @@
         <v>22</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
         <v>7.6</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4670,16 +4670,16 @@
         <v>1.05</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.56</v>
       </c>
       <c r="H17" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1</v>
+        <v>1.77</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,22 +4691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4718,7 +4718,7 @@
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>2.48</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="H19" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="I19" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="J19" t="n">
         <v>2.86</v>
@@ -5193,7 +5193,7 @@
         <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
@@ -5205,43 +5205,43 @@
         <v>1.34</v>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T19" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA19" t="n">
         <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC19" t="n">
         <v>8.199999999999999</v>
@@ -5250,25 +5250,25 @@
         <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
         <v>50</v>
       </c>
       <c r="AJ19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL19" t="n">
         <v>60</v>
@@ -5277,118 +5277,118 @@
         <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH19" t="n">
         <v>3.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ19" t="n">
         <v>10</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BV19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>2.12</v>
       </c>
       <c r="G22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
         <v>3.8</v>
@@ -5949,10 +5949,10 @@
         <v>4.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
         <v>1.5</v>
@@ -5988,7 +5988,7 @@
         <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X22" t="n">
         <v>12.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
         <v>1.01</v>
       </c>
       <c r="P28" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
         <v>3.55</v>
       </c>
       <c r="T30" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U30" t="n">
         <v>2.18</v>
@@ -8059,7 +8059,7 @@
         <v>55</v>
       </c>
       <c r="AJ30" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AK30" t="n">
         <v>23</v>
@@ -8107,7 +8107,7 @@
         <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA30" t="n">
         <v>44</v>
@@ -8122,7 +8122,7 @@
         <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF30" t="n">
         <v>15.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8223,13 +8223,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G31" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H31" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I31" t="n">
         <v>4.5</v>
@@ -8241,13 +8241,13 @@
         <v>3.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
         <v>1.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O31" t="n">
         <v>1.44</v>
@@ -8259,7 +8259,7 @@
         <v>2.28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S31" t="n">
         <v>4.4</v>
@@ -8271,10 +8271,10 @@
         <v>1.86</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W31" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X31" t="n">
         <v>13</v>
@@ -8334,7 +8334,7 @@
         <v>3.35</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AR31" t="n">
         <v>20</v>
@@ -8358,10 +8358,10 @@
         <v>3.45</v>
       </c>
       <c r="AY31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BA31" t="n">
         <v>4.3</v>
@@ -8379,7 +8379,7 @@
         <v>4.3</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG31" t="n">
         <v>4.2</v>
@@ -8391,37 +8391,37 @@
         <v>2.4</v>
       </c>
       <c r="BJ31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN31" t="n">
         <v>4.9</v>
       </c>
       <c r="BO31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ31" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR31" t="n">
         <v>38</v>
       </c>
       <c r="BS31" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU31" t="n">
         <v>5.5</v>
@@ -8430,13 +8430,13 @@
         <v>42</v>
       </c>
       <c r="BW31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX31" t="n">
         <v>60</v>
       </c>
       <c r="BY31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8480,16 +8480,16 @@
         <v>2.24</v>
       </c>
       <c r="G32" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H32" t="n">
         <v>3.65</v>
       </c>
       <c r="I32" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K32" t="n">
         <v>3.35</v>
@@ -8516,7 +8516,7 @@
         <v>1.17</v>
       </c>
       <c r="S32" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="T32" t="n">
         <v>2.1</v>
@@ -8525,10 +8525,10 @@
         <v>1.72</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X32" t="n">
         <v>10</v>
@@ -8588,7 +8588,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR32" t="n">
         <v>19</v>
@@ -8597,25 +8597,25 @@
         <v>4.2</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU32" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV32" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW32" t="n">
         <v>4.2</v>
       </c>
       <c r="AX32" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ32" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA32" t="n">
         <v>4.2</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8734,19 +8734,19 @@
         <v>1.98</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H33" t="n">
         <v>4.2</v>
       </c>
       <c r="I33" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J33" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L33" t="n">
         <v>1.49</v>
@@ -8761,10 +8761,10 @@
         <v>1.5</v>
       </c>
       <c r="P33" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R33" t="n">
         <v>1.19</v>
@@ -8782,7 +8782,7 @@
         <v>1.24</v>
       </c>
       <c r="W33" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X33" t="n">
         <v>10.5</v>
@@ -8842,7 +8842,7 @@
         <v>7</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR33" t="n">
         <v>4.6</v>
@@ -8863,7 +8863,7 @@
         <v>4.9</v>
       </c>
       <c r="AX33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY33" t="n">
         <v>8.800000000000001</v>
@@ -8881,7 +8881,7 @@
         <v>4.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE33" t="n">
         <v>5.1</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9239,13 +9239,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G35" t="n">
         <v>2.08</v>
       </c>
       <c r="H35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I35" t="n">
         <v>5.6</v>
@@ -9254,7 +9254,7 @@
         <v>3.15</v>
       </c>
       <c r="K35" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G37" t="n">
         <v>2.56</v>
@@ -9759,7 +9759,7 @@
         <v>3.65</v>
       </c>
       <c r="J37" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K37" t="n">
         <v>3.45</v>
@@ -9795,7 +9795,7 @@
         <v>2.04</v>
       </c>
       <c r="V37" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
         <v>1.64</v>
@@ -9825,7 +9825,7 @@
         <v>60</v>
       </c>
       <c r="AF37" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG37" t="n">
         <v>15.5</v>
@@ -9855,7 +9855,7 @@
         <v>70</v>
       </c>
       <c r="AP37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ37" t="n">
         <v>9</v>
@@ -9864,7 +9864,7 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT37" t="n">
         <v>5.4</v>
@@ -9876,7 +9876,7 @@
         <v>11</v>
       </c>
       <c r="AW37" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX37" t="n">
         <v>11</v>
@@ -9885,10 +9885,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB37" t="n">
         <v>10</v>
@@ -9897,16 +9897,16 @@
         <v>22</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE37" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BF37" t="n">
         <v>18</v>
       </c>
       <c r="BG37" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH37" t="n">
         <v>3.45</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
         <v>11.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY38" t="n">
         <v>9.4</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10375,7 @@
         <v>12</v>
       </c>
       <c r="AT39" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AU39" t="n">
         <v>8</v>
@@ -10393,7 +10393,7 @@
         <v>4.7</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="BA39" t="n">
         <v>4.5</v>
@@ -10414,7 +10414,7 @@
         <v>4.8</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH39" t="n">
         <v>4.2</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
         <v>2.98</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="BJ40" t="n">
         <v>11</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11065,7 @@
         <v>2.16</v>
       </c>
       <c r="V42" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W42" t="n">
         <v>2.14</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
         <v>2.66</v>
       </c>
       <c r="I43" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>3.5</v>
@@ -11307,7 +11307,7 @@
         <v>1.64</v>
       </c>
       <c r="R43" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S43" t="n">
         <v>2.66</v>
@@ -11319,7 +11319,7 @@
         <v>2.1</v>
       </c>
       <c r="V43" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W43" t="n">
         <v>1.54</v>
@@ -11382,7 +11382,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ43" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR43" t="n">
         <v>1.03</v>
@@ -11430,7 +11430,7 @@
         <v>13.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11540,7 +11540,7 @@
         <v>3.7</v>
       </c>
       <c r="K44" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L44" t="n">
         <v>1.24</v>
@@ -11549,7 +11549,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O44" t="n">
         <v>1.19</v>
@@ -11573,10 +11573,10 @@
         <v>2.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W44" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X44" t="n">
         <v>29</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -11812,13 +11812,13 @@
         <v>2.18</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R45" t="n">
         <v>1.48</v>
       </c>
       <c r="S45" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T45" t="n">
         <v>1.53</v>
@@ -11887,7 +11887,7 @@
         <v>29</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ45" t="n">
         <v>4</v>
@@ -11929,7 +11929,7 @@
         <v>4.3</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE45" t="n">
         <v>4.8</v>
@@ -11938,7 +11938,7 @@
         <v>3.9</v>
       </c>
       <c r="BG45" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH45" t="n">
         <v>4.1</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.06</v>
+        <v>2.42</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>1.72</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M3" t="n">
         <v>1.1</v>
       </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N3" t="n">
-        <v>1.34</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
@@ -1398,187 +1398,187 @@
         <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
         <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>4.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>3</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.55</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.65</v>
+        <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
         <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BH4" t="n">
         <v>3.7</v>
       </c>
       <c r="BI4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
         <v>2.86</v>
       </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>2.74</v>
-      </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -1619,100 +1619,100 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.21</v>
+        <v>2.38</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.47</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1724,67 +1724,67 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>2.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.8</v>
@@ -1933,13 +1933,13 @@
         <v>26</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
         <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC6" t="n">
         <v>13.5</v>
@@ -1981,10 +1981,10 @@
         <v>15.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.7</v>
+        <v>18.5</v>
       </c>
       <c r="AR6" t="n">
         <v>21</v>
@@ -1993,13 +1993,13 @@
         <v>5.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AU6" t="n">
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
@@ -2008,7 +2008,7 @@
         <v>18.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
         <v>11</v>
@@ -2017,13 +2017,13 @@
         <v>20</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.6</v>
+        <v>16.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="n">
         <v>34</v>
@@ -2032,10 +2032,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI6" t="n">
         <v>3.9</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN6" t="n">
         <v>6.2</v>
@@ -2068,7 +2068,7 @@
         <v>22</v>
       </c>
       <c r="BS6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT6" t="n">
         <v>7</v>
@@ -2080,13 +2080,13 @@
         <v>20</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6" t="n">
         <v>14</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
@@ -2402,25 +2402,25 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
         <v>1.02</v>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
         <v>1.41</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2919,7 +2919,7 @@
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Q10" t="n">
         <v>1.24</v>
@@ -2928,7 +2928,7 @@
         <v>1.05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I11" t="n">
         <v>3.25</v>
@@ -3167,16 +3167,16 @@
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O11" t="n">
         <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
@@ -3188,13 +3188,13 @@
         <v>1.87</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
         <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
@@ -3224,7 +3224,7 @@
         <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
@@ -3260,7 +3260,7 @@
         <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -3269,10 +3269,10 @@
         <v>4.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,7 +3284,7 @@
         <v>5.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
         <v>6.6</v>
@@ -3293,16 +3293,16 @@
         <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="BF11" t="n">
         <v>6.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="n">
         <v>3.1</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>3.15</v>
       </c>
       <c r="G12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I12" t="n">
         <v>2.52</v>
@@ -3412,43 +3412,43 @@
         <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R12" t="n">
         <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
         <v>1.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
         <v>16</v>
@@ -3466,7 +3466,7 @@
         <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
@@ -3496,7 +3496,7 @@
         <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
         <v>48</v>
@@ -3505,43 +3505,43 @@
         <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
         <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
         <v>4.6</v>
@@ -3550,67 +3550,67 @@
         <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
         <v>4.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BH12" t="n">
         <v>3.45</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ12" t="n">
         <v>10</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN12" t="n">
         <v>6.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP12" t="n">
         <v>29</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR12" t="n">
         <v>42</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.46</v>
+        <v>8.4</v>
       </c>
       <c r="BT12" t="n">
         <v>5.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -3651,28 +3651,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="G13" t="n">
         <v>2.94</v>
       </c>
       <c r="H13" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
         <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
         <v>2.94</v>
@@ -3693,13 +3693,13 @@
         <v>4.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
         <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
         <v>1.52</v>
@@ -3729,13 +3729,13 @@
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
         <v>65</v>
@@ -3750,7 +3750,7 @@
         <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="n">
         <v>50</v>
@@ -3780,19 +3780,19 @@
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="AX13" t="n">
         <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB13" t="n">
         <v>32</v>
@@ -3801,7 +3801,7 @@
         <v>30</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE13" t="n">
         <v>10</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.37</v>
       </c>
       <c r="G14" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H14" t="n">
         <v>6.8</v>
@@ -3917,7 +3917,7 @@
         <v>10.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
@@ -3956,7 +3956,7 @@
         <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="X14" t="n">
         <v>28</v>
@@ -3965,7 +3965,7 @@
         <v>34</v>
       </c>
       <c r="Z14" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA14" t="n">
         <v>320</v>
@@ -4001,7 +4001,7 @@
         <v>18</v>
       </c>
       <c r="AL14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
         <v>150</v>
@@ -4019,7 +4019,7 @@
         <v>22</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS14" t="n">
         <v>4.4</v>
@@ -4031,10 +4031,10 @@
         <v>9.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>22</v>
+        <v>4.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX14" t="n">
         <v>7.6</v>
@@ -4058,13 +4058,13 @@
         <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF14" t="n">
         <v>4.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="n">
         <v>4.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.77</v>
+        <v>1.1</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4700,7 +4700,7 @@
         <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
@@ -4718,7 +4718,7 @@
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -5175,31 +5175,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="G19" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="I19" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="J19" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="K19" t="n">
         <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>1.34</v>
@@ -5208,40 +5208,40 @@
         <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R19" t="n">
         <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="W19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
         <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC19" t="n">
         <v>8.199999999999999</v>
@@ -5250,13 +5250,13 @@
         <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
         <v>18.5</v>
@@ -5277,64 +5277,64 @@
         <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO19" t="n">
         <v>29</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.9</v>
+        <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF19" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG19" t="n">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="BH19" t="n">
         <v>3.4</v>
@@ -5346,22 +5346,22 @@
         <v>10</v>
       </c>
       <c r="BK19" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="BN19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
         <v>7.4</v>
@@ -5370,16 +5370,16 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="BV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW19" t="n">
         <v>6.8</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -5979,10 +5979,10 @@
         <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V22" t="n">
         <v>1.3</v>
@@ -5997,13 +5997,13 @@
         <v>14.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA22" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC22" t="n">
         <v>9</v>
@@ -6015,10 +6015,10 @@
         <v>75</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH22" t="n">
         <v>26</v>
@@ -6027,10 +6027,10 @@
         <v>95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL22" t="n">
         <v>65</v>
@@ -6039,7 +6039,7 @@
         <v>190</v>
       </c>
       <c r="AN22" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO22" t="n">
         <v>100</v>
@@ -6054,22 +6054,22 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.05</v>
+        <v>5.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.75</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AX22" t="n">
-        <v>3.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY22" t="n">
         <v>8.4</v>
@@ -6078,25 +6078,25 @@
         <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.95</v>
+        <v>18.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BH22" t="n">
         <v>3</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
         <v>1.02</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
@@ -6469,16 +6469,16 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
         <v>1.12</v>
@@ -6493,10 +6493,10 @@
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6511,25 +6511,25 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -6547,13 +6547,13 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.01</v>
@@ -6568,7 +6568,7 @@
         <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         <v>1000</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -7207,40 +7207,40 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H27" t="n">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>2.54</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N27" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="R27" t="n">
         <v>1.12</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -7739,13 +7739,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O29" t="n">
         <v>1.02</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
         <v>1.02</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
         <v>3.75</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
         <v>3.7</v>
@@ -8008,22 +8008,22 @@
         <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T30" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U30" t="n">
         <v>2.18</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W30" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
         <v>14.5</v>
@@ -8044,7 +8044,7 @@
         <v>15</v>
       </c>
       <c r="AE30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF30" t="n">
         <v>14.5</v>
@@ -8059,10 +8059,10 @@
         <v>55</v>
       </c>
       <c r="AJ30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
         <v>38</v>
@@ -8089,7 +8089,7 @@
         <v>55</v>
       </c>
       <c r="AT30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU30" t="n">
         <v>7.4</v>
@@ -8131,7 +8131,7 @@
         <v>34</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI30" t="n">
         <v>3.1</v>
@@ -8140,13 +8140,13 @@
         <v>9.6</v>
       </c>
       <c r="BK30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN30" t="n">
         <v>5.1</v>
@@ -8164,7 +8164,7 @@
         <v>30</v>
       </c>
       <c r="BS30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT30" t="n">
         <v>6.8</v>
@@ -8176,23 +8176,23 @@
         <v>29</v>
       </c>
       <c r="BW30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX30" t="n">
         <v>55</v>
       </c>
       <c r="BY30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ30" t="n">
         <v>27</v>
       </c>
       <c r="CA30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
         <v>1.48</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
         <v>2.92</v>
@@ -8280,7 +8280,7 @@
         <v>13</v>
       </c>
       <c r="Y31" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
         <v>36</v>
@@ -8298,7 +8298,7 @@
         <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="n">
         <v>15</v>
@@ -8310,7 +8310,7 @@
         <v>26</v>
       </c>
       <c r="AI31" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ31" t="n">
         <v>34</v>
@@ -8328,16 +8328,16 @@
         <v>28</v>
       </c>
       <c r="AO31" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.35</v>
+        <v>9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="AR31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS31" t="n">
         <v>4.2</v>
@@ -8349,37 +8349,37 @@
         <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="AW31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA31" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA31" t="n">
+      <c r="BB31" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB31" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BC31" t="n">
-        <v>3.95</v>
+        <v>19.5</v>
       </c>
       <c r="BD31" t="n">
         <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.85</v>
+        <v>19</v>
       </c>
       <c r="BG31" t="n">
         <v>4.2</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -8480,19 +8480,19 @@
         <v>2.24</v>
       </c>
       <c r="G32" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H32" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I32" t="n">
         <v>4.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="K32" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -8507,7 +8507,7 @@
         <v>1.54</v>
       </c>
       <c r="P32" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q32" t="n">
         <v>2.6</v>
@@ -8594,7 +8594,7 @@
         <v>19</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT32" t="n">
         <v>6</v>
@@ -8618,25 +8618,25 @@
         <v>20</v>
       </c>
       <c r="BA32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD32" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.1</v>
       </c>
       <c r="BE32" t="n">
         <v>4.3</v>
       </c>
       <c r="BF32" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH32" t="n">
         <v>3.05</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
         <v>4.2</v>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>3</v>
@@ -8761,7 +8761,7 @@
         <v>1.5</v>
       </c>
       <c r="P33" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q33" t="n">
         <v>2.48</v>
@@ -8770,16 +8770,16 @@
         <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T33" t="n">
         <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W33" t="n">
         <v>1.81</v>
@@ -8878,7 +8878,7 @@
         <v>20</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BD33" t="n">
         <v>4.8</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -9242,10 +9242,10 @@
         <v>1.89</v>
       </c>
       <c r="G35" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I35" t="n">
         <v>5.6</v>
@@ -9257,10 +9257,10 @@
         <v>3.5</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M35" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N35" t="n">
         <v>2.66</v>
@@ -9272,31 +9272,31 @@
         <v>1.56</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R35" t="n">
         <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U35" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V35" t="n">
         <v>1.22</v>
       </c>
       <c r="W35" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y35" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z35" t="n">
         <v>44</v>
@@ -9305,7 +9305,7 @@
         <v>180</v>
       </c>
       <c r="AB35" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC35" t="n">
         <v>8.800000000000001</v>
@@ -9353,10 +9353,10 @@
         <v>10</v>
       </c>
       <c r="AR35" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT35" t="n">
         <v>5.2</v>
@@ -9368,7 +9368,7 @@
         <v>16.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX35" t="n">
         <v>8.199999999999999</v>
@@ -9377,92 +9377,92 @@
         <v>8.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB35" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC35" t="n">
         <v>20</v>
       </c>
       <c r="BD35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE35" t="n">
         <v>5</v>
       </c>
-      <c r="BE35" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF35" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.48</v>
+        <v>5.9</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.48</v>
+        <v>10.5</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.48</v>
+        <v>3.5</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.48</v>
+        <v>6.6</v>
       </c>
       <c r="BR35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.48</v>
+        <v>4.8</v>
       </c>
       <c r="BV35" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.48</v>
+        <v>9.4</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.48</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -9493,13 +9493,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="G36" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="H36" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="I36" t="n">
         <v>6.2</v>
@@ -9514,145 +9514,145 @@
         <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="O36" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="P36" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R36" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S36" t="n">
-        <v>2.68</v>
+        <v>4.8</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V36" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W36" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA36" t="n">
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH36" t="n">
         <v>4.1</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -9747,40 +9747,40 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="G37" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="H37" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I37" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="J37" t="n">
         <v>3.15</v>
       </c>
       <c r="K37" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N37" t="n">
         <v>3.05</v>
       </c>
       <c r="O37" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P37" t="n">
         <v>1.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R37" t="n">
         <v>1.26</v>
@@ -9789,16 +9789,16 @@
         <v>4.2</v>
       </c>
       <c r="T37" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U37" t="n">
         <v>2.04</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W37" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X37" t="n">
         <v>15</v>
@@ -9816,7 +9816,7 @@
         <v>12</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD37" t="n">
         <v>20</v>
@@ -9825,7 +9825,7 @@
         <v>60</v>
       </c>
       <c r="AF37" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG37" t="n">
         <v>15.5</v>
@@ -9846,7 +9846,7 @@
         <v>65</v>
       </c>
       <c r="AM37" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN37" t="n">
         <v>36</v>
@@ -9864,19 +9864,19 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV37" t="n">
         <v>11</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AX37" t="n">
         <v>11</v>
@@ -9885,92 +9885,92 @@
         <v>9.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB37" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC37" t="n">
         <v>22</v>
       </c>
       <c r="BD37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE37" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>3.45</v>
       </c>
       <c r="BF37" t="n">
         <v>18</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="BJ37" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BK37" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>4.3</v>
+        <v>2.22</v>
       </c>
       <c r="BN37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BT37" t="n">
         <v>6.4</v>
       </c>
-      <c r="BO37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BR37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS37" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT37" t="n">
-        <v>8</v>
-      </c>
       <c r="BU37" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BV37" t="n">
         <v>1000</v>
       </c>
       <c r="BW37" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -10001,10 +10001,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G38" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H38" t="n">
         <v>4.5</v>
@@ -10016,22 +10016,22 @@
         <v>3.1</v>
       </c>
       <c r="K38" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M38" t="n">
         <v>1.12</v>
       </c>
       <c r="N38" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
         <v>1.51</v>
       </c>
       <c r="P38" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q38" t="n">
         <v>2.52</v>
@@ -10046,16 +10046,16 @@
         <v>2.14</v>
       </c>
       <c r="U38" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V38" t="n">
         <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X38" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y38" t="n">
         <v>12.5</v>
@@ -10142,13 +10142,13 @@
         <v>21</v>
       </c>
       <c r="BA38" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC38" t="n">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="BD38" t="n">
         <v>11</v>
@@ -10163,68 +10163,68 @@
         <v>12</v>
       </c>
       <c r="BH38" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BJ38" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP38" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR38" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT38" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV38" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>5.5</v>
       </c>
       <c r="G39" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H39" t="n">
         <v>1.56</v>
@@ -10279,7 +10279,7 @@
         <v>1.04</v>
       </c>
       <c r="N39" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
         <v>1.22</v>
@@ -10291,10 +10291,10 @@
         <v>1.65</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T39" t="n">
         <v>1.73</v>
@@ -10306,7 +10306,7 @@
         <v>2.42</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X39" t="n">
         <v>950</v>
@@ -10363,7 +10363,7 @@
         <v>8.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AQ39" t="n">
         <v>8</v>
@@ -10384,10 +10384,10 @@
         <v>7.8</v>
       </c>
       <c r="AW39" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AX39" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY39" t="n">
         <v>4.7</v>
@@ -10399,7 +10399,7 @@
         <v>4.5</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC39" t="n">
         <v>4.8</v>
@@ -10426,16 +10426,16 @@
         <v>10.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN39" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO39" t="n">
         <v>5.1</v>
@@ -10450,7 +10450,7 @@
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT39" t="n">
         <v>4.5</v>
@@ -10462,13 +10462,13 @@
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -10524,7 +10524,7 @@
         <v>3.15</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L40" t="n">
         <v>1.42</v>
@@ -10560,49 +10560,49 @@
         <v>1.27</v>
       </c>
       <c r="W40" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X40" t="n">
         <v>12.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA40" t="n">
         <v>130</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD40" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AE40" t="n">
         <v>85</v>
       </c>
       <c r="AF40" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI40" t="n">
         <v>100</v>
       </c>
       <c r="AJ40" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AK40" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AL40" t="n">
         <v>60</v>
@@ -10611,7 +10611,7 @@
         <v>190</v>
       </c>
       <c r="AN40" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AO40" t="n">
         <v>120</v>
@@ -10620,16 +10620,16 @@
         <v>7.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR40" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="AS40" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU40" t="n">
         <v>5.7</v>
@@ -10638,19 +10638,19 @@
         <v>13</v>
       </c>
       <c r="AW40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY40" t="n">
         <v>8</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>5</v>
       </c>
       <c r="AZ40" t="n">
         <v>15.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BB40" t="n">
         <v>19.5</v>
@@ -10659,16 +10659,16 @@
         <v>19</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="BE40" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF40" t="n">
         <v>16.5</v>
       </c>
       <c r="BG40" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BH40" t="n">
         <v>2.98</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
         <v>2.86</v>
       </c>
       <c r="I41" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -10781,34 +10781,34 @@
         <v>3.55</v>
       </c>
       <c r="L41" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M41" t="n">
         <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
         <v>1.41</v>
       </c>
       <c r="P41" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R41" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U41" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V41" t="n">
         <v>1.41</v>
@@ -10817,7 +10817,7 @@
         <v>1.52</v>
       </c>
       <c r="X41" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y41" t="n">
         <v>12</v>
@@ -10838,7 +10838,7 @@
         <v>16</v>
       </c>
       <c r="AE41" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF41" t="n">
         <v>20</v>
@@ -10847,7 +10847,7 @@
         <v>14.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI41" t="n">
         <v>65</v>
@@ -10862,28 +10862,28 @@
         <v>60</v>
       </c>
       <c r="AM41" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO41" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP41" t="n">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AR41" t="n">
         <v>15</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT41" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU41" t="n">
         <v>5.8</v>
@@ -10892,7 +10892,7 @@
         <v>10.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX41" t="n">
         <v>13</v>
@@ -10904,43 +10904,43 @@
         <v>14.5</v>
       </c>
       <c r="BA41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB41" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BC41" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC41" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG41" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH41" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI41" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BJ41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK41" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BN41" t="n">
         <v>5.8</v>
@@ -10949,19 +10949,19 @@
         <v>4.4</v>
       </c>
       <c r="BP41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ41" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT41" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU41" t="n">
         <v>4.7</v>
@@ -10970,23 +10970,23 @@
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ41" t="n">
         <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -11026,10 +11026,10 @@
         <v>4.5</v>
       </c>
       <c r="I42" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
         <v>4.6</v>
@@ -11050,7 +11050,7 @@
         <v>2.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R42" t="n">
         <v>1.47</v>
@@ -11059,13 +11059,13 @@
         <v>2.7</v>
       </c>
       <c r="T42" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U42" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V42" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W42" t="n">
         <v>2.14</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11307,7 @@
         <v>1.64</v>
       </c>
       <c r="R43" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S43" t="n">
         <v>2.66</v>
@@ -11319,7 +11319,7 @@
         <v>2.1</v>
       </c>
       <c r="V43" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W43" t="n">
         <v>1.54</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -11540,7 +11540,7 @@
         <v>3.7</v>
       </c>
       <c r="K44" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L44" t="n">
         <v>1.24</v>
@@ -11549,7 +11549,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="O44" t="n">
         <v>1.19</v>
@@ -11573,7 +11573,7 @@
         <v>2.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W44" t="n">
         <v>1.47</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
         <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O45" t="n">
         <v>1.23</v>
@@ -11815,7 +11815,7 @@
         <v>1.68</v>
       </c>
       <c r="R45" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S45" t="n">
         <v>2.68</v>
@@ -11872,16 +11872,16 @@
         <v>36</v>
       </c>
       <c r="AK45" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL45" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM45" t="n">
         <v>75</v>
       </c>
       <c r="AN45" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO45" t="n">
         <v>29</v>
@@ -11890,52 +11890,52 @@
         <v>4.6</v>
       </c>
       <c r="AQ45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AR45" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE45" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="BF45" t="n">
         <v>3.85</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>3.9</v>
       </c>
       <c r="BG45" t="n">
         <v>4.8</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 07:01:52</t>
+          <t>2026-06-19 09:14:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.25</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.24</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>3.45</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -1222,7 +1222,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
         <v>15.5</v>
@@ -1246,7 +1246,7 @@
         <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>15</v>
@@ -1258,16 +1258,16 @@
         <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>26</v>
+        <v>4.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>40</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
         <v>4.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
         <v>4.1</v>
@@ -1383,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1395,7 +1395,7 @@
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
         <v>1.83</v>
@@ -1416,7 +1416,7 @@
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X4" t="n">
         <v>19.5</v>
@@ -1434,7 +1434,7 @@
         <v>12.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
         <v>18.5</v>
@@ -1482,7 +1482,7 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT4" t="n">
         <v>8.800000000000001</v>
@@ -1494,7 +1494,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1506,79 +1506,79 @@
         <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
         <v>2.4</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="J5" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
         <v>3.7</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
         <v>2.08</v>
@@ -1667,10 +1667,10 @@
         <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1733,58 +1733,58 @@
         <v>3.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="AU5" t="n">
         <v>3.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AX5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BA5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG5" t="n">
         <v>3.25</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.15</v>
       </c>
       <c r="BH5" t="n">
         <v>3.75</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
         <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
         <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.17</v>
@@ -1906,13 +1906,13 @@
         <v>3.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R6" t="n">
         <v>1.84</v>
       </c>
       <c r="S6" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="T6" t="n">
         <v>1.43</v>
@@ -1924,10 +1924,10 @@
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="n">
         <v>29</v>
@@ -2026,10 +2026,10 @@
         <v>19</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
         <v>14.5</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
@@ -2062,7 +2062,7 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2092,11 +2092,11 @@
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2.24</v>
       </c>
       <c r="G7" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
         <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
         <v>2.94</v>
@@ -2160,13 +2160,13 @@
         <v>1.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
         <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
         <v>1.95</v>
@@ -2175,10 +2175,10 @@
         <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="X7" t="n">
         <v>11.5</v>
@@ -2253,7 +2253,7 @@
         <v>2.98</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AW7" t="n">
         <v>4.2</v>
@@ -2292,7 +2292,7 @@
         <v>2.98</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -2393,10 +2393,10 @@
         <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.17</v>
@@ -2420,7 +2420,7 @@
         <v>2.06</v>
       </c>
       <c r="S8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="T8" t="n">
         <v>1.6</v>
@@ -2489,16 +2489,16 @@
         <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
@@ -2507,10 +2507,10 @@
         <v>12.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
@@ -2531,16 +2531,16 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
         <v>2.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="n">
         <v>6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H9" t="n">
         <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.04</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.94</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.92</v>
       </c>
       <c r="X9" t="n">
         <v>15</v>
@@ -2698,7 +2698,7 @@
         <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB9" t="n">
         <v>9.6</v>
@@ -2710,7 +2710,7 @@
         <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF9" t="n">
         <v>13.5</v>
@@ -2722,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
         <v>27</v>
@@ -2731,31 +2731,31 @@
         <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
         <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
         <v>6.6</v>
@@ -2764,7 +2764,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
         <v>9.4</v>
@@ -2776,7 +2776,7 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
         <v>16</v>
@@ -2785,19 +2785,19 @@
         <v>14.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF9" t="n">
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI9" t="n">
         <v>1.01</v>
@@ -2806,59 +2806,59 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="G10" t="n">
         <v>1.97</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
         <v>4.4</v>
@@ -2910,10 +2910,10 @@
         <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.16</v>
@@ -2928,7 +2928,7 @@
         <v>1.67</v>
       </c>
       <c r="S10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
         <v>1.52</v>
@@ -3045,10 +3045,10 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BH10" t="n">
         <v>4.9</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
         <v>1.59</v>
@@ -3152,19 +3152,19 @@
         <v>6.2</v>
       </c>
       <c r="I11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
         <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
         <v>5.1</v>
@@ -3191,7 +3191,7 @@
         <v>2.16</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>2.68</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G12" t="n">
         <v>1.63</v>
@@ -3415,10 +3415,10 @@
         <v>5.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
         <v>6.2</v>
@@ -3436,7 +3436,7 @@
         <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
         <v>1.58</v>
@@ -3445,7 +3445,7 @@
         <v>2.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
         <v>2.58</v>
@@ -3505,16 +3505,16 @@
         <v>60</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -3526,7 +3526,7 @@
         <v>17</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
         <v>9.4</v>
@@ -3538,7 +3538,7 @@
         <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB12" t="n">
         <v>11.5</v>
@@ -3550,13 +3550,13 @@
         <v>17.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
         <v>4.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -3651,46 +3651,46 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="G13" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>2.98</v>
       </c>
       <c r="O13" t="n">
-        <v>1.07</v>
+        <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>2.46</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
         <v>1.84</v>
@@ -3699,10 +3699,10 @@
         <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
         <v>970</v>
@@ -3762,55 +3762,55 @@
         <v>1.12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.12</v>
+        <v>1.69</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.12</v>
+        <v>1.68</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.12</v>
+        <v>1.59</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.12</v>
+        <v>1.76</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.05</v>
+        <v>1.82</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -3905,58 +3905,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.09</v>
+        <v>2.24</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="O14" t="n">
         <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T14" t="n">
         <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4061,10 +4061,10 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.92</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
         <v>4</v>
@@ -4171,7 +4171,7 @@
         <v>4.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
         <v>3.85</v>
@@ -4198,7 +4198,7 @@
         <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
         <v>1.78</v>
@@ -4279,7 +4279,7 @@
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="AU15" t="n">
         <v>6</v>
@@ -4294,7 +4294,7 @@
         <v>9</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -4413,55 +4413,55 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
         <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N16" t="n">
         <v>2.96</v>
       </c>
-      <c r="K16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.78</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
         <v>4.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
         <v>1.65</v>
@@ -4476,16 +4476,16 @@
         <v>27</v>
       </c>
       <c r="AA16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
         <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE16" t="n">
         <v>60</v>
@@ -4497,10 +4497,10 @@
         <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="n">
         <v>36</v>
@@ -4512,7 +4512,7 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN16" t="n">
         <v>30</v>
@@ -4521,7 +4521,7 @@
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ16" t="n">
         <v>9.4</v>
@@ -4530,7 +4530,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT16" t="n">
         <v>6.8</v>
@@ -4542,7 +4542,7 @@
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="AX16" t="n">
         <v>10</v>
@@ -4554,89 +4554,89 @@
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BJ16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN16" t="n">
         <v>5.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
         <v>7.4</v>
       </c>
-      <c r="BT16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
         <v>7.6</v>
       </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>7.4</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
         <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
         <v>1.84</v>
@@ -4706,7 +4706,7 @@
         <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
         <v>1.81</v>
@@ -4727,16 +4727,16 @@
         <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>13.5</v>
@@ -4745,88 +4745,88 @@
         <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG17" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
         <v>48</v>
       </c>
       <c r="AJ17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP17" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY17" t="n">
         <v>12</v>
       </c>
-      <c r="AS17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU17" t="n">
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>30</v>
       </c>
       <c r="BG17" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BH17" t="n">
         <v>3.45</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
         <v>3.6</v>
@@ -4930,13 +4930,13 @@
         <v>2.12</v>
       </c>
       <c r="I18" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.26</v>
@@ -4945,7 +4945,7 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
@@ -4969,7 +4969,7 @@
         <v>2.34</v>
       </c>
       <c r="V18" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="W18" t="n">
         <v>1.39</v>
@@ -4984,7 +4984,7 @@
         <v>970</v>
       </c>
       <c r="AA18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB18" t="n">
         <v>970</v>
@@ -4996,7 +4996,7 @@
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF18" t="n">
         <v>30</v>
@@ -5029,7 +5029,7 @@
         <v>15</v>
       </c>
       <c r="AP18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
@@ -5068,7 +5068,7 @@
         <v>38</v>
       </c>
       <c r="BC18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD18" t="n">
         <v>28</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -5175,31 +5175,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G19" t="n">
         <v>2.86</v>
       </c>
       <c r="H19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I19" t="n">
         <v>3.15</v>
       </c>
       <c r="J19" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K19" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M19" t="n">
         <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O19" t="n">
         <v>1.47</v>
@@ -5211,7 +5211,7 @@
         <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
         <v>4.7</v>
@@ -5271,10 +5271,10 @@
         <v>38</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN19" t="n">
         <v>38</v>
@@ -5286,13 +5286,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -5304,13 +5304,13 @@
         <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="AX19" t="n">
         <v>15</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AZ19" t="n">
         <v>7</v>
@@ -5322,7 +5322,7 @@
         <v>8.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD19" t="n">
         <v>8.800000000000001</v>
@@ -5331,10 +5331,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BH19" t="n">
         <v>2.9</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G20" t="n">
         <v>1.41</v>
       </c>
       <c r="H20" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>10.5</v>
@@ -5465,7 +5465,7 @@
         <v>1.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
         <v>2.46</v>
@@ -5474,10 +5474,10 @@
         <v>1.82</v>
       </c>
       <c r="U20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
         <v>3.4</v>
@@ -5486,7 +5486,7 @@
         <v>28</v>
       </c>
       <c r="Y20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z20" t="n">
         <v>85</v>
@@ -5495,34 +5495,34 @@
         <v>330</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AD20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE20" t="n">
         <v>150</v>
       </c>
       <c r="AF20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG20" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH20" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI20" t="n">
         <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL20" t="n">
         <v>38</v>
@@ -5531,22 +5531,22 @@
         <v>150</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AO20" t="n">
         <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
@@ -5555,10 +5555,10 @@
         <v>9.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX20" t="n">
         <v>7.6</v>
@@ -5570,7 +5570,7 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
@@ -5579,16 +5579,16 @@
         <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF20" t="n">
         <v>4.9</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BH20" t="n">
         <v>4.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -5713,22 +5713,22 @@
         <v>1.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="R21" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="S21" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="T21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U21" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V21" t="n">
         <v>3.1</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -5940,16 +5940,16 @@
         <v>1.02</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H22" t="n">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5973,7 +5973,7 @@
         <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
         <v>1.71</v>
@@ -5988,7 +5988,7 @@
         <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="G23" t="n">
         <v>3.55</v>
       </c>
       <c r="H23" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6215,22 +6215,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.03</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
         <v>1.03</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="S23" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6239,7 +6239,7 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W23" t="n">
         <v>1.39</v>
@@ -6347,10 +6347,10 @@
         <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -6448,16 +6448,16 @@
         <v>3.6</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H24" t="n">
         <v>1.69</v>
       </c>
       <c r="I24" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="K24" t="n">
         <v>5.4</v>
@@ -6475,22 +6475,22 @@
         <v>1.12</v>
       </c>
       <c r="P24" t="n">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R24" t="n">
         <v>1.85</v>
       </c>
       <c r="S24" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T24" t="n">
         <v>1.44</v>
       </c>
       <c r="U24" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -6502,7 +6502,7 @@
         <v>46</v>
       </c>
       <c r="Y24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z24" t="n">
         <v>19.5</v>
@@ -6553,49 +6553,49 @@
         <v>6.8</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ24" t="n">
         <v>4.1</v>
       </c>
       <c r="AR24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>4</v>
       </c>
-      <c r="AS24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX24" t="n">
+      <c r="BA24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD24" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.5</v>
       </c>
       <c r="BE24" t="n">
         <v>4.7</v>
@@ -6604,13 +6604,13 @@
         <v>4.3</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BH24" t="n">
         <v>5.8</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="BJ24" t="n">
         <v>9</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
         <v>17</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="AR25" t="n">
         <v>5.9</v>
@@ -6837,7 +6837,7 @@
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="BA25" t="n">
         <v>5.9</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>1.41</v>
@@ -6989,10 +6989,10 @@
         <v>2.18</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T26" t="n">
         <v>1.84</v>
@@ -7001,7 +7001,7 @@
         <v>1.91</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
         <v>1.53</v>
@@ -7115,7 +7115,7 @@
         <v>3.95</v>
       </c>
       <c r="BH26" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI26" t="n">
         <v>2.44</v>
@@ -7124,13 +7124,13 @@
         <v>11</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN26" t="n">
         <v>5.8</v>
@@ -7142,13 +7142,13 @@
         <v>23</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR26" t="n">
         <v>42</v>
       </c>
       <c r="BS26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT26" t="n">
         <v>6.4</v>
@@ -7160,23 +7160,23 @@
         <v>29</v>
       </c>
       <c r="BW26" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX26" t="n">
         <v>46</v>
       </c>
       <c r="BY26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ26" t="n">
         <v>40</v>
       </c>
       <c r="CA26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
         <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R27" t="n">
         <v>1.31</v>
@@ -7249,10 +7249,10 @@
         <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V27" t="n">
         <v>1.6</v>
@@ -7321,13 +7321,13 @@
         <v>8.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS27" t="n">
         <v>6.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
         <v>6</v>
@@ -7351,19 +7351,19 @@
         <v>6.6</v>
       </c>
       <c r="BB27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD27" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>6.6</v>
       </c>
       <c r="BE27" t="n">
         <v>7.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG27" t="n">
         <v>20</v>
@@ -7378,7 +7378,7 @@
         <v>10</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
@@ -7408,7 +7408,7 @@
         <v>5.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV27" t="n">
         <v>20</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -7461,19 +7461,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G28" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
         <v>5.9</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K28" t="n">
         <v>5.9</v>
@@ -7485,13 +7485,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="O28" t="n">
         <v>1.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="Q28" t="n">
         <v>1.32</v>
@@ -7506,13 +7506,13 @@
         <v>1.46</v>
       </c>
       <c r="U28" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V28" t="n">
         <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X28" t="n">
         <v>60</v>
@@ -7548,7 +7548,7 @@
         <v>21</v>
       </c>
       <c r="AI28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ28" t="n">
         <v>22</v>
@@ -7563,64 +7563,64 @@
         <v>60</v>
       </c>
       <c r="AN28" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>36</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>3.9</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
         <v>5.6</v>
@@ -7739,22 +7739,22 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="R29" t="n">
         <v>2.26</v>
       </c>
       <c r="S29" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T29" t="n">
         <v>1.11</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -8223,25 +8223,25 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="G31" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H31" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="K31" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="M31" t="n">
         <v>1.15</v>
@@ -8262,7 +8262,7 @@
         <v>1.13</v>
       </c>
       <c r="S31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T31" t="n">
         <v>2.22</v>
@@ -8271,10 +8271,10 @@
         <v>1.62</v>
       </c>
       <c r="V31" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X31" t="n">
         <v>8.4</v>
@@ -8289,7 +8289,7 @@
         <v>85</v>
       </c>
       <c r="AB31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC31" t="n">
         <v>8.4</v>
@@ -8301,10 +8301,10 @@
         <v>75</v>
       </c>
       <c r="AF31" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH31" t="n">
         <v>34</v>
@@ -8340,10 +8340,10 @@
         <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU31" t="n">
         <v>5.2</v>
@@ -8352,7 +8352,7 @@
         <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AX31" t="n">
         <v>12.5</v>
@@ -8361,34 +8361,34 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH31" t="n">
         <v>2.56</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="BJ31" t="n">
         <v>13</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -8477,46 +8477,46 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G32" t="n">
         <v>2.42</v>
       </c>
       <c r="H32" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="J32" t="n">
-        <v>1.73</v>
+        <v>2.84</v>
       </c>
       <c r="K32" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.28</v>
+        <v>2.24</v>
       </c>
       <c r="O32" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="P32" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.56</v>
+        <v>2.56</v>
       </c>
       <c r="R32" t="n">
         <v>1.12</v>
       </c>
       <c r="S32" t="n">
-        <v>1.96</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
         <v>2.24</v>
@@ -8528,7 +8528,7 @@
         <v>1.23</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X32" t="n">
         <v>9.199999999999999</v>
@@ -8591,7 +8591,7 @@
         <v>8</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AS32" t="n">
         <v>4.2</v>
@@ -8621,7 +8621,7 @@
         <v>4.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BC32" t="n">
         <v>3.95</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -8740,16 +8740,16 @@
         <v>3.05</v>
       </c>
       <c r="I33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="K33" t="n">
         <v>3.15</v>
       </c>
       <c r="L33" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="M33" t="n">
         <v>1.13</v>
@@ -8779,7 +8779,7 @@
         <v>1.62</v>
       </c>
       <c r="V33" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W33" t="n">
         <v>1.49</v>
@@ -8788,7 +8788,7 @@
         <v>8.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z33" t="n">
         <v>25</v>
@@ -8800,7 +8800,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD33" t="n">
         <v>20</v>
@@ -8848,7 +8848,7 @@
         <v>15</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT33" t="n">
         <v>5.5</v>
@@ -8860,7 +8860,7 @@
         <v>11.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX33" t="n">
         <v>12</v>
@@ -8872,25 +8872,25 @@
         <v>19.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.1</v>
+        <v>34</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH33" t="n">
         <v>2.56</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -8985,46 +8985,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="G34" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="M34" t="n">
         <v>1.12</v>
       </c>
       <c r="N34" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O34" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P34" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R34" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S34" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="T34" t="n">
         <v>2.28</v>
@@ -9033,40 +9033,40 @@
         <v>1.64</v>
       </c>
       <c r="V34" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W34" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AA34" t="n">
         <v>170</v>
       </c>
       <c r="AB34" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD34" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AE34" t="n">
         <v>110</v>
       </c>
       <c r="AF34" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG34" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH34" t="n">
         <v>950</v>
@@ -9075,10 +9075,10 @@
         <v>140</v>
       </c>
       <c r="AJ34" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK34" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL34" t="n">
         <v>80</v>
@@ -9087,76 +9087,76 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO34" t="n">
         <v>200</v>
       </c>
       <c r="AP34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR34" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AS34" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA34" t="n">
         <v>7.4</v>
       </c>
       <c r="BB34" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC34" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC34" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD34" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE34" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG34" t="n">
         <v>7.6</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ34" t="n">
         <v>13</v>
       </c>
       <c r="BK34" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
@@ -9165,10 +9165,10 @@
         <v>10.5</v>
       </c>
       <c r="BN34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
@@ -9183,22 +9183,22 @@
         <v>9</v>
       </c>
       <c r="BT34" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BU34" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV34" t="n">
         <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX34" t="n">
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -9239,46 +9239,46 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G35" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="H35" t="n">
         <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="K35" t="n">
         <v>3.15</v>
       </c>
       <c r="L35" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M35" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N35" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="O35" t="n">
         <v>1.74</v>
       </c>
       <c r="P35" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
         <v>1.12</v>
       </c>
       <c r="S35" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="T35" t="n">
         <v>2.46</v>
@@ -9287,10 +9287,10 @@
         <v>1.52</v>
       </c>
       <c r="V35" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W35" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X35" t="n">
         <v>7.2</v>
@@ -9308,7 +9308,7 @@
         <v>6.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD35" t="n">
         <v>26</v>
@@ -9356,7 +9356,7 @@
         <v>4.8</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT35" t="n">
         <v>4.7</v>
@@ -9368,7 +9368,7 @@
         <v>16.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX35" t="n">
         <v>9.6</v>
@@ -9377,34 +9377,34 @@
         <v>10.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF35" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG35" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH35" t="n">
         <v>2.42</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BJ35" t="n">
         <v>14.5</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -9493,37 +9493,37 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H36" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J36" t="n">
-        <v>1.09</v>
+        <v>2.68</v>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L36" t="n">
         <v>1.47</v>
       </c>
       <c r="M36" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="O36" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="P36" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q36" t="n">
         <v>2.32</v>
@@ -9532,7 +9532,7 @@
         <v>1.12</v>
       </c>
       <c r="S36" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -9541,52 +9541,52 @@
         <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA36" t="n">
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL36" t="n">
         <v>1000</v>
@@ -9595,64 +9595,64 @@
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BH36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -9753,49 +9753,49 @@
         <v>2.52</v>
       </c>
       <c r="H37" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="K37" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M37" t="n">
         <v>1.16</v>
       </c>
       <c r="N37" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="O37" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="P37" t="n">
         <v>1.37</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
         <v>1.12</v>
       </c>
       <c r="S37" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="T37" t="n">
         <v>2.32</v>
       </c>
       <c r="U37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V37" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W37" t="n">
         <v>1.66</v>
@@ -9804,28 +9804,28 @@
         <v>7.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA37" t="n">
         <v>110</v>
       </c>
       <c r="AB37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE37" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG37" t="n">
         <v>15.5</v>
@@ -9864,10 +9864,10 @@
         <v>20</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AU37" t="n">
         <v>5.6</v>
@@ -9876,7 +9876,7 @@
         <v>14.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX37" t="n">
         <v>10.5</v>
@@ -9885,28 +9885,28 @@
         <v>10</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BC37" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF37" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
         <v>2.18</v>
       </c>
       <c r="G38" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H38" t="n">
         <v>3.7</v>
@@ -10013,40 +10013,40 @@
         <v>3.8</v>
       </c>
       <c r="J38" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K38" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L38" t="n">
         <v>1.43</v>
       </c>
       <c r="M38" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N38" t="n">
         <v>3.75</v>
       </c>
       <c r="O38" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P38" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S38" t="n">
         <v>3.55</v>
       </c>
       <c r="T38" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U38" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V38" t="n">
         <v>1.35</v>
@@ -10055,7 +10055,7 @@
         <v>1.81</v>
       </c>
       <c r="X38" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y38" t="n">
         <v>14</v>
@@ -10064,7 +10064,7 @@
         <v>26</v>
       </c>
       <c r="AA38" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB38" t="n">
         <v>9.800000000000001</v>
@@ -10100,13 +10100,13 @@
         <v>38</v>
       </c>
       <c r="AM38" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN38" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO38" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP38" t="n">
         <v>12</v>
@@ -10133,13 +10133,13 @@
         <v>38</v>
       </c>
       <c r="AX38" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY38" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ38" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA38" t="n">
         <v>46</v>
@@ -10154,13 +10154,13 @@
         <v>32</v>
       </c>
       <c r="BE38" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BG38" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH38" t="n">
         <v>3.35</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H39" t="n">
         <v>3.85</v>
@@ -10270,7 +10270,7 @@
         <v>3.15</v>
       </c>
       <c r="K39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L39" t="n">
         <v>1.49</v>
@@ -10288,7 +10288,7 @@
         <v>1.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R39" t="n">
         <v>1.24</v>
@@ -10423,37 +10423,37 @@
         <v>2.4</v>
       </c>
       <c r="BJ39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN39" t="n">
         <v>4.9</v>
       </c>
       <c r="BO39" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ39" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR39" t="n">
         <v>38</v>
       </c>
       <c r="BS39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT39" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU39" t="n">
         <v>5.5</v>
@@ -10462,13 +10462,13 @@
         <v>42</v>
       </c>
       <c r="BW39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX39" t="n">
         <v>60</v>
       </c>
       <c r="BY39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -10509,52 +10509,52 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G40" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H40" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I40" t="n">
         <v>4.3</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K40" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M40" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N40" t="n">
         <v>3.05</v>
       </c>
       <c r="O40" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P40" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R40" t="n">
         <v>1.17</v>
       </c>
       <c r="S40" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
       </c>
       <c r="U40" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="V40" t="n">
         <v>1.3</v>
@@ -10563,7 +10563,7 @@
         <v>1.72</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y40" t="n">
         <v>970</v>
@@ -10620,55 +10620,55 @@
         <v>1.11</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.05</v>
+        <v>1.84</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -10763,169 +10763,169 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2.54</v>
-      </c>
-      <c r="H41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.52</v>
       </c>
       <c r="R41" t="n">
         <v>1.19</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U41" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V41" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W41" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="X41" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y41" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="Z41" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA41" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AB41" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD41" t="n">
         <v>950</v>
       </c>
       <c r="AE41" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AF41" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH41" t="n">
         <v>950</v>
       </c>
       <c r="AI41" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ41" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AK41" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL41" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM41" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AN41" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AO41" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AP41" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ41" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AT41" t="n">
         <v>6</v>
       </c>
       <c r="AU41" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV41" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
       <c r="AW41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX41" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ41" t="n">
-        <v>17</v>
+        <v>5.9</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BD41" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BH41" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BI41" t="n">
         <v>2.3</v>
@@ -10934,22 +10934,22 @@
         <v>12</v>
       </c>
       <c r="BK41" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN41" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BO41" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP41" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BQ41" t="n">
         <v>6.6</v>
@@ -10958,35 +10958,35 @@
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BU41" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ41" t="n">
         <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -11017,58 +11017,58 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="G42" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="H42" t="n">
-        <v>2.18</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J42" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="L42" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="M42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N42" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>1.02</v>
       </c>
       <c r="P42" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.34</v>
+        <v>1.92</v>
       </c>
       <c r="R42" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="S42" t="n">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
         <v>2.04</v>
       </c>
       <c r="U42" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W42" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="G43" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H43" t="n">
         <v>3.15</v>
       </c>
       <c r="I43" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>3.15</v>
       </c>
       <c r="K43" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L43" t="n">
         <v>1.42</v>
@@ -11295,7 +11295,7 @@
         <v>1.09</v>
       </c>
       <c r="N43" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O43" t="n">
         <v>1.42</v>
@@ -11304,13 +11304,13 @@
         <v>1.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R43" t="n">
         <v>1.26</v>
       </c>
       <c r="S43" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T43" t="n">
         <v>1.9</v>
@@ -11319,10 +11319,10 @@
         <v>2.06</v>
       </c>
       <c r="V43" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X43" t="n">
         <v>13</v>
@@ -11337,7 +11337,7 @@
         <v>65</v>
       </c>
       <c r="AB43" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC43" t="n">
         <v>7.6</v>
@@ -11379,64 +11379,64 @@
         <v>55</v>
       </c>
       <c r="AP43" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AR43" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AU43" t="n">
         <v>6.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX43" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY43" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ43" t="n">
         <v>6.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.84</v>
+        <v>4.1</v>
       </c>
       <c r="BB43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC43" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC43" t="n">
-        <v>5</v>
-      </c>
       <c r="BD43" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE43" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF43" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH43" t="n">
         <v>3.05</v>
       </c>
       <c r="BI43" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ43" t="n">
         <v>10.5</v>
@@ -11448,53 +11448,53 @@
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>2.14</v>
+        <v>3.15</v>
       </c>
       <c r="BN43" t="n">
         <v>5.2</v>
       </c>
       <c r="BO43" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP43" t="n">
         <v>1000</v>
       </c>
       <c r="BQ43" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR43" t="n">
         <v>1000</v>
       </c>
       <c r="BS43" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="BT43" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU43" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV43" t="n">
         <v>1000</v>
       </c>
       <c r="BW43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX43" t="n">
         <v>1000</v>
       </c>
       <c r="BY43" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="BZ43" t="n">
         <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -11537,10 +11537,10 @@
         <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K44" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L44" t="n">
         <v>1.45</v>
@@ -11549,7 +11549,7 @@
         <v>1.12</v>
       </c>
       <c r="N44" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O44" t="n">
         <v>1.5</v>
@@ -11567,7 +11567,7 @@
         <v>5.1</v>
       </c>
       <c r="T44" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U44" t="n">
         <v>1.78</v>
@@ -11576,7 +11576,7 @@
         <v>1.25</v>
       </c>
       <c r="W44" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X44" t="n">
         <v>9.4</v>
@@ -11633,13 +11633,13 @@
         <v>160</v>
       </c>
       <c r="AP44" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ44" t="n">
         <v>11</v>
       </c>
       <c r="AR44" t="n">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="AS44" t="n">
         <v>12</v>
@@ -11675,7 +11675,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BD44" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BE44" t="n">
         <v>12</v>
@@ -11702,7 +11702,7 @@
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>2.38</v>
+        <v>15.5</v>
       </c>
       <c r="BN44" t="n">
         <v>4.5</v>
@@ -11726,7 +11726,7 @@
         <v>8</v>
       </c>
       <c r="BU44" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV44" t="n">
         <v>50</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -11779,10 +11779,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G45" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H45" t="n">
         <v>4.5</v>
@@ -11794,7 +11794,7 @@
         <v>2.84</v>
       </c>
       <c r="K45" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L45" t="n">
         <v>1.49</v>
@@ -11830,7 +11830,7 @@
         <v>1.2</v>
       </c>
       <c r="W45" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X45" t="n">
         <v>970</v>
@@ -11887,7 +11887,7 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ45" t="n">
         <v>4.2</v>
@@ -11902,7 +11902,7 @@
         <v>2.02</v>
       </c>
       <c r="AU45" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AV45" t="n">
         <v>2.46</v>
@@ -11923,7 +11923,7 @@
         <v>2.7</v>
       </c>
       <c r="BB45" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BC45" t="n">
         <v>2.54</v>
@@ -11944,7 +11944,7 @@
         <v>4.1</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>2.06</v>
       </c>
       <c r="H46" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I46" t="n">
         <v>5.6</v>
@@ -12051,7 +12051,7 @@
         <v>3.5</v>
       </c>
       <c r="L46" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="M46" t="n">
         <v>1.11</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>5.5</v>
       </c>
       <c r="G47" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H47" t="n">
         <v>1.56</v>
@@ -12338,7 +12338,7 @@
         <v>2.4</v>
       </c>
       <c r="W47" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X47" t="n">
         <v>24</v>
@@ -12395,37 +12395,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP47" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ47" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV47" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR47" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS47" t="n">
+      <c r="AW47" t="n">
         <v>12</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>4.4</v>
       </c>
       <c r="AX47" t="n">
         <v>4.7</v>
       </c>
       <c r="AY47" t="n">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BA47" t="n">
         <v>4.9</v>
@@ -12446,7 +12446,7 @@
         <v>4.8</v>
       </c>
       <c r="BG47" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BH47" t="n">
         <v>4.2</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
         <v>3.5</v>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M48" t="n">
         <v>1.1</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -12795,16 +12795,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="G49" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="H49" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="J49" t="n">
         <v>3.05</v>
@@ -12825,10 +12825,10 @@
         <v>1.39</v>
       </c>
       <c r="P49" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R49" t="n">
         <v>1.27</v>
@@ -12843,22 +12843,22 @@
         <v>1.98</v>
       </c>
       <c r="V49" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W49" t="n">
         <v>1.45</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.5</v>
       </c>
       <c r="X49" t="n">
         <v>13.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB49" t="n">
         <v>11.5</v>
@@ -12867,10 +12867,10 @@
         <v>8.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF49" t="n">
         <v>20</v>
@@ -12885,7 +12885,7 @@
         <v>60</v>
       </c>
       <c r="AJ49" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK49" t="n">
         <v>38</v>
@@ -12897,10 +12897,10 @@
         <v>130</v>
       </c>
       <c r="AN49" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AO49" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP49" t="n">
         <v>9</v>
@@ -12912,10 +12912,10 @@
         <v>15</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT49" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU49" t="n">
         <v>5.9</v>
@@ -12924,7 +12924,7 @@
         <v>10</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX49" t="n">
         <v>13</v>
@@ -12936,70 +12936,70 @@
         <v>14</v>
       </c>
       <c r="BA49" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC49" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB49" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD49" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG49" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH49" t="n">
         <v>3.25</v>
       </c>
       <c r="BI49" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="BJ49" t="n">
         <v>10.5</v>
       </c>
       <c r="BK49" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN49" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO49" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP49" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BQ49" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT49" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BU49" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BV49" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW49" t="n">
         <v>7</v>
@@ -13008,17 +13008,17 @@
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA49" t="n">
         <v>7.8</v>
       </c>
-      <c r="BZ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA49" t="n">
-        <v>7.6</v>
-      </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
         <v>4.3</v>
       </c>
       <c r="I50" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J50" t="n">
         <v>3.95</v>
@@ -13067,7 +13067,7 @@
         <v>4.6</v>
       </c>
       <c r="L50" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="M50" t="n">
         <v>1.05</v>
@@ -13091,7 +13091,7 @@
         <v>2.66</v>
       </c>
       <c r="T50" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U50" t="n">
         <v>2.2</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -13303,13 +13303,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G51" t="n">
         <v>2.8</v>
       </c>
       <c r="H51" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I51" t="n">
         <v>3.1</v>
@@ -13318,7 +13318,7 @@
         <v>3.5</v>
       </c>
       <c r="K51" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L51" t="n">
         <v>1.3</v>
@@ -13345,16 +13345,16 @@
         <v>2.92</v>
       </c>
       <c r="T51" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U51" t="n">
         <v>2.26</v>
       </c>
       <c r="V51" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W51" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X51" t="n">
         <v>21</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -13557,22 +13557,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="G52" t="n">
         <v>3.2</v>
       </c>
       <c r="H52" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="I52" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="J52" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="K52" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="L52" t="n">
         <v>1.24</v>
@@ -13593,10 +13593,10 @@
         <v>1.45</v>
       </c>
       <c r="R52" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S52" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T52" t="n">
         <v>1.27</v>
@@ -13605,7 +13605,7 @@
         <v>1.92</v>
       </c>
       <c r="V52" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W52" t="n">
         <v>1.48</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>
@@ -13931,10 +13931,10 @@
         <v>4.7</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="AV53" t="n">
         <v>11</v>
@@ -13967,7 +13967,7 @@
         <v>4.8</v>
       </c>
       <c r="BF53" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BG53" t="n">
         <v>19.5</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-19 16:02:59</t>
+          <t>2026-06-19 18:18:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="G2" t="n">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="H2" t="n">
         <v>2.6</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J2" t="n">
         <v>2.82</v>
@@ -908,10 +908,10 @@
         <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
         <v>950</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G3" t="n">
         <v>2.82</v>
@@ -1135,7 +1135,7 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O3" t="n">
         <v>1.44</v>
@@ -1144,7 +1144,7 @@
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
@@ -1156,7 +1156,7 @@
         <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
         <v>1.41</v>
@@ -1225,25 +1225,25 @@
         <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS3" t="n">
         <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU3" t="n">
         <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
         <v>10.5</v>
@@ -1255,10 +1255,10 @@
         <v>5.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BD3" t="n">
         <v>5.2</v>
@@ -1267,7 +1267,7 @@
         <v>5.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BG3" t="n">
         <v>5.2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -1374,34 +1374,34 @@
         <v>3.65</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
         <v>3.1</v>
@@ -1410,7 +1410,7 @@
         <v>1.72</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
@@ -1440,7 +1440,7 @@
         <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
         <v>16.5</v>
@@ -1449,31 +1449,31 @@
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
         <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>12</v>
@@ -1482,19 +1482,19 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1503,28 +1503,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BC4" t="n">
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.65</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="J5" t="n">
         <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.53</v>
@@ -1649,28 +1649,28 @@
         <v>1.55</v>
       </c>
       <c r="P5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
         <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
         <v>18</v>
@@ -1679,19 +1679,19 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
         <v>16</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
         <v>110</v>
@@ -1700,7 +1700,7 @@
         <v>85</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
@@ -1721,10 +1721,10 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
         <v>4.4</v>
@@ -1736,7 +1736,7 @@
         <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
@@ -1745,104 +1745,104 @@
         <v>4.4</v>
       </c>
       <c r="AV5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW5" t="n">
         <v>5</v>
       </c>
-      <c r="AW5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AX5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.08</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.75</v>
+        <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
@@ -1909,13 +1909,13 @@
         <v>1.41</v>
       </c>
       <c r="R6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U6" t="n">
         <v>2.88</v>
@@ -1933,7 +1933,7 @@
         <v>26</v>
       </c>
       <c r="Z6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="n">
         <v>470</v>
@@ -1987,10 +1987,10 @@
         <v>19.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT6" t="n">
         <v>15.5</v>
@@ -2002,7 +2002,7 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AX6" t="n">
         <v>16</v>
@@ -2032,71 +2032,71 @@
         <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BS6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
@@ -2148,34 +2148,34 @@
         <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
         <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
         <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
         <v>1.62</v>
@@ -2184,7 +2184,7 @@
         <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z7" t="n">
         <v>27</v>
@@ -2202,10 +2202,10 @@
         <v>19.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
         <v>13</v>
@@ -2214,7 +2214,7 @@
         <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>95</v>
@@ -2226,103 +2226,103 @@
         <v>160</v>
       </c>
       <c r="AM7" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO7" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.98</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>5.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.16</v>
+        <v>7.6</v>
       </c>
       <c r="BT7" t="n">
         <v>7</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.14</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.18</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>1.4</v>
       </c>
       <c r="H8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
         <v>10.5</v>
@@ -2420,10 +2420,10 @@
         <v>2.06</v>
       </c>
       <c r="S8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U8" t="n">
         <v>2.4</v>
@@ -2450,7 +2450,7 @@
         <v>34</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AD8" t="n">
         <v>85</v>
@@ -2474,7 +2474,7 @@
         <v>16</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2489,16 +2489,16 @@
         <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
@@ -2507,10 +2507,10 @@
         <v>12.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
@@ -2531,10 +2531,10 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF8" t="n">
         <v>2.9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G9" t="n">
         <v>2.04</v>
@@ -2653,7 +2653,7 @@
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2668,7 +2668,7 @@
         <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
@@ -2683,7 +2683,7 @@
         <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
         <v>1.96</v>
@@ -2728,7 +2728,7 @@
         <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
         <v>85</v>
@@ -2740,22 +2740,22 @@
         <v>55</v>
       </c>
       <c r="AO9" t="n">
-        <v>310</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="AQ9" t="n">
         <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
         <v>6.6</v>
@@ -2764,101 +2764,101 @@
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF9" t="n">
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>4.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
@@ -2922,22 +2922,22 @@
         <v>2.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
         <v>2.02</v>
@@ -2946,13 +2946,13 @@
         <v>120</v>
       </c>
       <c r="Y10" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Z10" t="n">
         <v>85</v>
       </c>
       <c r="AA10" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
         <v>15.5</v>
@@ -3018,7 +3018,7 @@
         <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
         <v>13</v>
@@ -3030,7 +3030,7 @@
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
         <v>18.5</v>
@@ -3048,7 +3048,7 @@
         <v>6</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="n">
         <v>4.9</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>4.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
@@ -3170,7 +3170,7 @@
         <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
         <v>2.42</v>
@@ -3182,7 +3182,7 @@
         <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
         <v>1.74</v>
@@ -3251,10 +3251,10 @@
         <v>80</v>
       </c>
       <c r="AP11" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="AR11" t="n">
         <v>6</v>
@@ -3263,13 +3263,13 @@
         <v>6.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>8.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AW11" t="n">
         <v>6.2</v>
@@ -3278,16 +3278,16 @@
         <v>9.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
         <v>6.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC11" t="n">
         <v>12.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -3406,16 +3406,16 @@
         <v>5.4</v>
       </c>
       <c r="I12" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
@@ -3427,13 +3427,13 @@
         <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q12" t="n">
         <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
         <v>2.1</v>
@@ -3442,7 +3442,7 @@
         <v>1.58</v>
       </c>
       <c r="U12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
         <v>1.18</v>
@@ -3451,7 +3451,7 @@
         <v>2.58</v>
       </c>
       <c r="X12" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Y12" t="n">
         <v>75</v>
@@ -3490,7 +3490,7 @@
         <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL12" t="n">
         <v>70</v>
@@ -3499,7 +3499,7 @@
         <v>320</v>
       </c>
       <c r="AN12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO12" t="n">
         <v>260</v>
@@ -3511,10 +3511,10 @@
         <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -3523,25 +3523,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="n">
         <v>9.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB12" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
         <v>10.5</v>
@@ -3550,7 +3550,7 @@
         <v>17.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF12" t="n">
         <v>4.7</v>
@@ -3559,13 +3559,13 @@
         <v>10.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK12" t="n">
         <v>1.01</v>
@@ -3577,13 +3577,13 @@
         <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.01</v>
@@ -3595,7 +3595,7 @@
         <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU12" t="n">
         <v>1.01</v>
@@ -3613,14 +3613,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA12" t="n">
         <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
         <v>2.88</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J13" t="n">
         <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
@@ -3678,10 +3678,10 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
         <v>2.24</v>
@@ -3702,7 +3702,7 @@
         <v>1.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
         <v>19.5</v>
@@ -3753,10 +3753,10 @@
         <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
         <v>7.4</v>
@@ -3768,7 +3768,7 @@
         <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AT13" t="n">
         <v>4.9</v>
@@ -3780,10 +3780,10 @@
         <v>5.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY13" t="n">
         <v>5.6</v>
@@ -3792,16 +3792,16 @@
         <v>6</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BC13" t="n">
         <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BE13" t="n">
         <v>2.04</v>
@@ -3813,68 +3813,68 @@
         <v>2.54</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -3920,10 +3920,10 @@
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3935,10 +3935,10 @@
         <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R14" t="n">
         <v>1.51</v>
@@ -3947,25 +3947,25 @@
         <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V14" t="n">
         <v>1.56</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X14" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3974,13 +3974,13 @@
         <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="AF14" t="n">
         <v>85</v>
@@ -3989,10 +3989,10 @@
         <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
         <v>230</v>
@@ -4010,19 +4010,19 @@
         <v>970</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ14" t="n">
         <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="AT14" t="n">
         <v>7</v>
@@ -4034,43 +4034,43 @@
         <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY14" t="n">
         <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.65</v>
+        <v>2.54</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.7</v>
+        <v>2.44</v>
       </c>
       <c r="BE14" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4103,10 +4103,10 @@
         <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -4171,40 +4171,40 @@
         <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
         <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
         <v>1.33</v>
@@ -4255,19 +4255,19 @@
         <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>440</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
         <v>150</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AQ15" t="n">
         <v>9.4</v>
@@ -4276,10 +4276,10 @@
         <v>21</v>
       </c>
       <c r="AS15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT15" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
         <v>6.2</v>
@@ -4294,67 +4294,67 @@
         <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
         <v>38</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
         <v>11</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT15" t="n">
         <v>7.2</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -4419,19 +4419,19 @@
         <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
         <v>4.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
         <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -4443,7 +4443,7 @@
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
         <v>1.97</v>
@@ -4464,7 +4464,7 @@
         <v>1.26</v>
       </c>
       <c r="W16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X16" t="n">
         <v>24</v>
@@ -4518,10 +4518,10 @@
         <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>310</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ16" t="n">
         <v>7.6</v>
@@ -4551,7 +4551,7 @@
         <v>6.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BA16" t="n">
         <v>6.6</v>
@@ -4578,7 +4578,7 @@
         <v>3.45</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H17" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
         <v>3.8</v>
@@ -4694,10 +4694,10 @@
         <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
         <v>1.98</v>
@@ -4706,7 +4706,7 @@
         <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
         <v>1.81</v>
@@ -4715,10 +4715,10 @@
         <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X17" t="n">
         <v>14.5</v>
@@ -4727,13 +4727,13 @@
         <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB17" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC17" t="n">
         <v>8.199999999999999</v>
@@ -4742,13 +4742,13 @@
         <v>14</v>
       </c>
       <c r="AE17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF17" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
         <v>18.5</v>
@@ -4769,19 +4769,19 @@
         <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS17" t="n">
         <v>26</v>
@@ -4799,7 +4799,7 @@
         <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
         <v>11.5</v>
@@ -4811,49 +4811,49 @@
         <v>32</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC17" t="n">
         <v>30</v>
       </c>
       <c r="BD17" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
         <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH17" t="n">
         <v>3.45</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ17" t="n">
         <v>10</v>
       </c>
       <c r="BK17" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BQ17" t="n">
         <v>7.4</v>
@@ -4862,16 +4862,16 @@
         <v>40</v>
       </c>
       <c r="BS17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW17" t="n">
         <v>6.6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G18" t="n">
         <v>3.5</v>
@@ -4930,7 +4930,7 @@
         <v>2.14</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
@@ -4951,25 +4951,25 @@
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R18" t="n">
         <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W18" t="n">
         <v>1.4</v>
@@ -4993,7 +4993,7 @@
         <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
         <v>22</v>
@@ -5026,7 +5026,7 @@
         <v>70</v>
       </c>
       <c r="AO18" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
         <v>15.5</v>
@@ -5044,7 +5044,7 @@
         <v>13.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV18" t="n">
         <v>8.800000000000001</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
         <v>2.88</v>
       </c>
       <c r="O19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P19" t="n">
         <v>1.64</v>
@@ -5316,22 +5316,22 @@
         <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB19" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG19" t="n">
         <v>36</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
         <v>1.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
         <v>2.46</v>
@@ -5540,10 +5540,10 @@
         <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS20" t="n">
         <v>6</v>
@@ -5555,10 +5555,10 @@
         <v>9.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX20" t="n">
         <v>7.6</v>
@@ -5570,7 +5570,7 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
@@ -5579,16 +5579,16 @@
         <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF20" t="n">
         <v>4.9</v>
       </c>
       <c r="BG20" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH20" t="n">
         <v>4.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>1.1</v>
@@ -5719,7 +5719,7 @@
         <v>1.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S21" t="n">
         <v>1.75</v>
@@ -5746,7 +5746,7 @@
         <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
         <v>950</v>
@@ -5770,7 +5770,7 @@
         <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -5803,7 +5803,7 @@
         <v>5.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU21" t="n">
         <v>5.5</v>
@@ -5818,7 +5818,7 @@
         <v>4.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AZ21" t="n">
         <v>4.6</v>
@@ -5839,7 +5839,7 @@
         <v>2.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG21" t="n">
         <v>2.96</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6191,166 +6191,166 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="G23" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="H23" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
         <v>1.07</v>
       </c>
       <c r="P23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q23" t="n">
         <v>1.23</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S23" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="X23" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Y23" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Z23" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA23" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB23" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AC23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK23" t="n">
         <v>17</v>
       </c>
-      <c r="AD23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AM23" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AN23" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO23" t="n">
-        <v>180</v>
+        <v>970</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.6</v>
+        <v>28</v>
       </c>
       <c r="AQ23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AR23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS23" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT23" t="n">
         <v>24</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>24</v>
+        <v>6.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.7</v>
+        <v>2.96</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BE23" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
         <v>1.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
         <v>2.56</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="n">
         <v>2.9</v>
@@ -6977,16 +6977,16 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R26" t="n">
         <v>1.24</v>
@@ -7010,7 +7010,7 @@
         <v>13</v>
       </c>
       <c r="Y26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
         <v>22</v>
@@ -7040,7 +7040,7 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ26" t="n">
         <v>46</v>
@@ -7070,7 +7070,7 @@
         <v>15</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT26" t="n">
         <v>6.8</v>
@@ -7082,7 +7082,7 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX26" t="n">
         <v>12</v>
@@ -7094,25 +7094,25 @@
         <v>14</v>
       </c>
       <c r="BA26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD26" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD26" t="n">
+      <c r="BE26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF26" t="n">
         <v>5.4</v>
       </c>
-      <c r="BE26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG26" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH26" t="n">
         <v>3.2</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7261,7 @@
         <v>1.4</v>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y27" t="n">
         <v>10.5</v>
@@ -7270,7 +7270,7 @@
         <v>17</v>
       </c>
       <c r="AA27" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB27" t="n">
         <v>12.5</v>
@@ -7300,13 +7300,13 @@
         <v>65</v>
       </c>
       <c r="AK27" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AL27" t="n">
         <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
         <v>42</v>
@@ -7324,7 +7324,7 @@
         <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT27" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX27" t="n">
         <v>18.5</v>
@@ -7351,19 +7351,19 @@
         <v>34</v>
       </c>
       <c r="BB27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC27" t="n">
         <v>32</v>
       </c>
       <c r="BD27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF27" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>6.6</v>
       </c>
       <c r="BG27" t="n">
         <v>20</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>2.12</v>
       </c>
       <c r="G28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H28" t="n">
         <v>3.8</v>
@@ -7512,16 +7512,16 @@
         <v>1.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="n">
         <v>14.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AA28" t="n">
         <v>900</v>
@@ -7536,7 +7536,7 @@
         <v>21</v>
       </c>
       <c r="AE28" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF28" t="n">
         <v>15.5</v>
@@ -7557,7 +7557,7 @@
         <v>34</v>
       </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM28" t="n">
         <v>500</v>
@@ -7578,7 +7578,7 @@
         <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT28" t="n">
         <v>5.9</v>
@@ -7590,7 +7590,7 @@
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AX28" t="n">
         <v>9.4</v>
@@ -7602,7 +7602,7 @@
         <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB28" t="n">
         <v>21</v>
@@ -7611,16 +7611,16 @@
         <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF28" t="n">
         <v>18.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH28" t="n">
         <v>3.05</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -7718,19 +7718,19 @@
         <v>1.53</v>
       </c>
       <c r="G29" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
         <v>5.9</v>
       </c>
       <c r="J29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,142 +7739,142 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P29" t="n">
         <v>3.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="R29" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="S29" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="T29" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="U29" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="V29" t="n">
         <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X29" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="Y29" t="n">
         <v>48</v>
       </c>
       <c r="Z29" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA29" t="n">
         <v>140</v>
       </c>
       <c r="AB29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD29" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE29" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AF29" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG29" t="n">
         <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
         <v>15.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="n">
         <v>60</v>
       </c>
       <c r="AN29" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AO29" t="n">
         <v>36</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O30" t="n">
         <v>1.07</v>
@@ -8002,19 +8002,19 @@
         <v>3.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="R30" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S30" t="n">
         <v>1.56</v>
       </c>
       <c r="T30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="U30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="V30" t="n">
         <v>1.4</v>
@@ -8026,10 +8026,10 @@
         <v>950</v>
       </c>
       <c r="Y30" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="Z30" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA30" t="n">
         <v>900</v>
@@ -8038,13 +8038,13 @@
         <v>34</v>
       </c>
       <c r="AC30" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AD30" t="n">
         <v>22</v>
       </c>
       <c r="AE30" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF30" t="n">
         <v>34</v>
@@ -8053,146 +8053,146 @@
         <v>15.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ30" t="n">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AK30" t="n">
         <v>20</v>
       </c>
       <c r="AL30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="n">
         <v>38</v>
       </c>
       <c r="AN30" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO30" t="n">
         <v>12.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AQ30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU30" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT30" t="n">
+      <c r="BV30" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>21</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CA30" t="n">
         <v>4.1</v>
       </c>
-      <c r="AU30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA30" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
         <v>2.74</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.64</v>
@@ -8250,7 +8250,7 @@
         <v>2.18</v>
       </c>
       <c r="O31" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P31" t="n">
         <v>1.41</v>
@@ -8283,10 +8283,10 @@
         <v>8.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA31" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AB31" t="n">
         <v>9</v>
@@ -8295,22 +8295,22 @@
         <v>8.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="AF31" t="n">
         <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH31" t="n">
         <v>34</v>
       </c>
       <c r="AI31" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ31" t="n">
         <v>70</v>
@@ -8331,58 +8331,58 @@
         <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR31" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX31" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ31" t="n">
         <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BC31" t="n">
         <v>38</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH31" t="n">
         <v>2.56</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -8480,10 +8480,10 @@
         <v>2.06</v>
       </c>
       <c r="G32" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H32" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
         <v>5.3</v>
@@ -8501,10 +8501,10 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="O32" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P32" t="n">
         <v>1.41</v>
@@ -8519,16 +8519,16 @@
         <v>2.56</v>
       </c>
       <c r="T32" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="V32" t="n">
         <v>1.23</v>
       </c>
       <c r="W32" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X32" t="n">
         <v>9.199999999999999</v>
@@ -8537,7 +8537,7 @@
         <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
@@ -8546,10 +8546,10 @@
         <v>7.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE32" t="n">
         <v>500</v>
@@ -8558,22 +8558,22 @@
         <v>15</v>
       </c>
       <c r="AG32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI32" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ32" t="n">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AK32" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AL32" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AM32" t="n">
         <v>500</v>
@@ -8585,31 +8585,31 @@
         <v>500</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ32" t="n">
         <v>8</v>
       </c>
       <c r="AR32" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV32" t="n">
         <v>14.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY32" t="n">
         <v>9</v>
@@ -8618,25 +8618,25 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB32" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF32" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD33" t="n">
         <v>20</v>
@@ -8848,7 +8848,7 @@
         <v>15</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT33" t="n">
         <v>5.5</v>
@@ -8860,7 +8860,7 @@
         <v>11.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX33" t="n">
         <v>12</v>
@@ -8872,25 +8872,25 @@
         <v>19.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE33" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC33" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF33" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH33" t="n">
         <v>2.56</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
         <v>1.99</v>
       </c>
       <c r="G34" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
         <v>4.3</v>
@@ -9036,7 +9036,7 @@
         <v>1.24</v>
       </c>
       <c r="W34" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
         <v>9.4</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
         <v>1.17</v>
       </c>
       <c r="N35" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="O35" t="n">
         <v>1.74</v>
@@ -9350,7 +9350,7 @@
         <v>4.9</v>
       </c>
       <c r="AQ35" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AR35" t="n">
         <v>5</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -9496,13 +9496,13 @@
         <v>1.66</v>
       </c>
       <c r="G36" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H36" t="n">
         <v>4.3</v>
       </c>
       <c r="I36" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="J36" t="n">
         <v>2.68</v>
@@ -9517,13 +9517,13 @@
         <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.02</v>
+        <v>1.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.28</v>
       </c>
       <c r="P36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Q36" t="n">
         <v>2.32</v>
@@ -9544,7 +9544,7 @@
         <v>1.13</v>
       </c>
       <c r="W36" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X36" t="n">
         <v>950</v>
@@ -9574,7 +9574,7 @@
         <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH36" t="n">
         <v>950</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
         <v>2.22</v>
       </c>
       <c r="O37" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P37" t="n">
         <v>1.37</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
         <v>3.7</v>
       </c>
       <c r="I38" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>3.5</v>
@@ -10139,7 +10139,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ38" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA38" t="n">
         <v>46</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -10512,10 +10512,10 @@
         <v>2.1</v>
       </c>
       <c r="G40" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H40" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I40" t="n">
         <v>4.3</v>
@@ -10524,7 +10524,7 @@
         <v>3.2</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.38</v>
@@ -10560,7 +10560,7 @@
         <v>1.31</v>
       </c>
       <c r="W40" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X40" t="n">
         <v>970</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -10772,10 +10772,10 @@
         <v>5</v>
       </c>
       <c r="I41" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K41" t="n">
         <v>8</v>
@@ -10790,7 +10790,7 @@
         <v>3</v>
       </c>
       <c r="O41" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="P41" t="n">
         <v>1.81</v>
@@ -10808,7 +10808,7 @@
         <v>2.04</v>
       </c>
       <c r="U41" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V41" t="n">
         <v>1.1</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -11026,10 +11026,10 @@
         <v>4.3</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K42" t="n">
         <v>3.35</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
@@ -11295,13 +11295,13 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O43" t="n">
         <v>1.01</v>
       </c>
       <c r="P43" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
         <v>2.6</v>
       </c>
       <c r="H44" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I44" t="n">
         <v>3.45</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -11779,40 +11779,40 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G45" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="H45" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J45" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K45" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M45" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O45" t="n">
         <v>1.5</v>
       </c>
       <c r="P45" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R45" t="n">
         <v>1.21</v>
@@ -11821,25 +11821,25 @@
         <v>5</v>
       </c>
       <c r="T45" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U45" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V45" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W45" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="X45" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y45" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Z45" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA45" t="n">
         <v>900</v>
@@ -11848,22 +11848,22 @@
         <v>7</v>
       </c>
       <c r="AC45" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE45" t="n">
         <v>100</v>
       </c>
       <c r="AF45" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG45" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH45" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI45" t="n">
         <v>500</v>
@@ -11875,7 +11875,7 @@
         <v>65</v>
       </c>
       <c r="AL45" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM45" t="n">
         <v>500</v>
@@ -11887,7 +11887,7 @@
         <v>500</v>
       </c>
       <c r="AP45" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ45" t="n">
         <v>11</v>
@@ -11896,7 +11896,7 @@
         <v>28</v>
       </c>
       <c r="AS45" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AT45" t="n">
         <v>6</v>
@@ -11908,43 +11908,43 @@
         <v>17</v>
       </c>
       <c r="AW45" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AX45" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY45" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ45" t="n">
         <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BB45" t="n">
         <v>20</v>
       </c>
       <c r="BC45" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BD45" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE45" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>12.5</v>
       </c>
       <c r="BF45" t="n">
         <v>20</v>
       </c>
       <c r="BG45" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH45" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI45" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ45" t="n">
         <v>11.5</v>
@@ -11956,16 +11956,16 @@
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP45" t="n">
         <v>15.5</v>
-      </c>
-      <c r="BN45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO45" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP45" t="n">
-        <v>16</v>
       </c>
       <c r="BQ45" t="n">
         <v>8.199999999999999</v>
@@ -11974,10 +11974,10 @@
         <v>38</v>
       </c>
       <c r="BS45" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU45" t="n">
         <v>6.2</v>
@@ -11986,23 +11986,23 @@
         <v>50</v>
       </c>
       <c r="BW45" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ45" t="n">
         <v>40</v>
       </c>
       <c r="CA45" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G46" t="n">
         <v>2.14</v>
@@ -12054,16 +12054,16 @@
         <v>1.49</v>
       </c>
       <c r="M46" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N46" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="O46" t="n">
         <v>1.51</v>
       </c>
       <c r="P46" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="Q46" t="n">
         <v>2.36</v>
@@ -12072,7 +12072,7 @@
         <v>1.2</v>
       </c>
       <c r="S46" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T46" t="n">
         <v>2.16</v>
@@ -12141,70 +12141,70 @@
         <v>700</v>
       </c>
       <c r="AP46" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="AT46" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE46" t="n">
         <v>2.08</v>
       </c>
-      <c r="AU46" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>2.48</v>
-      </c>
       <c r="BF46" t="n">
-        <v>17</v>
+        <v>1.95</v>
       </c>
       <c r="BG46" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="BH46" t="n">
         <v>4.1</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ46" t="n">
         <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
@@ -12222,7 +12222,7 @@
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
         <v>5.5</v>
       </c>
       <c r="G48" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H48" t="n">
         <v>1.58</v>
@@ -12649,37 +12649,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP48" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR48" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="AT48" t="n">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="AU48" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV48" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW48" t="n">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="AX48" t="n">
         <v>4.7</v>
       </c>
       <c r="AY48" t="n">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="AZ48" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="BA48" t="n">
         <v>4.9</v>
@@ -12700,7 +12700,7 @@
         <v>4.8</v>
       </c>
       <c r="BG48" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BH48" t="n">
         <v>4.2</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
         <v>3.15</v>
       </c>
       <c r="K49" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L49" t="n">
         <v>1.5</v>
@@ -12822,13 +12822,13 @@
         <v>2.9</v>
       </c>
       <c r="O49" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P49" t="n">
         <v>1.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R49" t="n">
         <v>1.24</v>
@@ -12837,7 +12837,7 @@
         <v>4.4</v>
       </c>
       <c r="T49" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U49" t="n">
         <v>1.84</v>
@@ -12849,10 +12849,10 @@
         <v>1.83</v>
       </c>
       <c r="X49" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z49" t="n">
         <v>38</v>
@@ -12861,13 +12861,13 @@
         <v>130</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC49" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE49" t="n">
         <v>85</v>
@@ -12876,10 +12876,10 @@
         <v>14.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI49" t="n">
         <v>100</v>
@@ -12909,10 +12909,10 @@
         <v>9.4</v>
       </c>
       <c r="AR49" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT49" t="n">
         <v>5.7</v>
@@ -12924,19 +12924,19 @@
         <v>13</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX49" t="n">
         <v>9</v>
       </c>
       <c r="AY49" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ49" t="n">
         <v>15.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB49" t="n">
         <v>19.5</v>
@@ -12945,16 +12945,16 @@
         <v>19</v>
       </c>
       <c r="BD49" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF49" t="n">
         <v>16</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH49" t="n">
         <v>3</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -13109,7 +13109,7 @@
         <v>11.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA50" t="n">
         <v>50</v>
@@ -13118,7 +13118,7 @@
         <v>11.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD50" t="n">
         <v>14.5</v>
@@ -13133,7 +13133,7 @@
         <v>14.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI50" t="n">
         <v>60</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="AS50" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT50" t="n">
         <v>8.199999999999999</v>
@@ -13178,37 +13178,37 @@
         <v>10</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX50" t="n">
         <v>13</v>
       </c>
       <c r="AY50" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ50" t="n">
         <v>14</v>
       </c>
       <c r="BA50" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD50" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE50" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG50" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>4.9</v>
       </c>
       <c r="BH50" t="n">
         <v>3.25</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13342,7 @@
         <v>1.48</v>
       </c>
       <c r="S51" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T51" t="n">
         <v>1.68</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13560,7 @@
         <v>2.48</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H52" t="n">
         <v>2.7</v>
@@ -13569,7 +13569,7 @@
         <v>3.1</v>
       </c>
       <c r="J52" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K52" t="n">
         <v>4.5</v>
@@ -13605,7 +13605,7 @@
         <v>2.26</v>
       </c>
       <c r="V52" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W52" t="n">
         <v>1.56</v>
@@ -13629,10 +13629,10 @@
         <v>10.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE52" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF52" t="n">
         <v>23</v>
@@ -13713,7 +13713,7 @@
         <v>1.03</v>
       </c>
       <c r="BF52" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG52" t="n">
         <v>16.5</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
         <v>2.44</v>
       </c>
       <c r="G53" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="H53" t="n">
         <v>2.2</v>
@@ -13835,7 +13835,7 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O53" t="n">
         <v>1.19</v>
@@ -13859,7 +13859,7 @@
         <v>1.92</v>
       </c>
       <c r="V53" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W53" t="n">
         <v>1.48</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
         <v>3.6</v>
       </c>
       <c r="K54" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L54" t="n">
         <v>1.29</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-19 20:34:23</t>
+          <t>2026-06-19 22:50:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
         <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,16 +881,16 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -905,10 +905,10 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H3" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
         <v>3.45</v>
@@ -1126,25 +1126,25 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
@@ -1153,16 +1153,16 @@
         <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
@@ -1180,10 +1180,10 @@
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
@@ -1192,7 +1192,7 @@
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
         <v>21</v>
@@ -1204,7 +1204,7 @@
         <v>50</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
         <v>60</v>
@@ -1213,25 +1213,25 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
         <v>17.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
         <v>6.2</v>
@@ -1240,7 +1240,7 @@
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
         <v>14</v>
@@ -1252,46 +1252,46 @@
         <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3" t="n">
         <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.34</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO3" t="n">
         <v>4.3</v>
@@ -1300,16 +1300,16 @@
         <v>23</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>42</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.24</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU3" t="n">
         <v>4.8</v>
@@ -1318,23 +1318,23 @@
         <v>29</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.26</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>42</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.24</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -1365,67 +1365,67 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
         <v>2.16</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
         <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
         <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
@@ -1467,13 +1467,13 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>12</v>
@@ -1482,19 +1482,19 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1503,46 +1503,46 @@
         <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB4" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.9</v>
       </c>
       <c r="BC4" t="n">
         <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN4" t="n">
         <v>5</v>
@@ -1551,34 +1551,34 @@
         <v>4.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
         <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z5" t="n">
         <v>38</v>
@@ -1688,13 +1688,13 @@
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>30</v>
       </c>
       <c r="AE5" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
         <v>85</v>
@@ -1706,22 +1706,22 @@
         <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>600</v>
@@ -1730,16 +1730,16 @@
         <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
         <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
         <v>4.4</v>
@@ -1748,37 +1748,37 @@
         <v>5.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
         <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.62</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.56</v>
+        <v>3.85</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -1927,13 +1927,13 @@
         <v>1.92</v>
       </c>
       <c r="X6" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="Y6" t="n">
         <v>26</v>
       </c>
       <c r="Z6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AA6" t="n">
         <v>470</v>
@@ -1960,16 +1960,16 @@
         <v>16</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AK6" t="n">
         <v>17.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
         <v>50</v>
@@ -1990,7 +1990,7 @@
         <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.4</v>
+        <v>50</v>
       </c>
       <c r="AT6" t="n">
         <v>15.5</v>
@@ -1999,7 +1999,7 @@
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
         <v>18</v>
@@ -2011,7 +2011,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
         <v>18.5</v>
@@ -2032,7 +2032,7 @@
         <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH6" t="n">
         <v>5.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
         <v>2.98</v>
@@ -2160,7 +2160,7 @@
         <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
         <v>1.21</v>
@@ -2259,10 +2259,10 @@
         <v>6.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
         <v>17.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -2387,19 +2387,19 @@
         <v>1.4</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I8" t="n">
         <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
         <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
@@ -2414,13 +2414,13 @@
         <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="R8" t="n">
         <v>2.06</v>
       </c>
       <c r="S8" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="T8" t="n">
         <v>1.61</v>
@@ -2432,7 +2432,7 @@
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X8" t="n">
         <v>130</v>
@@ -2447,7 +2447,7 @@
         <v>260</v>
       </c>
       <c r="AB8" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
         <v>19</v>
@@ -2459,7 +2459,7 @@
         <v>240</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
         <v>14</v>
@@ -2483,22 +2483,22 @@
         <v>80</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="AO8" t="n">
         <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
@@ -2507,10 +2507,10 @@
         <v>12.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
@@ -2531,10 +2531,10 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
         <v>2.9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>1.88</v>
       </c>
       <c r="G9" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
         <v>4.9</v>
@@ -2650,10 +2650,10 @@
         <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2662,22 +2662,22 @@
         <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
         <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="R9" t="n">
         <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="U9" t="n">
         <v>2.1</v>
@@ -2686,13 +2686,13 @@
         <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
         <v>85</v>
@@ -2701,7 +2701,7 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
         <v>9.4</v>
@@ -2716,7 +2716,7 @@
         <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AH9" t="n">
         <v>22</v>
@@ -2743,16 +2743,16 @@
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="AQ9" t="n">
         <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
@@ -2764,37 +2764,37 @@
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.9</v>
+        <v>3.65</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>3.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="n">
         <v>3.55</v>
@@ -2818,10 +2818,10 @@
         <v>4.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
         <v>6</v>
@@ -2833,16 +2833,16 @@
         <v>7.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
@@ -2854,11 +2854,11 @@
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.8</v>
       </c>
       <c r="G10" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
         <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.26</v>
@@ -2913,148 +2913,148 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P10" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q10" t="n">
         <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T10" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>2.52</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X10" t="n">
         <v>120</v>
       </c>
       <c r="Y10" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Z10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
         <v>260</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
         <v>150</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AL10" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM10" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="AO10" t="n">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.5</v>
+        <v>1.86</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.4</v>
+        <v>1.89</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="AT10" t="n">
-        <v>12.5</v>
+        <v>1.76</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>1.79</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>1.79</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>1.79</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.6</v>
+        <v>1.89</v>
       </c>
       <c r="BB10" t="n">
-        <v>18.5</v>
+        <v>1.88</v>
       </c>
       <c r="BC10" t="n">
-        <v>14.5</v>
+        <v>1.82</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.5</v>
+        <v>1.87</v>
       </c>
       <c r="BE10" t="n">
-        <v>8</v>
+        <v>1.91</v>
       </c>
       <c r="BF10" t="n">
-        <v>6</v>
+        <v>1.87</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ10" t="n">
         <v>9</v>
@@ -3066,53 +3066,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BU10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>8</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CA10" t="n">
         <v>6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
         <v>2.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R11" t="n">
         <v>1.56</v>
@@ -3185,7 +3185,7 @@
         <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
         <v>2.16</v>
@@ -3194,19 +3194,19 @@
         <v>1.18</v>
       </c>
       <c r="W11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X11" t="n">
         <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Z11" t="n">
         <v>60</v>
       </c>
       <c r="AA11" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AB11" t="n">
         <v>11.5</v>
@@ -3215,7 +3215,7 @@
         <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
         <v>200</v>
@@ -3230,7 +3230,7 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ11" t="n">
         <v>16</v>
@@ -3239,13 +3239,13 @@
         <v>18</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO11" t="n">
         <v>80</v>
@@ -3254,13 +3254,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
@@ -3272,7 +3272,7 @@
         <v>20</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX11" t="n">
         <v>9.4</v>
@@ -3284,7 +3284,7 @@
         <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
         <v>12.5</v>
@@ -3296,77 +3296,77 @@
         <v>21</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
         <v>5.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="n">
         <v>4.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BN11" t="n">
         <v>4.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP11" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
         <v>5.4</v>
@@ -3415,28 +3415,28 @@
         <v>5.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T12" t="n">
         <v>1.58</v>
@@ -3493,7 +3493,7 @@
         <v>15.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
         <v>320</v>
@@ -3568,13 +3568,13 @@
         <v>9.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN12" t="n">
         <v>4.9</v>
@@ -3586,41 +3586,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT12" t="n">
         <v>10</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>11.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -3654,22 +3654,22 @@
         <v>2.76</v>
       </c>
       <c r="G13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
         <v>3.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
@@ -3681,19 +3681,19 @@
         <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U13" t="n">
         <v>1.94</v>
@@ -3711,7 +3711,7 @@
         <v>130</v>
       </c>
       <c r="Z13" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
@@ -3726,7 +3726,7 @@
         <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
         <v>970</v>
@@ -3738,19 +3738,19 @@
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
         <v>600</v>
@@ -3765,58 +3765,58 @@
         <v>4.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="AT13" t="n">
         <v>4.9</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AV13" t="n">
         <v>5.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY13" t="n">
         <v>5.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BF13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG13" t="n">
         <v>2.52</v>
       </c>
-      <c r="BG13" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BH13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="BN13" t="n">
         <v>5.8</v>
@@ -3846,7 +3846,7 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BT13" t="n">
         <v>6.2</v>
@@ -3864,17 +3864,17 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -3911,19 +3911,19 @@
         <v>2.98</v>
       </c>
       <c r="H14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I14" t="n">
         <v>2.76</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
         <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3935,16 +3935,16 @@
         <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R14" t="n">
         <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
         <v>1.58</v>
@@ -3953,19 +3953,19 @@
         <v>2.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
         <v>1.51</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3980,10 +3980,10 @@
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
@@ -3992,16 +3992,16 @@
         <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
         <v>230</v>
       </c>
       <c r="AK14" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
@@ -4022,7 +4022,7 @@
         <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AT14" t="n">
         <v>7</v>
@@ -4046,25 +4046,25 @@
         <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BC14" t="n">
         <v>6.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH14" t="n">
         <v>4.2</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.45</v>
@@ -4183,43 +4183,43 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
         <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X15" t="n">
         <v>12</v>
       </c>
       <c r="Y15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AA15" t="n">
         <v>500</v>
@@ -4231,19 +4231,19 @@
         <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AF15" t="n">
         <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
         <v>160</v>
@@ -4261,7 +4261,7 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
         <v>150</v>
@@ -4276,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT15" t="n">
         <v>7.2</v>
@@ -4300,7 +4300,7 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -4312,7 +4312,7 @@
         <v>38</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>19.5</v>
@@ -4321,68 +4321,68 @@
         <v>11</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BJ15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP15" t="n">
         <v>19</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -4437,10 +4437,10 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
         <v>1.96</v>
@@ -4452,19 +4452,19 @@
         <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
         <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X16" t="n">
         <v>24</v>
@@ -4485,28 +4485,28 @@
         <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
         <v>25</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
         <v>36</v>
       </c>
       <c r="AI16" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
         <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL16" t="n">
         <v>100</v>
@@ -4527,10 +4527,10 @@
         <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT16" t="n">
         <v>5.1</v>
@@ -4539,13 +4539,13 @@
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX16" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>9</v>
       </c>
       <c r="AY16" t="n">
         <v>6.2</v>
@@ -4554,28 +4554,28 @@
         <v>10.5</v>
       </c>
       <c r="BA16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB16" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB16" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BC16" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD16" t="n">
         <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI16" t="n">
         <v>2.66</v>
@@ -4584,13 +4584,13 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN16" t="n">
         <v>4.8</v>
@@ -4602,41 +4602,41 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT16" t="n">
         <v>8</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -4670,22 +4670,22 @@
         <v>2.96</v>
       </c>
       <c r="G17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -4697,16 +4697,16 @@
         <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
         <v>1.98</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
         <v>1.81</v>
@@ -4715,19 +4715,19 @@
         <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
         <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA17" t="n">
         <v>38</v>
@@ -4739,7 +4739,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE17" t="n">
         <v>30</v>
@@ -4748,7 +4748,7 @@
         <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
         <v>18.5</v>
@@ -4766,22 +4766,22 @@
         <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>120</v>
+        <v>380</v>
       </c>
       <c r="AN17" t="n">
         <v>38</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS17" t="n">
         <v>26</v>
@@ -4799,7 +4799,7 @@
         <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY17" t="n">
         <v>11.5</v>
@@ -4811,22 +4811,22 @@
         <v>32</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="BD17" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
         <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH17" t="n">
         <v>3.45</v>
@@ -4844,43 +4844,43 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN17" t="n">
         <v>6.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP17" t="n">
         <v>27</v>
       </c>
       <c r="BQ17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR17" t="n">
         <v>40</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU17" t="n">
         <v>4.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX17" t="n">
         <v>34</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H18" t="n">
         <v>2.14</v>
@@ -4933,37 +4933,37 @@
         <v>2.22</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
         <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U18" t="n">
         <v>2.36</v>
@@ -4972,7 +4972,7 @@
         <v>1.81</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
@@ -4981,16 +4981,16 @@
         <v>15.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AA18" t="n">
         <v>32</v>
       </c>
       <c r="AB18" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
         <v>11.5</v>
@@ -4999,16 +4999,16 @@
         <v>22</v>
       </c>
       <c r="AF18" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ18" t="n">
         <v>900</v>
@@ -5023,7 +5023,7 @@
         <v>70</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AO18" t="n">
         <v>55</v>
@@ -5032,7 +5032,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR18" t="n">
         <v>12</v>
@@ -5047,34 +5047,34 @@
         <v>7.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
         <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BC18" t="n">
-        <v>26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD18" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE18" t="n">
         <v>28</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>48</v>
       </c>
       <c r="BF18" t="n">
         <v>18.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
         <v>3.15</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L19" t="n">
         <v>1.54</v>
@@ -5199,22 +5199,22 @@
         <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P19" t="n">
         <v>1.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T19" t="n">
         <v>1.98</v>
@@ -5223,16 +5223,16 @@
         <v>1.98</v>
       </c>
       <c r="V19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
         <v>1.54</v>
       </c>
       <c r="X19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z19" t="n">
         <v>20</v>
@@ -5244,7 +5244,7 @@
         <v>9.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD19" t="n">
         <v>14</v>
@@ -5277,16 +5277,16 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP19" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR19" t="n">
         <v>16.5</v>
@@ -5310,7 +5310,7 @@
         <v>15</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AZ19" t="n">
         <v>18</v>
@@ -5328,7 +5328,7 @@
         <v>9</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
         <v>8.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -5429,58 +5429,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="G20" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="H20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I20" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="T20" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="U20" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W20" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="X20" t="n">
         <v>28</v>
@@ -5495,10 +5495,10 @@
         <v>330</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD20" t="n">
         <v>36</v>
@@ -5507,7 +5507,7 @@
         <v>150</v>
       </c>
       <c r="AF20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
@@ -5531,34 +5531,34 @@
         <v>150</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO20" t="n">
         <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
         <v>7.6</v>
@@ -5567,10 +5567,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
@@ -5579,16 +5579,16 @@
         <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH20" t="n">
         <v>4.5</v>
@@ -5600,59 +5600,59 @@
         <v>12</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BP20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR20" t="n">
         <v>25</v>
       </c>
       <c r="BS20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BT20" t="n">
         <v>13</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV20" t="n">
         <v>75</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX20" t="n">
         <v>70</v>
       </c>
       <c r="BY20" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>9.4</v>
@@ -5692,46 +5692,46 @@
         <v>1.37</v>
       </c>
       <c r="I21" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="J21" t="n">
         <v>5.1</v>
       </c>
       <c r="K21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="O21" t="n">
         <v>1.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q21" t="n">
         <v>1.3</v>
       </c>
       <c r="R21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S21" t="n">
         <v>1.75</v>
       </c>
       <c r="T21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U21" t="n">
         <v>2.5</v>
       </c>
       <c r="V21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="W21" t="n">
         <v>1.13</v>
@@ -5824,7 +5824,7 @@
         <v>4.6</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BB21" t="n">
         <v>4.2</v>
@@ -5839,7 +5839,7 @@
         <v>2.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
         <v>2.96</v>
@@ -5854,59 +5854,59 @@
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>5.5</v>
+        <v>2.32</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.02</v>
+        <v>1.93</v>
       </c>
       <c r="G22" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="n">
-        <v>1.83</v>
+        <v>2.74</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
@@ -5964,25 +5964,25 @@
         <v>1.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S22" t="n">
         <v>1.71</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>3.15</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
@@ -5991,124 +5991,124 @@
         <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6120,7 +6120,7 @@
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
@@ -6138,7 +6138,7 @@
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
@@ -6156,11 +6156,11 @@
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>1.93</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I23" t="n">
         <v>4.2</v>
@@ -6206,7 +6206,7 @@
         <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.13</v>
@@ -6284,7 +6284,7 @@
         <v>40</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL23" t="n">
         <v>970</v>
@@ -6296,7 +6296,7 @@
         <v>4.9</v>
       </c>
       <c r="AO23" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AP23" t="n">
         <v>28</v>
@@ -6308,7 +6308,7 @@
         <v>38</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AT23" t="n">
         <v>24</v>
@@ -6320,10 +6320,10 @@
         <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>2.96</v>
+        <v>6.4</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
@@ -6332,13 +6332,13 @@
         <v>12.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB23" t="n">
         <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD23" t="n">
         <v>16</v>
@@ -6350,7 +6350,7 @@
         <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -6457,13 +6457,13 @@
         <v>1.91</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K24" t="n">
         <v>5.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="G25" t="n">
         <v>1.25</v>
@@ -6708,49 +6708,49 @@
         <v>20</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
         <v>1.21</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.58</v>
       </c>
       <c r="V25" t="n">
         <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="X25" t="n">
         <v>29</v>
@@ -6765,16 +6765,16 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
         <v>17.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AE25" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="AF25" t="n">
         <v>7.6</v>
@@ -6786,7 +6786,7 @@
         <v>48</v>
       </c>
       <c r="AI25" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AJ25" t="n">
         <v>10.5</v>
@@ -6795,10 +6795,10 @@
         <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AN25" t="n">
         <v>4.7</v>
@@ -6807,16 +6807,16 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>36</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT25" t="n">
         <v>7</v>
@@ -6825,10 +6825,10 @@
         <v>12</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX25" t="n">
         <v>6</v>
@@ -6840,89 +6840,89 @@
         <v>32</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
         <v>7</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF25" t="n">
         <v>3.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH25" t="n">
         <v>4.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BJ25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BN25" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BO25" t="n">
         <v>2.8</v>
       </c>
       <c r="BP25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BQ25" t="n">
         <v>4.9</v>
       </c>
       <c r="BR25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BS25" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BU25" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -6953,64 +6953,64 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H26" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I26" t="n">
         <v>3.45</v>
       </c>
       <c r="J26" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K26" t="n">
         <v>3.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="O26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P26" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W26" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z26" t="n">
         <v>22</v>
@@ -7019,10 +7019,10 @@
         <v>60</v>
       </c>
       <c r="AB26" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD26" t="n">
         <v>17</v>
@@ -7031,124 +7031,124 @@
         <v>44</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AJ26" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL26" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO26" t="n">
         <v>55</v>
       </c>
       <c r="AP26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT26" t="n">
         <v>8</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS26" t="n">
+      <c r="AU26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN26" t="n">
         <v>5.6</v>
       </c>
-      <c r="AT26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BO26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS26" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BT26" t="n">
         <v>6.4</v>
@@ -7160,23 +7160,23 @@
         <v>28</v>
       </c>
       <c r="BW26" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY26" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA26" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G27" t="n">
         <v>3.5</v>
       </c>
       <c r="H27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I27" t="n">
         <v>2.66</v>
@@ -7222,25 +7222,25 @@
         <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L27" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
         <v>1.31</v>
@@ -7276,7 +7276,7 @@
         <v>12.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD27" t="n">
         <v>12.5</v>
@@ -7315,28 +7315,28 @@
         <v>26</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR27" t="n">
         <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AT27" t="n">
         <v>10</v>
       </c>
       <c r="AU27" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV27" t="n">
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX27" t="n">
         <v>18.5</v>
@@ -7345,25 +7345,25 @@
         <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA27" t="n">
         <v>34</v>
       </c>
       <c r="BB27" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BC27" t="n">
         <v>32</v>
       </c>
       <c r="BD27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF27" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>6.8</v>
       </c>
       <c r="BG27" t="n">
         <v>20</v>
@@ -7414,7 +7414,7 @@
         <v>20</v>
       </c>
       <c r="BW27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -7461,40 +7461,40 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G28" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H28" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I28" t="n">
         <v>4.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
         <v>3.45</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="O28" t="n">
         <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R28" t="n">
         <v>1.23</v>
@@ -7506,13 +7506,13 @@
         <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X28" t="n">
         <v>11</v>
@@ -7539,7 +7539,7 @@
         <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG28" t="n">
         <v>12</v>
@@ -7551,10 +7551,10 @@
         <v>500</v>
       </c>
       <c r="AJ28" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK28" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL28" t="n">
         <v>150</v>
@@ -7563,34 +7563,34 @@
         <v>500</v>
       </c>
       <c r="AN28" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO28" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP28" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
         <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT28" t="n">
         <v>5.9</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV28" t="n">
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX28" t="n">
         <v>9.4</v>
@@ -7602,7 +7602,7 @@
         <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB28" t="n">
         <v>21</v>
@@ -7611,16 +7611,16 @@
         <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF28" t="n">
         <v>18.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH28" t="n">
         <v>3.05</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
         <v>1.09</v>
       </c>
       <c r="P29" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="Q29" t="n">
         <v>1.27</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="O30" t="n">
         <v>1.07</v>
@@ -8011,7 +8011,7 @@
         <v>1.56</v>
       </c>
       <c r="T30" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="U30" t="n">
         <v>3.55</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -8223,13 +8223,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="G31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H31" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I31" t="n">
         <v>3.5</v>
@@ -8238,37 +8238,37 @@
         <v>2.74</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L31" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M31" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N31" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="O31" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
         <v>1.41</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="R31" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S31" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U31" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V31" t="n">
         <v>1.4</v>
@@ -8277,19 +8277,19 @@
         <v>1.45</v>
       </c>
       <c r="X31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y31" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y31" t="n">
-        <v>8.6</v>
-      </c>
       <c r="Z31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
         <v>160</v>
       </c>
       <c r="AB31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC31" t="n">
         <v>8.4</v>
@@ -8298,13 +8298,13 @@
         <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="AF31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH31" t="n">
         <v>34</v>
@@ -8313,10 +8313,10 @@
         <v>540</v>
       </c>
       <c r="AJ31" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK31" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
@@ -8331,16 +8331,16 @@
         <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -8352,73 +8352,73 @@
         <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ31" t="n">
         <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BB31" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC31" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BI31" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BJ31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO31" t="n">
         <v>4.3</v>
       </c>
       <c r="BP31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ31" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT31" t="n">
         <v>6.4</v>
@@ -8430,23 +8430,23 @@
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G32" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H32" t="n">
         <v>3.65</v>
@@ -8489,10 +8489,10 @@
         <v>5.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K32" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="L32" t="n">
         <v>1.47</v>
@@ -8501,34 +8501,34 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="O32" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P32" t="n">
         <v>1.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.12</v>
       </c>
       <c r="S32" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="T32" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="V32" t="n">
         <v>1.23</v>
       </c>
       <c r="W32" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X32" t="n">
         <v>9.199999999999999</v>
@@ -8537,7 +8537,7 @@
         <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
@@ -8558,7 +8558,7 @@
         <v>15</v>
       </c>
       <c r="AG32" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
         <v>32</v>
@@ -8567,19 +8567,19 @@
         <v>540</v>
       </c>
       <c r="AJ32" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK32" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AL32" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AM32" t="n">
         <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO32" t="n">
         <v>500</v>
@@ -8594,7 +8594,7 @@
         <v>13</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AT32" t="n">
         <v>5.8</v>
@@ -8606,7 +8606,7 @@
         <v>14.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX32" t="n">
         <v>9.199999999999999</v>
@@ -8618,7 +8618,7 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB32" t="n">
         <v>11.5</v>
@@ -8627,16 +8627,16 @@
         <v>14.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF32" t="n">
         <v>6.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H33" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J33" t="n">
         <v>2.66</v>
@@ -8752,13 +8752,13 @@
         <v>1.64</v>
       </c>
       <c r="M33" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N33" t="n">
         <v>2.18</v>
       </c>
       <c r="O33" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P33" t="n">
         <v>1.39</v>
@@ -8770,7 +8770,7 @@
         <v>1.13</v>
       </c>
       <c r="S33" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="T33" t="n">
         <v>2.24</v>
@@ -8779,118 +8779,118 @@
         <v>1.62</v>
       </c>
       <c r="V33" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W33" t="n">
         <v>1.5</v>
       </c>
       <c r="X33" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z33" t="n">
         <v>25</v>
       </c>
       <c r="AA33" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF33" t="n">
         <v>20</v>
       </c>
-      <c r="AE33" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>21</v>
-      </c>
       <c r="AG33" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH33" t="n">
         <v>34</v>
       </c>
       <c r="AI33" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AJ33" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL33" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AM33" t="n">
         <v>500</v>
       </c>
       <c r="AN33" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO33" t="n">
         <v>120</v>
       </c>
       <c r="AP33" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB33" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC33" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH33" t="n">
         <v>2.56</v>
@@ -8902,7 +8902,7 @@
         <v>13</v>
       </c>
       <c r="BK33" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL33" t="n">
         <v>1000</v>
@@ -8911,40 +8911,40 @@
         <v>9.4</v>
       </c>
       <c r="BN33" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ33" t="n">
         <v>7.2</v>
       </c>
       <c r="BR33" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
         <v>8.4</v>
       </c>
       <c r="BT33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV33" t="n">
         <v>38</v>
       </c>
       <c r="BW33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX33" t="n">
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -8985,19 +8985,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G34" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
         <v>3.35</v>
@@ -9036,16 +9036,16 @@
         <v>1.24</v>
       </c>
       <c r="W34" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X34" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y34" t="n">
         <v>16</v>
       </c>
       <c r="Z34" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA34" t="n">
         <v>900</v>
@@ -9054,7 +9054,7 @@
         <v>6.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD34" t="n">
         <v>30</v>
@@ -9069,13 +9069,13 @@
         <v>15.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AI34" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ34" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK34" t="n">
         <v>65</v>
@@ -9099,13 +9099,13 @@
         <v>8.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS34" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU34" t="n">
         <v>6.8</v>
@@ -9114,7 +9114,7 @@
         <v>13.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX34" t="n">
         <v>8.6</v>
@@ -9126,25 +9126,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF34" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB34" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG34" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BH34" t="n">
         <v>2.68</v>
@@ -9168,7 +9168,7 @@
         <v>4.5</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
@@ -9180,7 +9180,7 @@
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT34" t="n">
         <v>8.800000000000001</v>
@@ -9198,17 +9198,17 @@
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G35" t="n">
         <v>2.54</v>
@@ -9260,19 +9260,19 @@
         <v>1.71</v>
       </c>
       <c r="M35" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N35" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="O35" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="P35" t="n">
         <v>1.33</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
         <v>1.12</v>
@@ -9281,7 +9281,7 @@
         <v>7.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U35" t="n">
         <v>1.52</v>
@@ -9293,13 +9293,13 @@
         <v>1.64</v>
       </c>
       <c r="X35" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="Y35" t="n">
         <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA35" t="n">
         <v>500</v>
@@ -9311,31 +9311,31 @@
         <v>7.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE35" t="n">
         <v>130</v>
       </c>
       <c r="AF35" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG35" t="n">
         <v>16</v>
       </c>
       <c r="AH35" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AI35" t="n">
         <v>500</v>
       </c>
       <c r="AJ35" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK35" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL35" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AM35" t="n">
         <v>500</v>
@@ -9347,67 +9347,67 @@
         <v>500</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AQ35" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT35" t="n">
         <v>5</v>
       </c>
-      <c r="AS35" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AU35" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV35" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX35" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH35" t="n">
         <v>2.42</v>
       </c>
       <c r="BI35" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BJ35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK35" t="n">
         <v>5.9</v>
@@ -9416,7 +9416,7 @@
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN35" t="n">
         <v>5.1</v>
@@ -9425,7 +9425,7 @@
         <v>3.85</v>
       </c>
       <c r="BP35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ35" t="n">
         <v>7</v>
@@ -9434,7 +9434,7 @@
         <v>65</v>
       </c>
       <c r="BS35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT35" t="n">
         <v>8</v>
@@ -9446,23 +9446,23 @@
         <v>60</v>
       </c>
       <c r="BW35" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ35" t="n">
         <v>80</v>
       </c>
       <c r="CA35" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -9493,16 +9493,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H36" t="n">
         <v>4.3</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>2.68</v>
@@ -9523,16 +9523,16 @@
         <v>1.28</v>
       </c>
       <c r="P36" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="R36" t="n">
         <v>1.12</v>
       </c>
       <c r="S36" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -9541,16 +9541,16 @@
         <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W36" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X36" t="n">
         <v>950</v>
       </c>
       <c r="Y36" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z36" t="n">
         <v>500</v>
@@ -9562,7 +9562,7 @@
         <v>7.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AD36" t="n">
         <v>950</v>
@@ -9571,22 +9571,22 @@
         <v>500</v>
       </c>
       <c r="AF36" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AG36" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AH36" t="n">
         <v>950</v>
       </c>
       <c r="AI36" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ36" t="n">
         <v>900</v>
       </c>
       <c r="AK36" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AL36" t="n">
         <v>500</v>
@@ -9601,16 +9601,16 @@
         <v>500</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.52</v>
+        <v>4.4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>2.26</v>
+        <v>7</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="AT36" t="n">
         <v>4</v>
@@ -9619,10 +9619,10 @@
         <v>5.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.44</v>
+        <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="AX36" t="n">
         <v>6.8</v>
@@ -9631,28 +9631,28 @@
         <v>7.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="BB36" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="BG36" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="BH36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="G37" t="n">
         <v>2.52</v>
@@ -9792,16 +9792,16 @@
         <v>2.32</v>
       </c>
       <c r="U37" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V37" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W37" t="n">
         <v>1.66</v>
       </c>
       <c r="X37" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Y37" t="n">
         <v>9.4</v>
@@ -9813,7 +9813,7 @@
         <v>500</v>
       </c>
       <c r="AB37" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC37" t="n">
         <v>7.6</v>
@@ -9828,22 +9828,22 @@
         <v>16</v>
       </c>
       <c r="AG37" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH37" t="n">
         <v>32</v>
       </c>
       <c r="AI37" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK37" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL37" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AM37" t="n">
         <v>500</v>
@@ -9855,7 +9855,7 @@
         <v>500</v>
       </c>
       <c r="AP37" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>7.2</v>
@@ -9864,19 +9864,19 @@
         <v>20</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT37" t="n">
         <v>5.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV37" t="n">
         <v>14.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX37" t="n">
         <v>10.5</v>
@@ -9885,28 +9885,28 @@
         <v>10</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="BA37" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB37" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC37" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD37" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
         <v>3.7</v>
       </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J38" t="n">
         <v>3.5</v>
@@ -10019,19 +10019,19 @@
         <v>3.55</v>
       </c>
       <c r="L38" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O38" t="n">
         <v>1.33</v>
       </c>
       <c r="P38" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
         <v>2.02</v>
@@ -10040,7 +10040,7 @@
         <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T38" t="n">
         <v>1.8</v>
@@ -10052,10 +10052,10 @@
         <v>1.35</v>
       </c>
       <c r="W38" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X38" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y38" t="n">
         <v>14</v>
@@ -10064,7 +10064,7 @@
         <v>26</v>
       </c>
       <c r="AA38" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB38" t="n">
         <v>9.800000000000001</v>
@@ -10094,7 +10094,7 @@
         <v>28</v>
       </c>
       <c r="AK38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL38" t="n">
         <v>38</v>
@@ -10103,7 +10103,7 @@
         <v>500</v>
       </c>
       <c r="AN38" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO38" t="n">
         <v>44</v>
@@ -10124,7 +10124,7 @@
         <v>9</v>
       </c>
       <c r="AU38" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV38" t="n">
         <v>14</v>
@@ -10139,7 +10139,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ38" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA38" t="n">
         <v>46</v>
@@ -10154,7 +10154,7 @@
         <v>32</v>
       </c>
       <c r="BE38" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BF38" t="n">
         <v>15</v>
@@ -10163,68 +10163,68 @@
         <v>38</v>
       </c>
       <c r="BH38" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ38" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BN38" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP38" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR38" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT38" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV38" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX38" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ38" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -10255,13 +10255,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G39" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H39" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I39" t="n">
         <v>4.3</v>
@@ -10273,13 +10273,13 @@
         <v>3.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
         <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O39" t="n">
         <v>1.44</v>
@@ -10288,7 +10288,7 @@
         <v>1.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R39" t="n">
         <v>1.24</v>
@@ -10297,7 +10297,7 @@
         <v>4.4</v>
       </c>
       <c r="T39" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U39" t="n">
         <v>1.86</v>
@@ -10306,16 +10306,16 @@
         <v>1.31</v>
       </c>
       <c r="W39" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X39" t="n">
         <v>12.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA39" t="n">
         <v>900</v>
@@ -10324,13 +10324,13 @@
         <v>9.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD39" t="n">
         <v>21</v>
       </c>
       <c r="AE39" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF39" t="n">
         <v>15.5</v>
@@ -10339,10 +10339,10 @@
         <v>14</v>
       </c>
       <c r="AH39" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI39" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ39" t="n">
         <v>34</v>
@@ -10351,10 +10351,10 @@
         <v>34</v>
       </c>
       <c r="AL39" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM39" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN39" t="n">
         <v>28</v>
@@ -10372,7 +10372,7 @@
         <v>21</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT39" t="n">
         <v>6.8</v>
@@ -10384,7 +10384,7 @@
         <v>12</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX39" t="n">
         <v>9.199999999999999</v>
@@ -10396,25 +10396,25 @@
         <v>18</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BC39" t="n">
         <v>19.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF39" t="n">
         <v>16.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BH39" t="n">
         <v>3.05</v>
@@ -10423,10 +10423,10 @@
         <v>2.4</v>
       </c>
       <c r="BJ39" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
@@ -10435,34 +10435,34 @@
         <v>10</v>
       </c>
       <c r="BN39" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO39" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP39" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ39" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR39" t="n">
         <v>38</v>
       </c>
       <c r="BS39" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT39" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU39" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV39" t="n">
         <v>42</v>
       </c>
       <c r="BW39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX39" t="n">
         <v>60</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G40" t="n">
         <v>2.38</v>
@@ -10521,10 +10521,10 @@
         <v>4.3</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K40" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L40" t="n">
         <v>1.38</v>
@@ -10533,28 +10533,28 @@
         <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="O40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R40" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S40" t="n">
         <v>3.15</v>
       </c>
       <c r="T40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="U40" t="n">
         <v>1.11</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.86</v>
       </c>
       <c r="V40" t="n">
         <v>1.31</v>
@@ -10578,7 +10578,7 @@
         <v>970</v>
       </c>
       <c r="AC40" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AD40" t="n">
         <v>970</v>
@@ -10608,7 +10608,7 @@
         <v>500</v>
       </c>
       <c r="AM40" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN40" t="n">
         <v>500</v>
@@ -10617,58 +10617,58 @@
         <v>500</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.17</v>
+        <v>1.77</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.17</v>
+        <v>1.68</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.63</v>
+        <v>4.4</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.63</v>
+        <v>4.2</v>
       </c>
       <c r="AV40" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BB40" t="n">
         <v>1.84</v>
       </c>
-      <c r="AW40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AX40" t="n">
+      <c r="BC40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE40" t="n">
         <v>1.8</v>
       </c>
-      <c r="AY40" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BF40" t="n">
-        <v>1.22</v>
+        <v>2.82</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.17</v>
+        <v>1.68</v>
       </c>
       <c r="BH40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
         <v>3</v>
       </c>
       <c r="O41" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="P41" t="n">
         <v>1.81</v>
@@ -10805,10 +10805,10 @@
         <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="V41" t="n">
         <v>1.1</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G42" t="n">
         <v>2.22</v>
@@ -11032,7 +11032,7 @@
         <v>2.94</v>
       </c>
       <c r="K42" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L42" t="n">
         <v>1.54</v>
@@ -11041,19 +11041,19 @@
         <v>1.12</v>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O42" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P42" t="n">
         <v>1.52</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R42" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S42" t="n">
         <v>5.1</v>
@@ -11128,7 +11128,7 @@
         <v>6.8</v>
       </c>
       <c r="AQ42" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR42" t="n">
         <v>24</v>
@@ -11182,22 +11182,22 @@
         <v>2.84</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ42" t="n">
         <v>12</v>
       </c>
       <c r="BK42" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN42" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO42" t="n">
         <v>3.65</v>
@@ -11206,13 +11206,13 @@
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT42" t="n">
         <v>8</v>
@@ -11224,23 +11224,23 @@
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
@@ -11295,13 +11295,13 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O43" t="n">
         <v>1.01</v>
       </c>
       <c r="P43" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -11528,10 +11528,10 @@
         <v>2.46</v>
       </c>
       <c r="G44" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H44" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I44" t="n">
         <v>3.45</v>
@@ -11543,19 +11543,19 @@
         <v>3.3</v>
       </c>
       <c r="L44" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
         <v>1.42</v>
       </c>
       <c r="P44" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q44" t="n">
         <v>2.24</v>
@@ -11567,7 +11567,7 @@
         <v>4.3</v>
       </c>
       <c r="T44" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U44" t="n">
         <v>2.06</v>
@@ -11579,7 +11579,7 @@
         <v>1.62</v>
       </c>
       <c r="X44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y44" t="n">
         <v>970</v>
@@ -11633,16 +11633,16 @@
         <v>500</v>
       </c>
       <c r="AP44" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ44" t="n">
         <v>9.4</v>
       </c>
       <c r="AR44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT44" t="n">
         <v>8</v>
@@ -11651,31 +11651,31 @@
         <v>6.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX44" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY44" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AZ44" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA44" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB44" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE44" t="n">
         <v>4.5</v>
@@ -11684,13 +11684,13 @@
         <v>22</v>
       </c>
       <c r="BG44" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH44" t="n">
         <v>3.05</v>
       </c>
       <c r="BI44" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ44" t="n">
         <v>10.5</v>
@@ -11702,7 +11702,7 @@
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="BN44" t="n">
         <v>5.2</v>
@@ -11711,16 +11711,16 @@
         <v>4.6</v>
       </c>
       <c r="BP44" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR44" t="n">
         <v>1000</v>
       </c>
       <c r="BS44" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="BT44" t="n">
         <v>6.4</v>
@@ -11732,23 +11732,23 @@
         <v>1000</v>
       </c>
       <c r="BW44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX44" t="n">
         <v>1000</v>
       </c>
       <c r="BY44" t="n">
-        <v>3.45</v>
+        <v>11.5</v>
       </c>
       <c r="BZ44" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA44" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G45" t="n">
         <v>2.04</v>
@@ -11788,34 +11788,34 @@
         <v>4.7</v>
       </c>
       <c r="I45" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K45" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M45" t="n">
         <v>1.11</v>
       </c>
       <c r="N45" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
         <v>1.5</v>
       </c>
       <c r="P45" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R45" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -11833,7 +11833,7 @@
         <v>1.96</v>
       </c>
       <c r="X45" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y45" t="n">
         <v>15</v>
@@ -11887,7 +11887,7 @@
         <v>500</v>
       </c>
       <c r="AP45" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ45" t="n">
         <v>11</v>
@@ -11920,7 +11920,7 @@
         <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB45" t="n">
         <v>20</v>
@@ -11929,10 +11929,10 @@
         <v>21</v>
       </c>
       <c r="BD45" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF45" t="n">
         <v>20</v>
@@ -11941,7 +11941,7 @@
         <v>10.5</v>
       </c>
       <c r="BH45" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI45" t="n">
         <v>2.44</v>
@@ -11950,13 +11950,13 @@
         <v>11.5</v>
       </c>
       <c r="BK45" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN45" t="n">
         <v>4.4</v>
@@ -11968,7 +11968,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ45" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR45" t="n">
         <v>38</v>
@@ -11992,17 +11992,17 @@
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ45" t="n">
         <v>40</v>
       </c>
       <c r="CA45" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G46" t="n">
         <v>2.14</v>
@@ -12084,7 +12084,7 @@
         <v>1.2</v>
       </c>
       <c r="W46" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X46" t="n">
         <v>970</v>
@@ -12141,16 +12141,16 @@
         <v>700</v>
       </c>
       <c r="AP46" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="AR46" t="n">
         <v>2</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AT46" t="n">
         <v>1.64</v>
@@ -12162,19 +12162,19 @@
         <v>1.93</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.06</v>
+        <v>5.3</v>
       </c>
       <c r="AX46" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="AY46" t="n">
-        <v>2.66</v>
+        <v>1.99</v>
       </c>
       <c r="AZ46" t="n">
         <v>1.96</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BB46" t="n">
         <v>1.95</v>
@@ -12192,7 +12192,7 @@
         <v>1.95</v>
       </c>
       <c r="BG46" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BH46" t="n">
         <v>4.1</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -12287,46 +12287,46 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G47" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H47" t="n">
         <v>4.7</v>
       </c>
       <c r="I47" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J47" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K47" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L47" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M47" t="n">
         <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O47" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P47" t="n">
         <v>1.56</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="R47" t="n">
         <v>1.2</v>
       </c>
       <c r="S47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T47" t="n">
         <v>2.14</v>
@@ -12338,7 +12338,7 @@
         <v>1.22</v>
       </c>
       <c r="W47" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X47" t="n">
         <v>11</v>
@@ -12449,16 +12449,16 @@
         <v>5.2</v>
       </c>
       <c r="BH47" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI47" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ47" t="n">
         <v>12.5</v>
       </c>
       <c r="BK47" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
@@ -12473,16 +12473,16 @@
         <v>3.5</v>
       </c>
       <c r="BP47" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ47" t="n">
         <v>6.6</v>
       </c>
       <c r="BR47" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS47" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT47" t="n">
         <v>8.6</v>
@@ -12494,23 +12494,23 @@
         <v>60</v>
       </c>
       <c r="BW47" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ47" t="n">
         <v>42</v>
       </c>
       <c r="CA47" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -12544,43 +12544,43 @@
         <v>5.5</v>
       </c>
       <c r="G48" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H48" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I48" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="J48" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K48" t="n">
         <v>5</v>
       </c>
       <c r="L48" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="M48" t="n">
         <v>1.04</v>
       </c>
       <c r="N48" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O48" t="n">
         <v>1.22</v>
       </c>
       <c r="P48" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R48" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S48" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="T48" t="n">
         <v>1.73</v>
@@ -12589,10 +12589,10 @@
         <v>2.08</v>
       </c>
       <c r="V48" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="W48" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X48" t="n">
         <v>24</v>
@@ -12616,7 +12616,7 @@
         <v>12</v>
       </c>
       <c r="AE48" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF48" t="n">
         <v>60</v>
@@ -12649,37 +12649,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP48" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ48" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR48" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS48" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AT48" t="n">
-        <v>17.5</v>
+        <v>4.3</v>
       </c>
       <c r="AU48" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV48" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AW48" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="AX48" t="n">
         <v>4.7</v>
       </c>
       <c r="AY48" t="n">
-        <v>17.5</v>
+        <v>4.3</v>
       </c>
       <c r="AZ48" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="BA48" t="n">
         <v>4.9</v>
@@ -12694,13 +12694,13 @@
         <v>4.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF48" t="n">
         <v>4.8</v>
       </c>
       <c r="BG48" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH48" t="n">
         <v>4.2</v>
@@ -12718,10 +12718,10 @@
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN48" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO48" t="n">
         <v>5</v>
@@ -12730,19 +12730,19 @@
         <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT48" t="n">
         <v>4.5</v>
       </c>
       <c r="BU48" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BV48" t="n">
         <v>1000</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -12810,16 +12810,16 @@
         <v>3.15</v>
       </c>
       <c r="K49" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M49" t="n">
         <v>1.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O49" t="n">
         <v>1.45</v>
@@ -12957,10 +12957,10 @@
         <v>4.7</v>
       </c>
       <c r="BH49" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI49" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ49" t="n">
         <v>11</v>
@@ -12987,10 +12987,10 @@
         <v>7.6</v>
       </c>
       <c r="BR49" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT49" t="n">
         <v>7.6</v>
@@ -13002,7 +13002,7 @@
         <v>42</v>
       </c>
       <c r="BW49" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
         <v>1.38</v>
       </c>
       <c r="P50" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q50" t="n">
         <v>2.1</v>
@@ -13109,7 +13109,7 @@
         <v>11.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA50" t="n">
         <v>50</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="AS50" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT50" t="n">
         <v>8.199999999999999</v>
@@ -13193,10 +13193,10 @@
         <v>5.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC50" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD50" t="n">
         <v>5.8</v>
@@ -13208,7 +13208,7 @@
         <v>5.6</v>
       </c>
       <c r="BG50" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH50" t="n">
         <v>3.25</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -13303,46 +13303,46 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G51" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="H51" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I51" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L51" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M51" t="n">
         <v>1.05</v>
       </c>
       <c r="N51" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O51" t="n">
         <v>1.23</v>
       </c>
       <c r="P51" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R51" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S51" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="T51" t="n">
         <v>1.68</v>
@@ -13351,10 +13351,10 @@
         <v>2.24</v>
       </c>
       <c r="V51" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W51" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X51" t="n">
         <v>25</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -13557,46 +13557,46 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G52" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H52" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>3.55</v>
       </c>
       <c r="K52" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L52" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M52" t="n">
         <v>1.05</v>
       </c>
       <c r="N52" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
         <v>1.26</v>
       </c>
       <c r="P52" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R52" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S52" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
         <v>1.63</v>
@@ -13605,10 +13605,10 @@
         <v>2.26</v>
       </c>
       <c r="V52" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W52" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X52" t="n">
         <v>21</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -13811,46 +13811,46 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="G53" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I53" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="J53" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K53" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="L53" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N53" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O53" t="n">
         <v>1.19</v>
       </c>
       <c r="P53" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R53" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="S53" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="T53" t="n">
         <v>1.27</v>
@@ -13859,22 +13859,22 @@
         <v>1.92</v>
       </c>
       <c r="V53" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="W53" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X53" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y53" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z53" t="n">
         <v>25</v>
       </c>
       <c r="AA53" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB53" t="n">
         <v>21</v>
@@ -13883,13 +13883,13 @@
         <v>12</v>
       </c>
       <c r="AD53" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE53" t="n">
         <v>29</v>
       </c>
       <c r="AF53" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG53" t="n">
         <v>16</v>
@@ -13904,16 +13904,16 @@
         <v>50</v>
       </c>
       <c r="AK53" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL53" t="n">
         <v>38</v>
       </c>
       <c r="AM53" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO53" t="n">
         <v>16.5</v>
@@ -13922,7 +13922,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR53" t="n">
         <v>1.03</v>
@@ -13931,10 +13931,10 @@
         <v>1.03</v>
       </c>
       <c r="AT53" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU53" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV53" t="n">
         <v>9.199999999999999</v>
@@ -13946,7 +13946,7 @@
         <v>1.03</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ53" t="n">
         <v>10.5</v>
@@ -13967,16 +13967,16 @@
         <v>1.03</v>
       </c>
       <c r="BF53" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG53" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH53" t="n">
         <v>4.6</v>
       </c>
       <c r="BI53" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ53" t="n">
         <v>1000</v>
@@ -14006,10 +14006,10 @@
         <v>1000</v>
       </c>
       <c r="BS53" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BT53" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU53" t="n">
         <v>4.5</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>
@@ -14065,58 +14065,58 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G54" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H54" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I54" t="n">
         <v>3.4</v>
       </c>
       <c r="J54" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K54" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L54" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M54" t="n">
         <v>1.05</v>
       </c>
       <c r="N54" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O54" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P54" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R54" t="n">
         <v>1.5</v>
       </c>
       <c r="S54" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T54" t="n">
         <v>1.6</v>
       </c>
       <c r="U54" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V54" t="n">
         <v>1.42</v>
       </c>
       <c r="W54" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X54" t="n">
         <v>23</v>
@@ -14167,7 +14167,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO54" t="n">
         <v>30</v>
@@ -14182,7 +14182,7 @@
         <v>19</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT54" t="n">
         <v>4.1</v>
@@ -14212,7 +14212,7 @@
         <v>4.9</v>
       </c>
       <c r="BC54" t="n">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="BD54" t="n">
         <v>5</v>
@@ -14233,7 +14233,7 @@
         <v>3.25</v>
       </c>
       <c r="BJ54" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK54" t="n">
         <v>6.8</v>
@@ -14245,7 +14245,7 @@
         <v>60</v>
       </c>
       <c r="BN54" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO54" t="n">
         <v>4.3</v>
@@ -14260,7 +14260,7 @@
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BT54" t="n">
         <v>7</v>
@@ -14284,11 +14284,11 @@
         <v>1000</v>
       </c>
       <c r="CA54" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-19 22:50:25</t>
+          <t>2026-06-20 01:06:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-20.xlsx
@@ -860,10 +860,10 @@
         <v>1.95</v>
       </c>
       <c r="G2" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
         <v>7.2</v>
@@ -872,25 +872,25 @@
         <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
         <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -908,7 +908,7 @@
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -917,7 +917,7 @@
         <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
         <v>900</v>
@@ -926,16 +926,16 @@
         <v>950</v>
       </c>
       <c r="AC2" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>950</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
         <v>950</v>
@@ -944,73 +944,73 @@
         <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BF2" t="n">
         <v>1.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -1111,73 +1111,73 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
         <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
         <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
         <v>7.4</v>
@@ -1192,49 +1192,49 @@
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ3" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
         <v>17.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
         <v>12</v>
@@ -1243,67 +1243,67 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY3" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
         <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BG3" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO3" t="n">
         <v>4.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ3" t="n">
         <v>8.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
         <v>10</v>
@@ -1315,26 +1315,26 @@
         <v>4.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="CA3" t="n">
         <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -1365,178 +1365,178 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.2</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AJ4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK4" t="n">
         <v>32</v>
       </c>
-      <c r="AK4" t="n">
-        <v>65</v>
-      </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AR4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB4" t="n">
         <v>20</v>
       </c>
-      <c r="AS4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF4" t="n">
         <v>9.4</v>
       </c>
-      <c r="AU4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,22 +1545,22 @@
         <v>11</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>7.6</v>
@@ -1569,16 +1569,16 @@
         <v>4.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="G5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H5" t="n">
         <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J5" t="n">
         <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X5" t="n">
         <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
         <v>38</v>
@@ -1685,7 +1685,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
         <v>14</v>
@@ -1730,55 +1730,55 @@
         <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
         <v>6.4</v>
       </c>
       <c r="AS5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG5" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.85</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.24</v>
@@ -1897,34 +1897,34 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
         <v>55</v>
@@ -1945,19 +1945,19 @@
         <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
         <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AI6" t="n">
         <v>55</v>
@@ -1966,25 +1966,25 @@
         <v>50</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL6" t="n">
         <v>40</v>
       </c>
       <c r="AM6" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP6" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR6" t="n">
         <v>18</v>
@@ -1993,34 +1993,34 @@
         <v>50</v>
       </c>
       <c r="AT6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU6" t="n">
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY6" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="BD6" t="n">
         <v>19</v>
@@ -2029,19 +2029,19 @@
         <v>34</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH6" t="n">
         <v>5.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK6" t="n">
         <v>6.8</v>
@@ -2050,31 +2050,31 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>5.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP6" t="n">
         <v>13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR6" t="n">
         <v>20</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT6" t="n">
         <v>8</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2092,11 +2092,11 @@
         <v>13</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -2142,10 +2142,10 @@
         <v>2.98</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>
@@ -2160,13 +2160,13 @@
         <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
         <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.95</v>
@@ -2175,7 +2175,7 @@
         <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
         <v>1.62</v>
@@ -2274,7 +2274,7 @@
         <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD7" t="n">
         <v>6.4</v>
@@ -2283,7 +2283,7 @@
         <v>7</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
         <v>6.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>1.4</v>
       </c>
       <c r="H8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J8" t="n">
         <v>6</v>
@@ -2399,7 +2399,7 @@
         <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
@@ -2420,7 +2420,7 @@
         <v>2.06</v>
       </c>
       <c r="S8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="T8" t="n">
         <v>1.61</v>
@@ -2429,7 +2429,7 @@
         <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
         <v>3.5</v>
@@ -2483,22 +2483,22 @@
         <v>80</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AO8" t="n">
         <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
@@ -2507,10 +2507,10 @@
         <v>12.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>10.5</v>
@@ -2531,10 +2531,10 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
         <v>2.9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -2635,61 +2635,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="H9" t="n">
         <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="T9" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
@@ -2701,25 +2701,25 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>19</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>160</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="AG9" t="n">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
         <v>160</v>
@@ -2743,85 +2743,85 @@
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG9" t="n">
         <v>8</v>
       </c>
-      <c r="AU9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI9" t="n">
         <v>3.05</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BJ9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO9" t="n">
         <v>3.65</v>
       </c>
-      <c r="BA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ9" t="n">
         <v>6</v>
@@ -2836,29 +2836,29 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G10" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>4.5</v>
@@ -2904,10 +2904,10 @@
         <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
@@ -2916,73 +2916,73 @@
         <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.44</v>
       </c>
       <c r="V10" t="n">
         <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X10" t="n">
         <v>120</v>
       </c>
       <c r="Y10" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="Z10" t="n">
         <v>90</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>260</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>150</v>
       </c>
       <c r="AJ10" t="n">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AL10" t="n">
         <v>130</v>
@@ -2991,73 +2991,73 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.86</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.89</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.91</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.76</v>
+        <v>11.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.79</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.79</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.79</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.89</v>
+        <v>8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.88</v>
+        <v>17.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.82</v>
+        <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.87</v>
+        <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.91</v>
+        <v>8.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.87</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BJ10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK10" t="n">
         <v>4.9</v>
@@ -3066,7 +3066,7 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10" t="n">
         <v>5.2</v>
@@ -3078,41 +3078,41 @@
         <v>12</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
         <v>8.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>8</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA10" t="n">
         <v>6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -3143,79 +3143,79 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="G11" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I11" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W11" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.6</v>
-      </c>
       <c r="X11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
         <v>75</v>
       </c>
       <c r="Z11" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AA11" t="n">
         <v>700</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AE11" t="n">
         <v>200</v>
@@ -3224,7 +3224,7 @@
         <v>11.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -3233,46 +3233,46 @@
         <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX11" t="n">
         <v>9.4</v>
@@ -3281,46 +3281,46 @@
         <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD11" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>21</v>
-      </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
         <v>4.5</v>
@@ -3332,41 +3332,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU11" t="n">
         <v>5.3</v>
       </c>
-      <c r="BR11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="CA11" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.24</v>
@@ -3421,31 +3421,31 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W12" t="n">
         <v>2.58</v>
@@ -3460,7 +3460,7 @@
         <v>350</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="n">
         <v>16.5</v>
@@ -3496,7 +3496,7 @@
         <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>5.5</v>
@@ -3508,13 +3508,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -3526,7 +3526,7 @@
         <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX12" t="n">
         <v>9.4</v>
@@ -3538,7 +3538,7 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB12" t="n">
         <v>13.5</v>
@@ -3550,7 +3550,7 @@
         <v>17.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF12" t="n">
         <v>4.7</v>
@@ -3559,28 +3559,28 @@
         <v>10.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI12" t="n">
         <v>3.85</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
         <v>4.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP12" t="n">
         <v>9.800000000000001</v>
@@ -3604,7 +3604,7 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -3657,16 +3657,16 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="K13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>1.5</v>
@@ -3675,25 +3675,25 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U13" t="n">
         <v>1.94</v>
@@ -3702,7 +3702,7 @@
         <v>1.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
         <v>19.5</v>
@@ -3720,7 +3720,7 @@
         <v>120</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
         <v>970</v>
@@ -3729,7 +3729,7 @@
         <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -3762,16 +3762,16 @@
         <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
         <v>4.1</v>
@@ -3780,7 +3780,7 @@
         <v>5.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
         <v>6.2</v>
@@ -3792,25 +3792,25 @@
         <v>6.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.52</v>
+        <v>5.1</v>
       </c>
       <c r="BH13" t="n">
         <v>3.05</v>
@@ -3846,7 +3846,7 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BT13" t="n">
         <v>6.2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>2.98</v>
       </c>
       <c r="H14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I14" t="n">
         <v>2.76</v>
@@ -3920,7 +3920,7 @@
         <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.31</v>
@@ -3929,13 +3929,13 @@
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
         <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
         <v>1.64</v>
@@ -3944,7 +3944,7 @@
         <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
         <v>1.58</v>
@@ -3956,7 +3956,7 @@
         <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
         <v>500</v>
@@ -4022,7 +4022,7 @@
         <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="AT14" t="n">
         <v>7</v>
@@ -4046,7 +4046,7 @@
         <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.56</v>
+        <v>3.7</v>
       </c>
       <c r="BB14" t="n">
         <v>2.64</v>
@@ -4055,13 +4055,13 @@
         <v>6.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.46</v>
+        <v>3.75</v>
       </c>
       <c r="BE14" t="n">
         <v>3.35</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.42</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
         <v>2.64</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H15" t="n">
         <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
         <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
@@ -4189,37 +4189,37 @@
         <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
         <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
         <v>1.87</v>
       </c>
       <c r="U15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X15" t="n">
         <v>12</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
         <v>500</v>
@@ -4231,7 +4231,7 @@
         <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
         <v>120</v>
@@ -4249,7 +4249,7 @@
         <v>160</v>
       </c>
       <c r="AJ15" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AK15" t="n">
         <v>32</v>
@@ -4261,7 +4261,7 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
         <v>150</v>
@@ -4273,10 +4273,10 @@
         <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
         <v>7.2</v>
@@ -4300,7 +4300,7 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -4312,7 +4312,7 @@
         <v>38</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF15" t="n">
         <v>19.5</v>
@@ -4321,46 +4321,46 @@
         <v>11</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN15" t="n">
         <v>5.3</v>
       </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BO15" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BP15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT15" t="n">
         <v>6.8</v>
       </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>7</v>
-      </c>
       <c r="BU15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4372,17 +4372,17 @@
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -4413,25 +4413,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
         <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
         <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -4440,19 +4440,19 @@
         <v>3.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
         <v>1.8</v>
@@ -4464,10 +4464,10 @@
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4485,7 +4485,7 @@
         <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
         <v>500</v>
@@ -4494,7 +4494,7 @@
         <v>25</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>36</v>
@@ -4527,10 +4527,10 @@
         <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
         <v>5.1</v>
@@ -4539,10 +4539,10 @@
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX16" t="n">
         <v>6.4</v>
@@ -4551,28 +4551,28 @@
         <v>6.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="BE16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG16" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="n">
         <v>3.4</v>
@@ -4605,7 +4605,7 @@
         <v>6.2</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS16" t="n">
         <v>8.199999999999999</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H17" t="n">
         <v>2.4</v>
@@ -4682,46 +4682,46 @@
         <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q17" t="n">
         <v>1.98</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
         <v>1.81</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
         <v>1.62</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
         <v>11</v>
@@ -4730,7 +4730,7 @@
         <v>17</v>
       </c>
       <c r="AA17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB17" t="n">
         <v>12.5</v>
@@ -4739,46 +4739,46 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF17" t="n">
         <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ17" t="n">
         <v>70</v>
       </c>
       <c r="AK17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
         <v>380</v>
       </c>
       <c r="AN17" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR17" t="n">
         <v>13.5</v>
@@ -4790,7 +4790,7 @@
         <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
         <v>10</v>
@@ -4811,31 +4811,31 @@
         <v>32</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BD17" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BE17" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BG17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK17" t="n">
         <v>7.4</v>
@@ -4850,16 +4850,16 @@
         <v>6.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ17" t="n">
         <v>7.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS17" t="n">
         <v>8.4</v>
@@ -4877,7 +4877,7 @@
         <v>6.8</v>
       </c>
       <c r="BX17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY17" t="n">
         <v>8.199999999999999</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -4921,46 +4921,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="I18" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="J18" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
         <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T18" t="n">
         <v>1.61</v>
@@ -4969,25 +4969,25 @@
         <v>2.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="W18" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
         <v>970</v>
       </c>
       <c r="AA18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB18" t="n">
         <v>32</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>970</v>
       </c>
       <c r="AC18" t="n">
         <v>9.6</v>
@@ -4996,13 +4996,13 @@
         <v>11.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF18" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
         <v>16.5</v>
@@ -5014,16 +5014,16 @@
         <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>85</v>
+        <v>250</v>
       </c>
       <c r="AM18" t="n">
         <v>70</v>
       </c>
       <c r="AN18" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AO18" t="n">
         <v>55</v>
@@ -5035,43 +5035,43 @@
         <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AT18" t="n">
         <v>13.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX18" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB18" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BC18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BD18" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE18" t="n">
         <v>28</v>
@@ -5083,10 +5083,10 @@
         <v>10</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
@@ -5104,7 +5104,7 @@
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5119,10 +5119,10 @@
         <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -5184,115 +5184,115 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.15</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.46</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.47</v>
       </c>
       <c r="W19" t="n">
         <v>1.54</v>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN19" t="n">
         <v>44</v>
       </c>
-      <c r="AF19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>370</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>600</v>
-      </c>
       <c r="AO19" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>8.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS19" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -5301,58 +5301,58 @@
         <v>6.4</v>
       </c>
       <c r="AV19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="BK19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>10.5</v>
       </c>
       <c r="BN19" t="n">
         <v>5.8</v>
@@ -5361,16 +5361,16 @@
         <v>4.8</v>
       </c>
       <c r="BP19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BS19" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT19" t="n">
         <v>6.4</v>
@@ -5379,26 +5379,26 @@
         <v>5.2</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW19" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ19" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="CA19" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -5441,40 +5441,40 @@
         <v>9.4</v>
       </c>
       <c r="J20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P20" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="T20" t="n">
         <v>1.89</v>
       </c>
       <c r="U20" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>1.12</v>
@@ -5486,70 +5486,70 @@
         <v>28</v>
       </c>
       <c r="Y20" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="Z20" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AA20" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AB20" t="n">
         <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE20" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
         <v>260</v>
       </c>
       <c r="AJ20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AO20" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU20" t="n">
         <v>9.800000000000001</v>
@@ -5558,19 +5558,19 @@
         <v>22</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
@@ -5582,77 +5582,77 @@
         <v>24</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO20" t="n">
         <v>3.4</v>
       </c>
       <c r="BP20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BR20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BS20" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BX20" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G21" t="n">
         <v>9.4</v>
@@ -5692,28 +5692,28 @@
         <v>1.37</v>
       </c>
       <c r="I21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="J21" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="K21" t="n">
         <v>7.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.54</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>1.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q21" t="n">
         <v>1.3</v>
@@ -5728,7 +5728,7 @@
         <v>1.54</v>
       </c>
       <c r="U21" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V21" t="n">
         <v>3.15</v>
@@ -5746,7 +5746,7 @@
         <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="AB21" t="n">
         <v>950</v>
@@ -5788,43 +5788,43 @@
         <v>60</v>
       </c>
       <c r="AO21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="AR21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS21" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS21" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AT21" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX21" t="n">
         <v>4.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.6</v>
+        <v>2.32</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="BB21" t="n">
         <v>4.2</v>
@@ -5836,7 +5836,7 @@
         <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BF21" t="n">
         <v>10.5</v>
@@ -5845,7 +5845,7 @@
         <v>2.96</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI21" t="n">
         <v>3.95</v>
@@ -5854,59 +5854,59 @@
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>2.32</v>
+        <v>5.5</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
         <v>1.71</v>
       </c>
       <c r="T22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="U22" t="n">
         <v>3.15</v>
@@ -6045,70 +6045,70 @@
         <v>970</v>
       </c>
       <c r="AP22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT22" t="n">
         <v>2.26</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR22" t="n">
+      <c r="AU22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV22" t="n">
         <v>2.22</v>
       </c>
-      <c r="AS22" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AW22" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AY22" t="n">
         <v>4.1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6120,13 +6120,13 @@
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -6191,97 +6191,97 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G23" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="H23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="K23" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.07</v>
       </c>
       <c r="P23" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q23" t="n">
         <v>1.23</v>
       </c>
       <c r="R23" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="S23" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="U23" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W23" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X23" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y23" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="Z23" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AA23" t="n">
         <v>100</v>
       </c>
       <c r="AB23" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AC23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG23" t="n">
         <v>970</v>
       </c>
-      <c r="AD23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>26</v>
-      </c>
       <c r="AH23" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AI23" t="n">
         <v>500</v>
       </c>
       <c r="AJ23" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
         <v>970</v>
@@ -6293,22 +6293,22 @@
         <v>38</v>
       </c>
       <c r="AN23" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO23" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AP23" t="n">
         <v>28</v>
       </c>
       <c r="AQ23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AR23" t="n">
         <v>38</v>
       </c>
       <c r="AS23" t="n">
-        <v>30</v>
+        <v>5.8</v>
       </c>
       <c r="AT23" t="n">
         <v>24</v>
@@ -6320,25 +6320,25 @@
         <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD23" t="n">
         <v>16</v>
@@ -6347,10 +6347,10 @@
         <v>30</v>
       </c>
       <c r="BF23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -6469,13 +6469,13 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>1.12</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q24" t="n">
         <v>1.36</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1.21</v>
       </c>
       <c r="G25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="H25" t="n">
         <v>20</v>
@@ -6711,7 +6711,7 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K25" t="n">
         <v>8</v>
@@ -6720,28 +6720,28 @@
         <v>1.31</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
         <v>1.6</v>
@@ -6750,31 +6750,31 @@
         <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y25" t="n">
         <v>60</v>
       </c>
       <c r="Z25" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AD25" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="AE25" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="AF25" t="n">
         <v>7.6</v>
@@ -6783,13 +6783,13 @@
         <v>14.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI25" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AJ25" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AK25" t="n">
         <v>18</v>
@@ -6798,40 +6798,40 @@
         <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AN25" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
         <v>36</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY25" t="n">
         <v>10</v>
@@ -6840,31 +6840,31 @@
         <v>32</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC25" t="n">
         <v>12.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH25" t="n">
         <v>4.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BJ25" t="n">
         <v>15.5</v>
@@ -6882,7 +6882,7 @@
         <v>3.65</v>
       </c>
       <c r="BO25" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BP25" t="n">
         <v>6.8</v>
@@ -6918,11 +6918,11 @@
         <v>10.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G26" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H26" t="n">
         <v>2.94</v>
       </c>
       <c r="I26" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L26" t="n">
         <v>1.48</v>
@@ -6977,13 +6977,13 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.41</v>
       </c>
       <c r="P26" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q26" t="n">
         <v>2.24</v>
@@ -6998,19 +6998,19 @@
         <v>1.88</v>
       </c>
       <c r="U26" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V26" t="n">
         <v>1.45</v>
       </c>
       <c r="W26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X26" t="n">
         <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
         <v>22</v>
@@ -7019,7 +7019,7 @@
         <v>60</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC26" t="n">
         <v>7.6</v>
@@ -7031,10 +7031,10 @@
         <v>44</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
         <v>20</v>
@@ -7064,13 +7064,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
         <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
@@ -7094,7 +7094,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB26" t="n">
         <v>13</v>
@@ -7106,7 +7106,7 @@
         <v>17.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
         <v>23</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -7207,175 +7207,175 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G27" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H27" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I27" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="U27" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG27" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AI27" t="n">
         <v>46</v>
       </c>
       <c r="AJ27" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK27" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AL27" t="n">
         <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS27" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AX27" t="n">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY27" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BC27" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK27" t="n">
         <v>7.6</v>
@@ -7384,43 +7384,43 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN27" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO27" t="n">
         <v>5.4</v>
       </c>
       <c r="BP27" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BQ27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT27" t="n">
         <v>5.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BW27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -7467,13 +7467,13 @@
         <v>2.28</v>
       </c>
       <c r="H28" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I28" t="n">
         <v>4.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
         <v>3.45</v>
@@ -7485,13 +7485,13 @@
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
         <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q28" t="n">
         <v>2.34</v>
@@ -7506,19 +7506,19 @@
         <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="V28" t="n">
         <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X28" t="n">
         <v>11</v>
       </c>
       <c r="Y28" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z28" t="n">
         <v>75</v>
@@ -7578,7 +7578,7 @@
         <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT28" t="n">
         <v>5.9</v>
@@ -7590,7 +7590,7 @@
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX28" t="n">
         <v>9.4</v>
@@ -7602,7 +7602,7 @@
         <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB28" t="n">
         <v>21</v>
@@ -7611,22 +7611,22 @@
         <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF28" t="n">
         <v>18.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH28" t="n">
         <v>3.05</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ28" t="n">
         <v>11</v>
@@ -7647,7 +7647,7 @@
         <v>3.7</v>
       </c>
       <c r="BP28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ28" t="n">
         <v>6.6</v>
@@ -7656,13 +7656,13 @@
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT28" t="n">
         <v>7.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
@@ -7674,7 +7674,7 @@
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v>6.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
@@ -7757,7 +7757,7 @@
         <v>1.68</v>
       </c>
       <c r="T29" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U29" t="n">
         <v>2.92</v>
@@ -7784,7 +7784,7 @@
         <v>23</v>
       </c>
       <c r="AC29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD29" t="n">
         <v>25</v>
@@ -7826,10 +7826,10 @@
         <v>7.8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS29" t="n">
         <v>8.4</v>
@@ -7844,7 +7844,7 @@
         <v>6.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX29" t="n">
         <v>6</v>
@@ -7853,7 +7853,7 @@
         <v>5.2</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA29" t="n">
         <v>7.4</v>
@@ -7862,7 +7862,7 @@
         <v>6.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD29" t="n">
         <v>6.2</v>
@@ -7871,19 +7871,19 @@
         <v>7.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BG29" t="n">
         <v>7.2</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI29" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK29" t="n">
         <v>1.01</v>
@@ -7895,25 +7895,25 @@
         <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO29" t="n">
         <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ29" t="n">
         <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BS29" t="n">
         <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU29" t="n">
         <v>1.01</v>
@@ -7931,14 +7931,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="CA29" t="n">
         <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
         <v>2.16</v>
       </c>
       <c r="H30" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I30" t="n">
         <v>3.5</v>
@@ -7987,19 +7987,19 @@
         <v>5.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O30" t="n">
         <v>1.07</v>
       </c>
       <c r="P30" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q30" t="n">
         <v>1.23</v>
@@ -8014,7 +8014,7 @@
         <v>1.33</v>
       </c>
       <c r="U30" t="n">
-        <v>3.55</v>
+        <v>1.11</v>
       </c>
       <c r="V30" t="n">
         <v>1.4</v>
@@ -8047,7 +8047,7 @@
         <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AG30" t="n">
         <v>15.5</v>
@@ -8080,55 +8080,55 @@
         <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX30" t="n">
         <v>5.4</v>
       </c>
       <c r="AY30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH30" t="n">
         <v>7.6</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -8223,100 +8223,100 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="G31" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="H31" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I31" t="n">
         <v>2.9</v>
-      </c>
-      <c r="I31" t="n">
-        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>2.74</v>
       </c>
       <c r="K31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="O31" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="P31" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="R31" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S31" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V31" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W31" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="X31" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AA31" t="n">
         <v>160</v>
       </c>
       <c r="AB31" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
-        <v>160</v>
+        <v>440</v>
       </c>
       <c r="AF31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG31" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI31" t="n">
         <v>540</v>
       </c>
       <c r="AJ31" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="AK31" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
@@ -8331,34 +8331,34 @@
         <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ31" t="n">
         <v>6.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AS31" t="n">
         <v>5.9</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW31" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>5.9</v>
       </c>
       <c r="AX31" t="n">
         <v>14.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ31" t="n">
         <v>21</v>
@@ -8367,67 +8367,67 @@
         <v>6</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC31" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="BD31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE31" t="n">
         <v>6.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="BG31" t="n">
         <v>6</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="BI31" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BJ31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BO31" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP31" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT31" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BU31" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BV31" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW31" t="n">
         <v>7.2</v>
@@ -8436,17 +8436,17 @@
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -8480,58 +8480,58 @@
         <v>2.1</v>
       </c>
       <c r="G32" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="H32" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I32" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J32" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
         <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="O32" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P32" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R32" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>2.96</v>
+        <v>4.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V32" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W32" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="X32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y32" t="n">
         <v>13</v>
@@ -8558,10 +8558,10 @@
         <v>15</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI32" t="n">
         <v>540</v>
@@ -8579,46 +8579,46 @@
         <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AO32" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AR32" t="n">
         <v>13</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU32" t="n">
         <v>6.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX32" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB32" t="n">
         <v>11.5</v>
@@ -8627,25 +8627,25 @@
         <v>14.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF32" t="n">
         <v>6.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH32" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ32" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK32" t="n">
         <v>1.04</v>
@@ -8657,13 +8657,13 @@
         <v>1.04</v>
       </c>
       <c r="BN32" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP32" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ32" t="n">
         <v>1.04</v>
@@ -8675,10 +8675,10 @@
         <v>1.04</v>
       </c>
       <c r="BT32" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G33" t="n">
         <v>3.05</v>
@@ -8749,28 +8749,28 @@
         <v>3.15</v>
       </c>
       <c r="L33" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M33" t="n">
         <v>1.15</v>
       </c>
       <c r="N33" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O33" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P33" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
         <v>1.13</v>
       </c>
       <c r="S33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T33" t="n">
         <v>2.24</v>
@@ -8797,7 +8797,7 @@
         <v>95</v>
       </c>
       <c r="AB33" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC33" t="n">
         <v>7.4</v>
@@ -8827,7 +8827,7 @@
         <v>55</v>
       </c>
       <c r="AL33" t="n">
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="AM33" t="n">
         <v>500</v>
@@ -8848,19 +8848,19 @@
         <v>17.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AT33" t="n">
         <v>6</v>
       </c>
       <c r="AU33" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV33" t="n">
         <v>13.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AX33" t="n">
         <v>13</v>
@@ -8872,25 +8872,25 @@
         <v>16</v>
       </c>
       <c r="BA33" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BB33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE33" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF33" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BH33" t="n">
         <v>2.56</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
         <v>4.4</v>
@@ -9009,7 +9009,7 @@
         <v>1.13</v>
       </c>
       <c r="N34" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="O34" t="n">
         <v>1.57</v>
@@ -9036,7 +9036,7 @@
         <v>1.24</v>
       </c>
       <c r="W34" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
         <v>8.6</v>
@@ -9054,7 +9054,7 @@
         <v>6.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD34" t="n">
         <v>30</v>
@@ -9075,7 +9075,7 @@
         <v>540</v>
       </c>
       <c r="AJ34" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK34" t="n">
         <v>65</v>
@@ -9144,7 +9144,7 @@
         <v>7.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH34" t="n">
         <v>2.68</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -9257,22 +9257,22 @@
         <v>3.15</v>
       </c>
       <c r="L35" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="M35" t="n">
         <v>1.18</v>
       </c>
       <c r="N35" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="O35" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="P35" t="n">
         <v>1.33</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
         <v>1.12</v>
@@ -9290,7 +9290,7 @@
         <v>1.25</v>
       </c>
       <c r="W35" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X35" t="n">
         <v>6.6</v>
@@ -9347,7 +9347,7 @@
         <v>500</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ35" t="n">
         <v>8</v>
@@ -9374,7 +9374,7 @@
         <v>10</v>
       </c>
       <c r="AY35" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>18</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -9493,73 +9493,73 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="G36" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="H36" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="I36" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="K36" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="L36" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N36" t="n">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="O36" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="P36" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="R36" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S36" t="n">
-        <v>2.46</v>
+        <v>6</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="V36" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W36" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="X36" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y36" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="Z36" t="n">
         <v>500</v>
       </c>
       <c r="AA36" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB36" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC36" t="n">
         <v>16.5</v>
@@ -9571,22 +9571,22 @@
         <v>500</v>
       </c>
       <c r="AF36" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AG36" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AH36" t="n">
         <v>950</v>
       </c>
       <c r="AI36" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ36" t="n">
         <v>900</v>
       </c>
       <c r="AK36" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AL36" t="n">
         <v>500</v>
@@ -9601,64 +9601,64 @@
         <v>500</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>7</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="AT36" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AU36" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AV36" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.92</v>
+        <v>2.06</v>
       </c>
       <c r="AX36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB36" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY36" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>9</v>
-      </c>
       <c r="BC36" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="BF36" t="n">
         <v>5</v>
       </c>
       <c r="BG36" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ36" t="n">
         <v>1000</v>
@@ -9676,7 +9676,7 @@
         <v>1000</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -9747,13 +9747,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G37" t="n">
         <v>2.52</v>
       </c>
       <c r="H37" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I37" t="n">
         <v>4.2</v>
@@ -9762,10 +9762,10 @@
         <v>2.78</v>
       </c>
       <c r="K37" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L37" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="M37" t="n">
         <v>1.16</v>
@@ -9774,13 +9774,13 @@
         <v>2.22</v>
       </c>
       <c r="O37" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P37" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
         <v>1.12</v>
@@ -9795,7 +9795,7 @@
         <v>1.56</v>
       </c>
       <c r="V37" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W37" t="n">
         <v>1.66</v>
@@ -9858,7 +9858,7 @@
         <v>5.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR37" t="n">
         <v>20</v>
@@ -9867,22 +9867,22 @@
         <v>7.6</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU37" t="n">
         <v>5.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW37" t="n">
         <v>7.4</v>
       </c>
       <c r="AX37" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ37" t="n">
         <v>16</v>
@@ -9909,68 +9909,68 @@
         <v>7.6</v>
       </c>
       <c r="BH37" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BJ37" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN37" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO37" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP37" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ37" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR37" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS37" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT37" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU37" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV37" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW37" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX37" t="n">
         <v>1000</v>
       </c>
       <c r="BY37" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ37" t="n">
         <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G38" t="n">
         <v>2.24</v>
@@ -10010,7 +10010,7 @@
         <v>3.7</v>
       </c>
       <c r="I38" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>3.5</v>
@@ -10019,7 +10019,7 @@
         <v>3.55</v>
       </c>
       <c r="L38" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
@@ -10028,19 +10028,19 @@
         <v>3.8</v>
       </c>
       <c r="O38" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P38" t="n">
         <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R38" t="n">
         <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T38" t="n">
         <v>1.8</v>
@@ -10049,13 +10049,13 @@
         <v>2.16</v>
       </c>
       <c r="V38" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W38" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X38" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y38" t="n">
         <v>14</v>
@@ -10094,16 +10094,16 @@
         <v>28</v>
       </c>
       <c r="AK38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL38" t="n">
         <v>38</v>
       </c>
       <c r="AM38" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN38" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO38" t="n">
         <v>44</v>
@@ -10139,7 +10139,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ38" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA38" t="n">
         <v>46</v>
@@ -10163,68 +10163,68 @@
         <v>38</v>
       </c>
       <c r="BH38" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ38" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BN38" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP38" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR38" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS38" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BT38" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV38" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW38" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX38" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA38" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -10258,10 +10258,10 @@
         <v>2.12</v>
       </c>
       <c r="G39" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H39" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I39" t="n">
         <v>4.3</v>
@@ -10276,10 +10276,10 @@
         <v>1.5</v>
       </c>
       <c r="M39" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O39" t="n">
         <v>1.44</v>
@@ -10288,16 +10288,16 @@
         <v>1.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R39" t="n">
         <v>1.24</v>
       </c>
       <c r="S39" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T39" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U39" t="n">
         <v>1.86</v>
@@ -10309,13 +10309,13 @@
         <v>1.78</v>
       </c>
       <c r="X39" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y39" t="n">
         <v>12.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA39" t="n">
         <v>900</v>
@@ -10333,16 +10333,16 @@
         <v>160</v>
       </c>
       <c r="AF39" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG39" t="n">
         <v>14</v>
       </c>
       <c r="AH39" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI39" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="AJ39" t="n">
         <v>34</v>
@@ -10360,7 +10360,7 @@
         <v>28</v>
       </c>
       <c r="AO39" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AP39" t="n">
         <v>7.8</v>
@@ -10372,7 +10372,7 @@
         <v>21</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT39" t="n">
         <v>6.8</v>
@@ -10384,7 +10384,7 @@
         <v>12</v>
       </c>
       <c r="AW39" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AX39" t="n">
         <v>9.199999999999999</v>
@@ -10396,7 +10396,7 @@
         <v>18</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB39" t="n">
         <v>10.5</v>
@@ -10405,16 +10405,16 @@
         <v>19.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF39" t="n">
         <v>16.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH39" t="n">
         <v>3.05</v>
@@ -10426,49 +10426,49 @@
         <v>11.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN39" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO39" t="n">
         <v>3.6</v>
       </c>
       <c r="BP39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ39" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR39" t="n">
         <v>38</v>
       </c>
       <c r="BS39" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT39" t="n">
         <v>7.8</v>
       </c>
       <c r="BU39" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV39" t="n">
         <v>42</v>
       </c>
       <c r="BW39" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX39" t="n">
         <v>60</v>
       </c>
       <c r="BY39" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -10509,52 +10509,52 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G40" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H40" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I40" t="n">
         <v>4.3</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="M40" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O40" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P40" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R40" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S40" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="T40" t="n">
-        <v>1.12</v>
+        <v>1.9</v>
       </c>
       <c r="U40" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="V40" t="n">
         <v>1.31</v>
@@ -10563,176 +10563,176 @@
         <v>1.72</v>
       </c>
       <c r="X40" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y40" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA40" t="n">
         <v>500</v>
       </c>
-      <c r="AA40" t="n">
-        <v>900</v>
-      </c>
       <c r="AB40" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="AD40" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE40" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF40" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH40" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI40" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ40" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AK40" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AL40" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM40" t="n">
         <v>580</v>
       </c>
       <c r="AN40" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AO40" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AP40" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AQ40" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.77</v>
+        <v>11.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.68</v>
+        <v>7.8</v>
       </c>
       <c r="AT40" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AU40" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.02</v>
+        <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.68</v>
+        <v>7.6</v>
       </c>
       <c r="AX40" t="n">
-        <v>2.54</v>
+        <v>11</v>
       </c>
       <c r="AY40" t="n">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.98</v>
+        <v>16.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.68</v>
+        <v>7.8</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.84</v>
+        <v>13</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.76</v>
+        <v>14.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.67</v>
+        <v>7.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.82</v>
+        <v>20</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.68</v>
+        <v>7.8</v>
       </c>
       <c r="BH40" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI40" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ40" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN40" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP40" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR40" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT40" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV40" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX40" t="n">
         <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -10763,46 +10763,46 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="G41" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="I41" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>3.95</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="L41" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="M41" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O41" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="P41" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="R41" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
@@ -10811,182 +10811,182 @@
         <v>1.8</v>
       </c>
       <c r="V41" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="W41" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ41" t="n">
-        <v>900</v>
+        <v>15.5</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH41" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI41" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ41" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK41" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN41" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO41" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP41" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ41" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT41" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU41" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ41" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -11020,37 +11020,37 @@
         <v>1.98</v>
       </c>
       <c r="G42" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="H42" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J42" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K42" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L42" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
         <v>1.12</v>
       </c>
       <c r="N42" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O42" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P42" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R42" t="n">
         <v>1.2</v>
@@ -11065,16 +11065,16 @@
         <v>1.71</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W42" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="X42" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y42" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Z42" t="n">
         <v>500</v>
@@ -11083,13 +11083,13 @@
         <v>900</v>
       </c>
       <c r="AB42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC42" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC42" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AD42" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AE42" t="n">
         <v>500</v>
@@ -11098,28 +11098,28 @@
         <v>11.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AH42" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI42" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ42" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL42" t="n">
         <v>500</v>
       </c>
       <c r="AM42" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN42" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AO42" t="n">
         <v>500</v>
@@ -11128,25 +11128,25 @@
         <v>6.8</v>
       </c>
       <c r="AQ42" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR42" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT42" t="n">
         <v>6</v>
       </c>
       <c r="AU42" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AX42" t="n">
         <v>8.800000000000001</v>
@@ -11155,92 +11155,92 @@
         <v>10</v>
       </c>
       <c r="AZ42" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BA42" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB42" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BC42" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF42" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BG42" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH42" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI42" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ42" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK42" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU42" t="n">
         <v>4.7</v>
       </c>
-      <c r="BO42" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ42" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS42" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT42" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU42" t="n">
-        <v>6</v>
-      </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY42" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BX42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY42" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -11280,10 +11280,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="J43" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
@@ -11319,7 +11319,7 @@
         <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -11525,46 +11525,46 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G44" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H44" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I44" t="n">
         <v>3.45</v>
       </c>
       <c r="J44" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K44" t="n">
         <v>3.3</v>
       </c>
       <c r="L44" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O44" t="n">
         <v>1.42</v>
       </c>
       <c r="P44" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R44" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S44" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T44" t="n">
         <v>1.91</v>
@@ -11576,13 +11576,13 @@
         <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X44" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z44" t="n">
         <v>500</v>
@@ -11597,7 +11597,7 @@
         <v>7.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AE44" t="n">
         <v>500</v>
@@ -11606,7 +11606,7 @@
         <v>970</v>
       </c>
       <c r="AG44" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AH44" t="n">
         <v>23</v>
@@ -11615,16 +11615,16 @@
         <v>500</v>
       </c>
       <c r="AJ44" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK44" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AL44" t="n">
         <v>500</v>
       </c>
       <c r="AM44" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN44" t="n">
         <v>500</v>
@@ -11633,16 +11633,16 @@
         <v>500</v>
       </c>
       <c r="AP44" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ44" t="n">
         <v>9.4</v>
       </c>
       <c r="AR44" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT44" t="n">
         <v>8</v>
@@ -11651,40 +11651,40 @@
         <v>6.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AW44" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AX44" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY44" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB44" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BC44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE44" t="n">
         <v>8</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>4.5</v>
       </c>
       <c r="BF44" t="n">
         <v>22</v>
       </c>
       <c r="BG44" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH44" t="n">
         <v>3.05</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -11782,43 +11782,43 @@
         <v>1.97</v>
       </c>
       <c r="G45" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H45" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K45" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="M45" t="n">
         <v>1.11</v>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="O45" t="n">
         <v>1.5</v>
       </c>
       <c r="P45" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R45" t="n">
         <v>1.22</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T45" t="n">
         <v>2.14</v>
@@ -11830,13 +11830,13 @@
         <v>1.25</v>
       </c>
       <c r="W45" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X45" t="n">
         <v>9.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z45" t="n">
         <v>48</v>
@@ -11854,7 +11854,7 @@
         <v>21</v>
       </c>
       <c r="AE45" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF45" t="n">
         <v>11</v>
@@ -11869,19 +11869,19 @@
         <v>500</v>
       </c>
       <c r="AJ45" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK45" t="n">
         <v>65</v>
       </c>
       <c r="AL45" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM45" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO45" t="n">
         <v>500</v>
@@ -11896,7 +11896,7 @@
         <v>28</v>
       </c>
       <c r="AS45" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT45" t="n">
         <v>6</v>
@@ -11908,7 +11908,7 @@
         <v>17</v>
       </c>
       <c r="AW45" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX45" t="n">
         <v>9.6</v>
@@ -11920,7 +11920,7 @@
         <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB45" t="n">
         <v>20</v>
@@ -11929,16 +11929,16 @@
         <v>21</v>
       </c>
       <c r="BD45" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BF45" t="n">
         <v>20</v>
       </c>
       <c r="BG45" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH45" t="n">
         <v>2.82</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -12033,46 +12033,46 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G46" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="H46" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I46" t="n">
         <v>6</v>
       </c>
       <c r="J46" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K46" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L46" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="M46" t="n">
         <v>1.12</v>
       </c>
       <c r="N46" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="O46" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P46" t="n">
         <v>1.54</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="R46" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S46" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T46" t="n">
         <v>2.16</v>
@@ -12081,13 +12081,13 @@
         <v>1.72</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W46" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="X46" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y46" t="n">
         <v>970</v>
@@ -12102,7 +12102,7 @@
         <v>7.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD46" t="n">
         <v>950</v>
@@ -12141,70 +12141,70 @@
         <v>700</v>
       </c>
       <c r="AP46" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.08</v>
+        <v>2.82</v>
       </c>
       <c r="AR46" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="AW46" t="n">
         <v>5.3</v>
       </c>
       <c r="AX46" t="n">
-        <v>2.08</v>
+        <v>2.64</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.99</v>
+        <v>2.46</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.96</v>
+        <v>2.44</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.08</v>
+        <v>2.68</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="BG46" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="BH46" t="n">
         <v>4.1</v>
       </c>
       <c r="BI46" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BJ46" t="n">
         <v>1000</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.95</v>
+        <v>3.45</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
@@ -12213,7 +12213,7 @@
         <v>1.04</v>
       </c>
       <c r="BN46" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO46" t="n">
         <v>3.5</v>
@@ -12222,19 +12222,19 @@
         <v>1000</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BT46" t="n">
         <v>1000</v>
       </c>
       <c r="BU46" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV46" t="n">
         <v>1000</v>
@@ -12252,11 +12252,11 @@
         <v>1000</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -12287,94 +12287,94 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G47" t="n">
         <v>2.02</v>
       </c>
       <c r="H47" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I47" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J47" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K47" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L47" t="n">
         <v>1.55</v>
       </c>
       <c r="M47" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N47" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O47" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P47" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R47" t="n">
         <v>1.2</v>
       </c>
       <c r="S47" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T47" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U47" t="n">
         <v>1.73</v>
       </c>
       <c r="V47" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W47" t="n">
         <v>1.98</v>
       </c>
       <c r="X47" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z47" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA47" t="n">
         <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC47" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD47" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE47" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF47" t="n">
         <v>12.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI47" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AJ47" t="n">
         <v>25</v>
@@ -12386,7 +12386,7 @@
         <v>70</v>
       </c>
       <c r="AM47" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN47" t="n">
         <v>27</v>
@@ -12401,13 +12401,13 @@
         <v>10</v>
       </c>
       <c r="AR47" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT47" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU47" t="n">
         <v>6</v>
@@ -12416,7 +12416,7 @@
         <v>16.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AX47" t="n">
         <v>8.199999999999999</v>
@@ -12428,7 +12428,7 @@
         <v>19</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BB47" t="n">
         <v>18</v>
@@ -12437,34 +12437,34 @@
         <v>20</v>
       </c>
       <c r="BD47" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BE47" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF47" t="n">
         <v>17</v>
       </c>
       <c r="BG47" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH47" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BI47" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ47" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK47" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL47" t="n">
         <v>1000</v>
       </c>
       <c r="BM47" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN47" t="n">
         <v>4.5</v>
@@ -12476,41 +12476,41 @@
         <v>16.5</v>
       </c>
       <c r="BQ47" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR47" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS47" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT47" t="n">
         <v>8.6</v>
       </c>
       <c r="BU47" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV47" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ47" t="n">
         <v>42</v>
       </c>
       <c r="CA47" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G49" t="n">
         <v>2.2</v>
@@ -12810,34 +12810,34 @@
         <v>3.15</v>
       </c>
       <c r="K49" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L49" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M49" t="n">
         <v>1.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="O49" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P49" t="n">
         <v>1.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R49" t="n">
         <v>1.24</v>
       </c>
       <c r="S49" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T49" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U49" t="n">
         <v>1.84</v>
@@ -12846,10 +12846,10 @@
         <v>1.27</v>
       </c>
       <c r="W49" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X49" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y49" t="n">
         <v>15</v>
@@ -12861,7 +12861,7 @@
         <v>130</v>
       </c>
       <c r="AB49" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC49" t="n">
         <v>9</v>
@@ -12891,7 +12891,7 @@
         <v>32</v>
       </c>
       <c r="AL49" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM49" t="n">
         <v>190</v>
@@ -12909,10 +12909,10 @@
         <v>9.4</v>
       </c>
       <c r="AR49" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT49" t="n">
         <v>5.7</v>
@@ -12924,7 +12924,7 @@
         <v>13</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX49" t="n">
         <v>9</v>
@@ -12936,7 +12936,7 @@
         <v>15.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB49" t="n">
         <v>19.5</v>
@@ -12945,19 +12945,19 @@
         <v>19</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF49" t="n">
         <v>16</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH49" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI49" t="n">
         <v>2.44</v>
@@ -12966,19 +12966,19 @@
         <v>11</v>
       </c>
       <c r="BK49" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>3.45</v>
+        <v>13</v>
       </c>
       <c r="BN49" t="n">
         <v>4.7</v>
       </c>
       <c r="BO49" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP49" t="n">
         <v>17</v>
@@ -13002,13 +13002,13 @@
         <v>42</v>
       </c>
       <c r="BW49" t="n">
-        <v>3.25</v>
+        <v>10.5</v>
       </c>
       <c r="BX49" t="n">
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>3.3</v>
+        <v>11.5</v>
       </c>
       <c r="BZ49" t="n">
         <v>38</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -13049,58 +13049,58 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G50" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H50" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="I50" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J50" t="n">
         <v>3.05</v>
       </c>
       <c r="K50" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L50" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M50" t="n">
         <v>1.08</v>
       </c>
       <c r="N50" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O50" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P50" t="n">
         <v>1.72</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="R50" t="n">
         <v>1.27</v>
       </c>
       <c r="S50" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T50" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U50" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W50" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X50" t="n">
         <v>13.5</v>
@@ -13109,22 +13109,22 @@
         <v>11.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB50" t="n">
         <v>11.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD50" t="n">
         <v>14.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF50" t="n">
         <v>20</v>
@@ -13136,7 +13136,7 @@
         <v>19.5</v>
       </c>
       <c r="AI50" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ50" t="n">
         <v>55</v>
@@ -13151,10 +13151,10 @@
         <v>130</v>
       </c>
       <c r="AN50" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO50" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP50" t="n">
         <v>9</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="AS50" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT50" t="n">
         <v>8.199999999999999</v>
@@ -13178,7 +13178,7 @@
         <v>10</v>
       </c>
       <c r="AW50" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX50" t="n">
         <v>13</v>
@@ -13190,25 +13190,25 @@
         <v>14</v>
       </c>
       <c r="BA50" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC50" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BD50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG50" t="n">
         <v>5.8</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>5.5</v>
       </c>
       <c r="BH50" t="n">
         <v>3.25</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G51" t="n">
         <v>1.86</v>
@@ -13342,7 +13342,7 @@
         <v>1.5</v>
       </c>
       <c r="S51" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T51" t="n">
         <v>1.68</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
         <v>4.1</v>
       </c>
       <c r="L52" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M52" t="n">
         <v>1.05</v>
@@ -13587,22 +13587,22 @@
         <v>1.26</v>
       </c>
       <c r="P52" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R52" t="n">
         <v>1.43</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T52" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U52" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V52" t="n">
         <v>1.51</v>
@@ -13614,7 +13614,7 @@
         <v>21</v>
       </c>
       <c r="Y52" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z52" t="n">
         <v>25</v>
@@ -13629,10 +13629,10 @@
         <v>10.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF52" t="n">
         <v>23</v>
@@ -13671,7 +13671,7 @@
         <v>1.03</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS52" t="n">
         <v>1.03</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
         <v>2.68</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H53" t="n">
         <v>2.4</v>
@@ -13823,7 +13823,7 @@
         <v>2.64</v>
       </c>
       <c r="J53" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K53" t="n">
         <v>4.4</v>
@@ -13841,10 +13841,10 @@
         <v>1.19</v>
       </c>
       <c r="P53" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R53" t="n">
         <v>1.61</v>
@@ -13853,10 +13853,10 @@
         <v>2.44</v>
       </c>
       <c r="T53" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="U53" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="V53" t="n">
         <v>1.61</v>
@@ -13865,7 +13865,7 @@
         <v>1.51</v>
       </c>
       <c r="X53" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y53" t="n">
         <v>19.5</v>
@@ -13883,7 +13883,7 @@
         <v>12</v>
       </c>
       <c r="AD53" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE53" t="n">
         <v>29</v>
@@ -13910,10 +13910,10 @@
         <v>38</v>
       </c>
       <c r="AM53" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN53" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO53" t="n">
         <v>16.5</v>
@@ -13925,16 +13925,16 @@
         <v>11.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS53" t="n">
         <v>1.03</v>
       </c>
       <c r="AT53" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU53" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV53" t="n">
         <v>9.199999999999999</v>
@@ -13967,7 +13967,7 @@
         <v>1.03</v>
       </c>
       <c r="BF53" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG53" t="n">
         <v>10</v>
@@ -13976,7 +13976,7 @@
         <v>4.6</v>
       </c>
       <c r="BI53" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ53" t="n">
         <v>1000</v>
@@ -14024,7 +14024,7 @@
         <v>1000</v>
       </c>
       <c r="BY53" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BZ53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
         <v>3.65</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L54" t="n">
         <v>1.33</v>
@@ -14098,7 +14098,7 @@
         <v>2.26</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R54" t="n">
         <v>1.5</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
